--- a/Financial Analysis/F.xlsx
+++ b/Financial Analysis/F.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E805D6-2262-415F-8DAC-9AA96B36505D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C8FB418-6509-4919-A85D-362D94A701C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{DBEEBD90-F12B-4C1A-B913-1AA5EC76930C}"/>
   </bookViews>
@@ -793,17 +793,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>9.77</v>
+        <v>10.67</v>
       </c>
       <c r="E3" s="5">
-        <v>45771</v>
+        <v>45869</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45771</v>
+        <v>45869</v>
       </c>
       <c r="G3" s="5">
-        <v>45782</v>
+        <v>45952</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -811,11 +811,10 @@
         <v>2</v>
       </c>
       <c r="D4" s="6">
-        <f>3892.6+70.9</f>
-        <v>3963.5</v>
+        <v>3980</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -824,7 +823,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>38723.394999999997</v>
+        <v>42466.6</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -832,11 +831,11 @@
         <v>6</v>
       </c>
       <c r="D6" s="6">
-        <f>24862+15309</f>
-        <v>40171</v>
+        <f>22935+15413+6821</f>
+        <v>45169</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -844,11 +843,11 @@
         <v>7</v>
       </c>
       <c r="D7" s="6">
-        <f>477+49192+19467+80095</f>
-        <v>149231</v>
+        <f>1756+53193+18898+84675</f>
+        <v>158522</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -857,7 +856,7 @@
       </c>
       <c r="D8" s="6">
         <f>D6-D7</f>
-        <v>-109060</v>
+        <v>-113353</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -866,7 +865,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>147783.39499999999</v>
+        <v>155819.6</v>
       </c>
     </row>
   </sheetData>
@@ -1139,10 +1138,20 @@
         <f>AP3-AC3-AB3-AA3</f>
         <v>48211</v>
       </c>
-      <c r="AE3" s="8"/>
-      <c r="AF3" s="8"/>
-      <c r="AG3" s="8"/>
-      <c r="AH3" s="8"/>
+      <c r="AE3" s="8">
+        <v>40659</v>
+      </c>
+      <c r="AF3" s="8">
+        <v>50184</v>
+      </c>
+      <c r="AG3" s="8">
+        <f>AC3*1.05</f>
+        <v>48505.8</v>
+      </c>
+      <c r="AH3" s="8">
+        <f>AD3*1.05</f>
+        <v>50621.55</v>
+      </c>
       <c r="AJ3" s="8">
         <f>SUM(C3:F3)</f>
         <v>160338</v>
@@ -1167,48 +1176,48 @@
         <v>184992</v>
       </c>
       <c r="AQ3" s="8">
-        <f>AP3*1.04</f>
-        <v>192391.67999999999</v>
+        <f>SUM(AE3:AH3)</f>
+        <v>189970.34999999998</v>
       </c>
       <c r="AR3" s="8">
-        <f>AQ3*1.02</f>
-        <v>196239.51360000001</v>
+        <f>AQ3*1.05</f>
+        <v>199468.86749999999</v>
       </c>
       <c r="AS3" s="8">
-        <f t="shared" ref="AS3:BA3" si="0">AR3*1.01</f>
-        <v>198201.90873600001</v>
+        <f>AR3*1.04</f>
+        <v>207447.62220000001</v>
       </c>
       <c r="AT3" s="8">
-        <f t="shared" si="0"/>
-        <v>200183.92782336002</v>
+        <f>AS3*1.03</f>
+        <v>213671.05086600001</v>
       </c>
       <c r="AU3" s="8">
-        <f t="shared" si="0"/>
-        <v>202185.76710159364</v>
+        <f>AT3*1.02</f>
+        <v>217944.47188332002</v>
       </c>
       <c r="AV3" s="8">
-        <f t="shared" si="0"/>
-        <v>204207.62477260956</v>
+        <f t="shared" ref="AS3:BA3" si="0">AU3*1.01</f>
+        <v>220123.91660215321</v>
       </c>
       <c r="AW3" s="8">
         <f t="shared" si="0"/>
-        <v>206249.70102033566</v>
+        <v>222325.15576817474</v>
       </c>
       <c r="AX3" s="8">
         <f t="shared" si="0"/>
-        <v>208312.19803053903</v>
+        <v>224548.40732585647</v>
       </c>
       <c r="AY3" s="8">
         <f t="shared" si="0"/>
-        <v>210395.32001084441</v>
+        <v>226793.89139911503</v>
       </c>
       <c r="AZ3" s="8">
         <f t="shared" si="0"/>
-        <v>212499.27321095287</v>
+        <v>229061.83031310618</v>
       </c>
       <c r="BA3" s="8">
         <f t="shared" si="0"/>
-        <v>214624.2659430624</v>
+        <v>231352.44861623723</v>
       </c>
     </row>
     <row r="4" spans="2:139" x14ac:dyDescent="0.3">
@@ -1306,10 +1315,20 @@
         <f>AP4-AC4-AB4-AA4</f>
         <v>41301</v>
       </c>
-      <c r="AE4" s="6"/>
-      <c r="AF4" s="6"/>
-      <c r="AG4" s="6"/>
-      <c r="AH4" s="6"/>
+      <c r="AE4" s="6">
+        <v>35188</v>
+      </c>
+      <c r="AF4" s="6">
+        <v>44245</v>
+      </c>
+      <c r="AG4" s="6">
+        <f>AG3-AG5</f>
+        <v>42685.104000000007</v>
+      </c>
+      <c r="AH4" s="6">
+        <f>AH3-AH5</f>
+        <v>44546.964</v>
+      </c>
       <c r="AJ4" s="6">
         <f>SUM(C4:F4)</f>
         <v>136269</v>
@@ -1334,48 +1353,48 @@
         <v>158434</v>
       </c>
       <c r="AQ4" s="6">
-        <f t="shared" ref="AQ4:AV4" si="1">AQ3-AQ5</f>
-        <v>165456.84479999999</v>
+        <f>SUM(AE4:AH4)</f>
+        <v>166665.068</v>
       </c>
       <c r="AR4" s="6">
-        <f t="shared" si="1"/>
-        <v>168765.981696</v>
+        <f t="shared" ref="AQ4:AV4" si="1">AR3-AR5</f>
+        <v>173537.91472499998</v>
       </c>
       <c r="AS4" s="6">
         <f t="shared" si="1"/>
-        <v>170453.64151296002</v>
+        <v>178404.95509200002</v>
       </c>
       <c r="AT4" s="6">
         <f t="shared" si="1"/>
-        <v>172158.17792808963</v>
+        <v>183757.10374476001</v>
       </c>
       <c r="AU4" s="6">
         <f t="shared" si="1"/>
-        <v>173879.75970737054</v>
+        <v>187432.24581965522</v>
       </c>
       <c r="AV4" s="6">
         <f t="shared" si="1"/>
-        <v>175618.55730444423</v>
+        <v>189306.56827785177</v>
       </c>
       <c r="AW4" s="6">
         <f t="shared" ref="AW4:BA4" si="2">AW3-AW5</f>
-        <v>177374.74287748866</v>
+        <v>191199.63396063028</v>
       </c>
       <c r="AX4" s="6">
         <f t="shared" si="2"/>
-        <v>179148.49030626356</v>
+        <v>193111.63030023657</v>
       </c>
       <c r="AY4" s="6">
         <f t="shared" si="2"/>
-        <v>180939.97520932619</v>
+        <v>195042.74660323892</v>
       </c>
       <c r="AZ4" s="6">
         <f t="shared" si="2"/>
-        <v>182749.37496141947</v>
+        <v>196993.17406927131</v>
       </c>
       <c r="BA4" s="6">
         <f t="shared" si="2"/>
-        <v>184576.86871103366</v>
+        <v>198963.10580996401</v>
       </c>
     </row>
     <row r="5" spans="2:139" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -1487,17 +1506,29 @@
         <v>7319</v>
       </c>
       <c r="AC5" s="8">
-        <f t="shared" ref="AC5" si="14">AC3-AC4</f>
+        <f t="shared" ref="AC5:AD5" si="14">AC3-AC4</f>
         <v>6028</v>
       </c>
       <c r="AD5" s="8">
-        <f>AD3*0.13</f>
-        <v>6267.43</v>
-      </c>
-      <c r="AE5" s="8"/>
-      <c r="AF5" s="8"/>
-      <c r="AG5" s="8"/>
-      <c r="AH5" s="8"/>
+        <f t="shared" si="14"/>
+        <v>6910</v>
+      </c>
+      <c r="AE5" s="8">
+        <f t="shared" ref="AE5:AF5" si="15">AE3-AE4</f>
+        <v>5471</v>
+      </c>
+      <c r="AF5" s="8">
+        <f t="shared" si="15"/>
+        <v>5939</v>
+      </c>
+      <c r="AG5" s="8">
+        <f>AG3*0.12</f>
+        <v>5820.6959999999999</v>
+      </c>
+      <c r="AH5" s="8">
+        <f>AH3*0.12</f>
+        <v>6074.5860000000002</v>
+      </c>
       <c r="AJ5" s="8">
         <f>AJ3-AJ4</f>
         <v>24069</v>
@@ -1511,64 +1542,64 @@
         <v>14392</v>
       </c>
       <c r="AM5" s="8">
-        <f t="shared" ref="AM5:AP5" si="15">AM3-AM4</f>
+        <f t="shared" ref="AM5:AQ5" si="16">AM3-AM4</f>
         <v>21690</v>
       </c>
       <c r="AN5" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>23660</v>
       </c>
       <c r="AO5" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>25641</v>
       </c>
       <c r="AP5" s="8">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>26558</v>
       </c>
       <c r="AQ5" s="8">
-        <f>AQ3*0.14</f>
-        <v>26934.835200000001</v>
+        <f t="shared" si="16"/>
+        <v>23305.281999999977</v>
       </c>
       <c r="AR5" s="8">
-        <f t="shared" ref="AR5:BA5" si="16">AR3*0.14</f>
-        <v>27473.531904000003</v>
+        <f>AR3*0.13</f>
+        <v>25930.952775000002</v>
       </c>
       <c r="AS5" s="8">
-        <f t="shared" si="16"/>
-        <v>27748.267223040006</v>
+        <f t="shared" ref="AR5:BA5" si="17">AS3*0.14</f>
+        <v>29042.667108000005</v>
       </c>
       <c r="AT5" s="8">
-        <f t="shared" si="16"/>
-        <v>28025.749895270405</v>
+        <f t="shared" si="17"/>
+        <v>29913.947121240002</v>
       </c>
       <c r="AU5" s="8">
-        <f t="shared" si="16"/>
-        <v>28306.00739422311</v>
+        <f t="shared" si="17"/>
+        <v>30512.226063664806</v>
       </c>
       <c r="AV5" s="8">
-        <f t="shared" si="16"/>
-        <v>28589.06746816534</v>
+        <f t="shared" si="17"/>
+        <v>30817.348324301453</v>
       </c>
       <c r="AW5" s="8">
-        <f t="shared" si="16"/>
-        <v>28874.958142846994</v>
+        <f t="shared" si="17"/>
+        <v>31125.521807544465</v>
       </c>
       <c r="AX5" s="8">
-        <f t="shared" si="16"/>
-        <v>29163.707724275468</v>
+        <f t="shared" si="17"/>
+        <v>31436.777025619911</v>
       </c>
       <c r="AY5" s="8">
-        <f t="shared" si="16"/>
-        <v>29455.344801518222</v>
+        <f t="shared" si="17"/>
+        <v>31751.144795876109</v>
       </c>
       <c r="AZ5" s="8">
-        <f t="shared" si="16"/>
-        <v>29749.898249533406</v>
+        <f t="shared" si="17"/>
+        <v>32068.65624383487</v>
       </c>
       <c r="BA5" s="8">
-        <f t="shared" si="16"/>
-        <v>30047.397232028739</v>
+        <f t="shared" si="17"/>
+        <v>32389.342806273216</v>
       </c>
     </row>
     <row r="6" spans="2:139" x14ac:dyDescent="0.3">
@@ -1663,13 +1694,23 @@
         <v>2456</v>
       </c>
       <c r="AD6" s="6">
-        <f t="shared" ref="AD6:AD7" si="17">AP6-AC6-AB6-AA6</f>
+        <f t="shared" ref="AD6:AD7" si="18">AP6-AC6-AB6-AA6</f>
         <v>2777</v>
       </c>
-      <c r="AE6" s="6"/>
-      <c r="AF6" s="6"/>
-      <c r="AG6" s="6"/>
-      <c r="AH6" s="6"/>
+      <c r="AE6" s="6">
+        <v>2431</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>2706</v>
+      </c>
+      <c r="AG6" s="6">
+        <f>AC6*1.01</f>
+        <v>2480.56</v>
+      </c>
+      <c r="AH6" s="6">
+        <f>AD6*1.01</f>
+        <v>2804.77</v>
+      </c>
       <c r="AJ6" s="6">
         <f>SUM(C6:F6)</f>
         <v>11403</v>
@@ -1694,48 +1735,48 @@
         <v>10287</v>
       </c>
       <c r="AQ6" s="6">
-        <f>AP6*0.93</f>
-        <v>9566.91</v>
+        <f t="shared" ref="AQ6:AQ7" si="19">SUM(AE6:AH6)</f>
+        <v>10422.33</v>
       </c>
       <c r="AR6" s="6">
         <f>AQ6*0.95</f>
-        <v>9088.5644999999986</v>
+        <v>9901.2134999999998</v>
       </c>
       <c r="AS6" s="6">
-        <f t="shared" ref="AS6:BA7" si="18">AR6*1.01</f>
-        <v>9179.4501449999989</v>
+        <f t="shared" ref="AS6:BA7" si="20">AR6*1.01</f>
+        <v>10000.225635000001</v>
       </c>
       <c r="AT6" s="6">
-        <f t="shared" si="18"/>
-        <v>9271.244646449999</v>
+        <f t="shared" si="20"/>
+        <v>10100.227891350001</v>
       </c>
       <c r="AU6" s="6">
-        <f t="shared" si="18"/>
-        <v>9363.9570929144993</v>
+        <f t="shared" si="20"/>
+        <v>10201.230170263501</v>
       </c>
       <c r="AV6" s="6">
-        <f t="shared" si="18"/>
-        <v>9457.5966638436439</v>
+        <f t="shared" si="20"/>
+        <v>10303.242471966136</v>
       </c>
       <c r="AW6" s="6">
-        <f t="shared" si="18"/>
-        <v>9552.1726304820804</v>
+        <f t="shared" si="20"/>
+        <v>10406.274896685798</v>
       </c>
       <c r="AX6" s="6">
-        <f t="shared" si="18"/>
-        <v>9647.6943567869021</v>
+        <f t="shared" si="20"/>
+        <v>10510.337645652657</v>
       </c>
       <c r="AY6" s="6">
-        <f t="shared" si="18"/>
-        <v>9744.171300354772</v>
+        <f t="shared" si="20"/>
+        <v>10615.441022109184</v>
       </c>
       <c r="AZ6" s="6">
-        <f t="shared" si="18"/>
-        <v>9841.6130133583192</v>
+        <f t="shared" si="20"/>
+        <v>10721.595432330276</v>
       </c>
       <c r="BA6" s="6">
-        <f t="shared" si="18"/>
-        <v>9940.0291434919018</v>
+        <f t="shared" si="20"/>
+        <v>10828.811386653579</v>
       </c>
     </row>
     <row r="7" spans="2:139" x14ac:dyDescent="0.3">
@@ -1830,13 +1871,23 @@
         <v>2692</v>
       </c>
       <c r="AD7" s="6">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>2902</v>
       </c>
-      <c r="AE7" s="6"/>
-      <c r="AF7" s="6"/>
-      <c r="AG7" s="6"/>
-      <c r="AH7" s="6"/>
+      <c r="AE7" s="6">
+        <v>2721</v>
+      </c>
+      <c r="AF7" s="6">
+        <v>2722</v>
+      </c>
+      <c r="AG7" s="6">
+        <f>AC7*1.01</f>
+        <v>2718.92</v>
+      </c>
+      <c r="AH7" s="6">
+        <f>AD7*0.99</f>
+        <v>2872.98</v>
+      </c>
       <c r="AJ7" s="6">
         <f>SUM(C7:F7)</f>
         <v>9463</v>
@@ -1861,48 +1912,48 @@
         <v>11052</v>
       </c>
       <c r="AQ7" s="6">
-        <f>AP7*1.01</f>
-        <v>11162.52</v>
+        <f t="shared" si="19"/>
+        <v>11034.9</v>
       </c>
       <c r="AR7" s="6">
-        <f t="shared" ref="AR7:BA7" si="19">AQ7*1.01</f>
-        <v>11274.145200000001</v>
+        <f t="shared" ref="AR7" si="21">AQ7*1.01</f>
+        <v>11145.249</v>
       </c>
       <c r="AS7" s="6">
-        <f t="shared" si="18"/>
-        <v>11386.886652000001</v>
+        <f t="shared" si="20"/>
+        <v>11256.701489999999</v>
       </c>
       <c r="AT7" s="6">
-        <f t="shared" si="18"/>
-        <v>11500.755518520002</v>
+        <f t="shared" si="20"/>
+        <v>11369.268504899999</v>
       </c>
       <c r="AU7" s="6">
-        <f t="shared" si="18"/>
-        <v>11615.763073705202</v>
+        <f t="shared" si="20"/>
+        <v>11482.961189948999</v>
       </c>
       <c r="AV7" s="6">
-        <f t="shared" si="18"/>
-        <v>11731.920704442255</v>
+        <f t="shared" si="20"/>
+        <v>11597.790801848489</v>
       </c>
       <c r="AW7" s="6">
-        <f t="shared" si="18"/>
-        <v>11849.239911486677</v>
+        <f t="shared" si="20"/>
+        <v>11713.768709866974</v>
       </c>
       <c r="AX7" s="6">
-        <f t="shared" si="18"/>
-        <v>11967.732310601543</v>
+        <f t="shared" si="20"/>
+        <v>11830.906396965644</v>
       </c>
       <c r="AY7" s="6">
-        <f t="shared" si="18"/>
-        <v>12087.409633707559</v>
+        <f t="shared" si="20"/>
+        <v>11949.2154609353</v>
       </c>
       <c r="AZ7" s="6">
-        <f t="shared" si="18"/>
-        <v>12208.283730044635</v>
+        <f t="shared" si="20"/>
+        <v>12068.707615544654</v>
       </c>
       <c r="BA7" s="6">
-        <f t="shared" si="18"/>
-        <v>12330.366567345081</v>
+        <f t="shared" si="20"/>
+        <v>12189.394691700101</v>
       </c>
     </row>
     <row r="8" spans="2:139" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -1910,121 +1961,133 @@
         <v>27</v>
       </c>
       <c r="C8" s="8">
-        <f t="shared" ref="C8:O8" si="20">C5-C6-C7</f>
+        <f t="shared" ref="C8:O8" si="22">C5-C6-C7</f>
         <v>1121</v>
       </c>
       <c r="D8" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>586</v>
       </c>
       <c r="E8" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>864</v>
       </c>
       <c r="F8" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>632</v>
       </c>
       <c r="G8" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>1202</v>
       </c>
       <c r="H8" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>90</v>
       </c>
       <c r="I8" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-261</v>
       </c>
       <c r="J8" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-457</v>
       </c>
       <c r="K8" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-1558</v>
       </c>
       <c r="L8" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>-2759</v>
       </c>
       <c r="M8" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>2351</v>
       </c>
       <c r="N8" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>73.800000000000182</v>
       </c>
       <c r="O8" s="8">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>2464</v>
       </c>
       <c r="P8" s="8">
-        <f t="shared" ref="P8" si="21">P5-P6-P7</f>
+        <f t="shared" ref="P8" si="23">P5-P6-P7</f>
         <v>-22</v>
       </c>
       <c r="Q8" s="8">
-        <f t="shared" ref="Q8:R8" si="22">Q5-Q6-Q7</f>
+        <f t="shared" ref="Q8:R8" si="24">Q5-Q6-Q7</f>
         <v>1342</v>
       </c>
       <c r="R8" s="8">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>739</v>
       </c>
       <c r="S8" s="8">
-        <f t="shared" ref="S8" si="23">S5-S6-S7</f>
+        <f t="shared" ref="S8" si="25">S5-S6-S7</f>
         <v>1343</v>
       </c>
       <c r="T8" s="8">
-        <f t="shared" ref="T8" si="24">T5-T6-T7</f>
+        <f t="shared" ref="T8" si="26">T5-T6-T7</f>
         <v>2868</v>
       </c>
       <c r="U8" s="8">
-        <f t="shared" ref="U8:W8" si="25">U5-U6-U7</f>
+        <f t="shared" ref="U8:W8" si="27">U5-U6-U7</f>
         <v>504</v>
       </c>
       <c r="V8" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1561</v>
       </c>
       <c r="W8" s="8">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>2113</v>
       </c>
       <c r="X8" s="8">
-        <f t="shared" ref="X8" si="26">X5-X6-X7</f>
+        <f t="shared" ref="X8" si="28">X5-X6-X7</f>
         <v>2461</v>
       </c>
       <c r="Y8" s="8">
-        <f t="shared" ref="Y8:Z8" si="27">Y5-Y6-Y7</f>
+        <f t="shared" ref="Y8:Z8" si="29">Y5-Y6-Y7</f>
         <v>1129</v>
       </c>
       <c r="Z8" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="29"/>
         <v>-245</v>
       </c>
       <c r="AA8" s="8">
-        <f t="shared" ref="AA8" si="28">AA5-AA6-AA7</f>
+        <f t="shared" ref="AA8" si="30">AA5-AA6-AA7</f>
         <v>1225</v>
       </c>
       <c r="AB8" s="8">
-        <f t="shared" ref="AB8" si="29">AB5-AB6-AB7</f>
+        <f t="shared" ref="AB8" si="31">AB5-AB6-AB7</f>
         <v>1883</v>
       </c>
       <c r="AC8" s="8">
-        <f t="shared" ref="AC8:AD8" si="30">AC5-AC6-AC7</f>
+        <f t="shared" ref="AC8:AD8" si="32">AC5-AC6-AC7</f>
         <v>880</v>
       </c>
       <c r="AD8" s="8">
-        <f t="shared" si="30"/>
-        <v>588.43000000000029</v>
-      </c>
-      <c r="AE8" s="8"/>
-      <c r="AF8" s="8"/>
-      <c r="AG8" s="8"/>
-      <c r="AH8" s="8"/>
+        <f t="shared" si="32"/>
+        <v>1231</v>
+      </c>
+      <c r="AE8" s="8">
+        <f t="shared" ref="AE8:AH8" si="33">AE5-AE6-AE7</f>
+        <v>319</v>
+      </c>
+      <c r="AF8" s="8">
+        <f t="shared" si="33"/>
+        <v>511</v>
+      </c>
+      <c r="AG8" s="8">
+        <f t="shared" si="33"/>
+        <v>621.21599999999989</v>
+      </c>
+      <c r="AH8" s="8">
+        <f t="shared" si="33"/>
+        <v>396.83600000000024</v>
+      </c>
       <c r="AJ8" s="8">
         <f>AJ5-AJ6-AJ7</f>
         <v>3203</v>
@@ -2038,64 +2101,64 @@
         <v>-4408</v>
       </c>
       <c r="AM8" s="8">
-        <f t="shared" ref="AM8:AV8" si="31">AM5-AM6-AM7</f>
+        <f t="shared" ref="AM8:AV8" si="34">AM5-AM6-AM7</f>
         <v>4523</v>
       </c>
       <c r="AN8" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>6276</v>
       </c>
       <c r="AO8" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>5458</v>
       </c>
       <c r="AP8" s="8">
-        <f t="shared" si="31"/>
+        <f t="shared" si="34"/>
         <v>5219</v>
       </c>
       <c r="AQ8" s="8">
-        <f t="shared" si="31"/>
-        <v>6205.4052000000011</v>
+        <f t="shared" si="34"/>
+        <v>1848.0519999999779</v>
       </c>
       <c r="AR8" s="8">
-        <f t="shared" si="31"/>
-        <v>7110.8222040000019</v>
+        <f t="shared" si="34"/>
+        <v>4884.4902750000019</v>
       </c>
       <c r="AS8" s="8">
-        <f t="shared" si="31"/>
-        <v>7181.9304260400058</v>
+        <f t="shared" si="34"/>
+        <v>7785.7399830000068</v>
       </c>
       <c r="AT8" s="8">
-        <f t="shared" si="31"/>
-        <v>7253.7497303004038</v>
+        <f t="shared" si="34"/>
+        <v>8444.4507249900016</v>
       </c>
       <c r="AU8" s="8">
-        <f t="shared" si="31"/>
-        <v>7326.2872276034104</v>
+        <f t="shared" si="34"/>
+        <v>8828.0347034523056</v>
       </c>
       <c r="AV8" s="8">
-        <f t="shared" si="31"/>
-        <v>7399.5500998794414</v>
+        <f t="shared" si="34"/>
+        <v>8916.3150504868281</v>
       </c>
       <c r="AW8" s="8">
-        <f t="shared" ref="AW8:BA8" si="32">AW5-AW6-AW7</f>
-        <v>7473.5456008782367</v>
+        <f t="shared" ref="AW8:BA8" si="35">AW5-AW6-AW7</f>
+        <v>9005.4782009916926</v>
       </c>
       <c r="AX8" s="8">
-        <f t="shared" si="32"/>
-        <v>7548.2810568870227</v>
+        <f t="shared" si="35"/>
+        <v>9095.5329830016108</v>
       </c>
       <c r="AY8" s="8">
-        <f t="shared" si="32"/>
-        <v>7623.763867455893</v>
+        <f t="shared" si="35"/>
+        <v>9186.4883128316233</v>
       </c>
       <c r="AZ8" s="8">
-        <f t="shared" si="32"/>
-        <v>7700.0015061304493</v>
+        <f t="shared" si="35"/>
+        <v>9278.3531959599404</v>
       </c>
       <c r="BA8" s="8">
-        <f t="shared" si="32"/>
-        <v>7777.0015211917562</v>
+        <f t="shared" si="35"/>
+        <v>9371.1367279195365</v>
       </c>
     </row>
     <row r="9" spans="2:139" x14ac:dyDescent="0.3">
@@ -2214,10 +2277,20 @@
         <f>AP9-AC9-AB9-AA9</f>
         <v>-1083</v>
       </c>
-      <c r="AE9" s="6"/>
-      <c r="AF9" s="6"/>
-      <c r="AG9" s="6"/>
-      <c r="AH9" s="6"/>
+      <c r="AE9" s="6">
+        <f>288-496-94</f>
+        <v>-302</v>
+      </c>
+      <c r="AF9" s="6">
+        <f>297-577+250</f>
+        <v>-30</v>
+      </c>
+      <c r="AG9" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="6">
+        <v>0</v>
+      </c>
       <c r="AJ9" s="6">
         <f>SUM(C9:F9)</f>
         <v>-1142</v>
@@ -2247,48 +2320,48 @@
         <v>-2014</v>
       </c>
       <c r="AQ9" s="6">
-        <f t="shared" ref="AQ9:AV9" si="33">AP9*1.01</f>
-        <v>-2034.14</v>
+        <f>SUM(AE9:AH9)</f>
+        <v>-332</v>
       </c>
       <c r="AR9" s="6">
-        <f t="shared" si="33"/>
-        <v>-2054.4814000000001</v>
+        <f t="shared" ref="AQ9:AV9" si="36">AQ9*1.01</f>
+        <v>-335.32</v>
       </c>
       <c r="AS9" s="6">
-        <f t="shared" si="33"/>
-        <v>-2075.026214</v>
+        <f t="shared" si="36"/>
+        <v>-338.67320000000001</v>
       </c>
       <c r="AT9" s="6">
-        <f t="shared" si="33"/>
-        <v>-2095.7764761399999</v>
+        <f t="shared" si="36"/>
+        <v>-342.059932</v>
       </c>
       <c r="AU9" s="6">
-        <f t="shared" si="33"/>
-        <v>-2116.7342409014</v>
+        <f t="shared" si="36"/>
+        <v>-345.48053132000001</v>
       </c>
       <c r="AV9" s="6">
-        <f t="shared" si="33"/>
-        <v>-2137.901583310414</v>
+        <f t="shared" si="36"/>
+        <v>-348.9353366332</v>
       </c>
       <c r="AW9" s="6">
-        <f t="shared" ref="AW9" si="34">AV9*1.01</f>
-        <v>-2159.280599143518</v>
+        <f t="shared" ref="AW9" si="37">AV9*1.01</f>
+        <v>-352.42468999953201</v>
       </c>
       <c r="AX9" s="6">
-        <f t="shared" ref="AX9" si="35">AW9*1.01</f>
-        <v>-2180.8734051349534</v>
+        <f t="shared" ref="AX9" si="38">AW9*1.01</f>
+        <v>-355.94893689952733</v>
       </c>
       <c r="AY9" s="6">
-        <f t="shared" ref="AY9" si="36">AX9*1.01</f>
-        <v>-2202.6821391863027</v>
+        <f t="shared" ref="AY9" si="39">AX9*1.01</f>
+        <v>-359.50842626852261</v>
       </c>
       <c r="AZ9" s="6">
-        <f t="shared" ref="AZ9" si="37">AY9*1.01</f>
-        <v>-2224.7089605781657</v>
+        <f t="shared" ref="AZ9" si="40">AY9*1.01</f>
+        <v>-363.10351053120786</v>
       </c>
       <c r="BA9" s="6">
-        <f t="shared" ref="BA9" si="38">AZ9*1.01</f>
-        <v>-2246.9560501839474</v>
+        <f t="shared" ref="BA9" si="41">AZ9*1.01</f>
+        <v>-366.73454563651995</v>
       </c>
     </row>
     <row r="10" spans="2:139" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -2296,121 +2369,133 @@
         <v>29</v>
       </c>
       <c r="C10" s="8">
-        <f t="shared" ref="C10:O10" si="39">C8-C9</f>
+        <f t="shared" ref="C10:O10" si="42">C8-C9</f>
         <v>1919</v>
       </c>
       <c r="D10" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>1349</v>
       </c>
       <c r="E10" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>1094</v>
       </c>
       <c r="F10" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-17</v>
       </c>
       <c r="G10" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>1610</v>
       </c>
       <c r="H10" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>205</v>
       </c>
       <c r="I10" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-19</v>
       </c>
       <c r="J10" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-2436</v>
       </c>
       <c r="K10" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-1146</v>
       </c>
       <c r="L10" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>1084</v>
       </c>
       <c r="M10" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>2756</v>
       </c>
       <c r="N10" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>-1294.1999999999998</v>
       </c>
       <c r="O10" s="8">
-        <f t="shared" si="39"/>
+        <f t="shared" si="42"/>
         <v>3942</v>
       </c>
       <c r="P10" s="8">
-        <f t="shared" ref="P10" si="40">P8-P9</f>
+        <f t="shared" ref="P10" si="43">P8-P9</f>
         <v>735</v>
       </c>
       <c r="Q10" s="8">
-        <f t="shared" ref="Q10:R10" si="41">Q8-Q9</f>
+        <f t="shared" ref="Q10:R10" si="44">Q8-Q9</f>
         <v>1885</v>
       </c>
       <c r="R10" s="8">
-        <f t="shared" si="41"/>
+        <f t="shared" si="44"/>
         <v>11218</v>
       </c>
       <c r="S10" s="8">
-        <f t="shared" ref="S10" si="42">S8-S9</f>
+        <f t="shared" ref="S10" si="45">S8-S9</f>
         <v>-3848</v>
       </c>
       <c r="T10" s="8">
-        <f t="shared" ref="T10" si="43">T8-T9</f>
+        <f t="shared" ref="T10" si="46">T8-T9</f>
         <v>791</v>
       </c>
       <c r="U10" s="8">
-        <f t="shared" ref="U10:W10" si="44">U8-U9</f>
+        <f t="shared" ref="U10:W10" si="47">U8-U9</f>
         <v>-1125</v>
       </c>
       <c r="V10" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>1166</v>
       </c>
       <c r="W10" s="8">
-        <f t="shared" si="44"/>
+        <f t="shared" si="47"/>
         <v>2159</v>
       </c>
       <c r="X10" s="8">
-        <f t="shared" ref="X10" si="45">X8-X9</f>
+        <f t="shared" ref="X10" si="48">X8-X9</f>
         <v>2288</v>
       </c>
       <c r="Y10" s="8">
-        <f t="shared" ref="Y10:Z10" si="46">Y8-Y9</f>
+        <f t="shared" ref="Y10:Z10" si="49">Y8-Y9</f>
         <v>1387</v>
       </c>
       <c r="Z10" s="8">
-        <f t="shared" si="46"/>
+        <f t="shared" si="49"/>
         <v>-1867</v>
       </c>
       <c r="AA10" s="8">
-        <f t="shared" ref="AA10" si="47">AA8-AA9</f>
+        <f t="shared" ref="AA10" si="50">AA8-AA9</f>
         <v>1612</v>
       </c>
       <c r="AB10" s="8">
-        <f t="shared" ref="AB10" si="48">AB8-AB9</f>
+        <f t="shared" ref="AB10" si="51">AB8-AB9</f>
         <v>2438</v>
       </c>
       <c r="AC10" s="8">
-        <f t="shared" ref="AC10:AD10" si="49">AC8-AC9</f>
+        <f t="shared" ref="AC10:AD10" si="52">AC8-AC9</f>
         <v>869</v>
       </c>
       <c r="AD10" s="8">
-        <f t="shared" si="49"/>
-        <v>1671.4300000000003</v>
-      </c>
-      <c r="AE10" s="8"/>
-      <c r="AF10" s="8"/>
-      <c r="AG10" s="8"/>
-      <c r="AH10" s="8"/>
+        <f t="shared" si="52"/>
+        <v>2314</v>
+      </c>
+      <c r="AE10" s="8">
+        <f t="shared" ref="AE10:AH10" si="53">AE8-AE9</f>
+        <v>621</v>
+      </c>
+      <c r="AF10" s="8">
+        <f t="shared" si="53"/>
+        <v>541</v>
+      </c>
+      <c r="AG10" s="8">
+        <f t="shared" si="53"/>
+        <v>621.21599999999989</v>
+      </c>
+      <c r="AH10" s="8">
+        <f t="shared" si="53"/>
+        <v>396.83600000000024</v>
+      </c>
       <c r="AJ10" s="8">
         <f>AJ8-AJ9</f>
         <v>4345</v>
@@ -2428,60 +2513,60 @@
         <v>17780</v>
       </c>
       <c r="AN10" s="8">
-        <f t="shared" ref="AN10:AV10" si="50">AN8-AN9</f>
+        <f t="shared" ref="AN10:AV10" si="54">AN8-AN9</f>
         <v>-3016</v>
       </c>
       <c r="AO10" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v>3967</v>
       </c>
       <c r="AP10" s="8">
-        <f t="shared" si="50"/>
+        <f t="shared" si="54"/>
         <v>7233</v>
       </c>
       <c r="AQ10" s="8">
-        <f t="shared" si="50"/>
-        <v>8239.5452000000005</v>
+        <f t="shared" si="54"/>
+        <v>2180.0519999999779</v>
       </c>
       <c r="AR10" s="8">
-        <f t="shared" si="50"/>
-        <v>9165.3036040000025</v>
+        <f t="shared" si="54"/>
+        <v>5219.8102750000016</v>
       </c>
       <c r="AS10" s="8">
-        <f t="shared" si="50"/>
-        <v>9256.9566400400054</v>
+        <f t="shared" si="54"/>
+        <v>8124.4131830000069</v>
       </c>
       <c r="AT10" s="8">
-        <f t="shared" si="50"/>
-        <v>9349.5262064404033</v>
+        <f t="shared" si="54"/>
+        <v>8786.5106569900017</v>
       </c>
       <c r="AU10" s="8">
-        <f t="shared" si="50"/>
-        <v>9443.0214685048104</v>
+        <f t="shared" si="54"/>
+        <v>9173.5152347723051</v>
       </c>
       <c r="AV10" s="8">
-        <f t="shared" si="50"/>
-        <v>9537.4516831898545</v>
+        <f t="shared" si="54"/>
+        <v>9265.2503871200279</v>
       </c>
       <c r="AW10" s="8">
-        <f t="shared" ref="AW10:BA10" si="51">AW8-AW9</f>
-        <v>9632.8262000217546</v>
+        <f t="shared" ref="AW10:BA10" si="55">AW8-AW9</f>
+        <v>9357.9028909912249</v>
       </c>
       <c r="AX10" s="8">
-        <f t="shared" si="51"/>
-        <v>9729.1544620219756</v>
+        <f t="shared" si="55"/>
+        <v>9451.4819199011381</v>
       </c>
       <c r="AY10" s="8">
-        <f t="shared" si="51"/>
-        <v>9826.4460066421962</v>
+        <f t="shared" si="55"/>
+        <v>9545.9967391001464</v>
       </c>
       <c r="AZ10" s="8">
-        <f t="shared" si="51"/>
-        <v>9924.7104667086151</v>
+        <f t="shared" si="55"/>
+        <v>9641.456706491148</v>
       </c>
       <c r="BA10" s="8">
-        <f t="shared" si="51"/>
-        <v>10023.957571375704</v>
+        <f t="shared" si="55"/>
+        <v>9737.8712735560566</v>
       </c>
     </row>
     <row r="11" spans="2:139" x14ac:dyDescent="0.3">
@@ -2579,10 +2664,20 @@
         <f>AP11-AC11-AB11-AA11</f>
         <v>483</v>
       </c>
-      <c r="AE11" s="6"/>
-      <c r="AF11" s="6"/>
-      <c r="AG11" s="6"/>
-      <c r="AH11" s="6"/>
+      <c r="AE11" s="6">
+        <v>148</v>
+      </c>
+      <c r="AF11" s="6">
+        <v>570</v>
+      </c>
+      <c r="AG11" s="6">
+        <f>AG10*0.2</f>
+        <v>124.24319999999999</v>
+      </c>
+      <c r="AH11" s="6">
+        <f>AH10*0.2</f>
+        <v>79.367200000000054</v>
+      </c>
       <c r="AJ11" s="6">
         <f>SUM(C11:F11)</f>
         <v>650</v>
@@ -2607,48 +2702,48 @@
         <v>1339</v>
       </c>
       <c r="AQ11" s="6">
-        <f>AQ10*0.18</f>
-        <v>1483.118136</v>
+        <f t="shared" ref="AQ11:AQ12" si="56">SUM(AE11:AH11)</f>
+        <v>921.61040000000003</v>
       </c>
       <c r="AR11" s="6">
-        <f t="shared" ref="AR11:BA11" si="52">AR10*0.18</f>
-        <v>1649.7546487200004</v>
+        <f t="shared" ref="AR11:BA11" si="57">AR10*0.18</f>
+        <v>939.56584950000024</v>
       </c>
       <c r="AS11" s="6">
-        <f t="shared" si="52"/>
-        <v>1666.2521952072009</v>
+        <f t="shared" si="57"/>
+        <v>1462.3943729400012</v>
       </c>
       <c r="AT11" s="6">
-        <f t="shared" si="52"/>
-        <v>1682.9147171592724</v>
+        <f t="shared" si="57"/>
+        <v>1581.5719182582002</v>
       </c>
       <c r="AU11" s="6">
-        <f t="shared" si="52"/>
-        <v>1699.7438643308658</v>
+        <f t="shared" si="57"/>
+        <v>1651.2327422590149</v>
       </c>
       <c r="AV11" s="6">
-        <f t="shared" si="52"/>
-        <v>1716.7413029741738</v>
+        <f t="shared" si="57"/>
+        <v>1667.7450696816049</v>
       </c>
       <c r="AW11" s="6">
-        <f t="shared" si="52"/>
-        <v>1733.9087160039157</v>
+        <f t="shared" si="57"/>
+        <v>1684.4225203784204</v>
       </c>
       <c r="AX11" s="6">
-        <f t="shared" si="52"/>
-        <v>1751.2478031639555</v>
+        <f t="shared" si="57"/>
+        <v>1701.2667455822047</v>
       </c>
       <c r="AY11" s="6">
-        <f t="shared" si="52"/>
-        <v>1768.7602811955953</v>
+        <f t="shared" si="57"/>
+        <v>1718.2794130380264</v>
       </c>
       <c r="AZ11" s="6">
-        <f t="shared" si="52"/>
-        <v>1786.4478840075506</v>
+        <f t="shared" si="57"/>
+        <v>1735.4622071684066</v>
       </c>
       <c r="BA11" s="6">
-        <f t="shared" si="52"/>
-        <v>1804.3123628476267</v>
+        <f t="shared" si="57"/>
+        <v>1752.8168292400901</v>
       </c>
     </row>
     <row r="12" spans="2:139" x14ac:dyDescent="0.3">
@@ -2746,10 +2841,18 @@
         <f>AP12-AC12-AB12-AA12</f>
         <v>7</v>
       </c>
-      <c r="AE12" s="6"/>
-      <c r="AF12" s="6"/>
-      <c r="AG12" s="6"/>
-      <c r="AH12" s="6"/>
+      <c r="AE12" s="6">
+        <v>2</v>
+      </c>
+      <c r="AF12" s="6">
+        <v>7</v>
+      </c>
+      <c r="AG12" s="6">
+        <v>5</v>
+      </c>
+      <c r="AH12" s="6">
+        <v>5</v>
+      </c>
       <c r="AJ12" s="6">
         <f>SUM(C12:F12)</f>
         <v>18</v>
@@ -2774,48 +2877,48 @@
         <v>15</v>
       </c>
       <c r="AQ12" s="6">
-        <f t="shared" ref="AQ12:AV12" si="53">AP12*1.005</f>
-        <v>15.074999999999999</v>
+        <f t="shared" si="56"/>
+        <v>19</v>
       </c>
       <c r="AR12" s="6">
-        <f t="shared" si="53"/>
-        <v>15.150374999999997</v>
+        <f t="shared" ref="AQ12:AV12" si="58">AQ12*1.005</f>
+        <v>19.094999999999999</v>
       </c>
       <c r="AS12" s="6">
-        <f t="shared" si="53"/>
-        <v>15.226126874999995</v>
+        <f t="shared" si="58"/>
+        <v>19.190474999999996</v>
       </c>
       <c r="AT12" s="6">
-        <f t="shared" si="53"/>
-        <v>15.302257509374993</v>
+        <f t="shared" si="58"/>
+        <v>19.286427374999995</v>
       </c>
       <c r="AU12" s="6">
-        <f t="shared" si="53"/>
-        <v>15.378768796921866</v>
+        <f t="shared" si="58"/>
+        <v>19.382859511874994</v>
       </c>
       <c r="AV12" s="6">
-        <f t="shared" si="53"/>
-        <v>15.455662640906475</v>
+        <f t="shared" si="58"/>
+        <v>19.479773809434366</v>
       </c>
       <c r="AW12" s="6">
-        <f t="shared" ref="AW12" si="54">AV12*1.005</f>
-        <v>15.532940954111005</v>
+        <f t="shared" ref="AW12" si="59">AV12*1.005</f>
+        <v>19.577172678481535</v>
       </c>
       <c r="AX12" s="6">
-        <f t="shared" ref="AX12" si="55">AW12*1.005</f>
-        <v>15.610605658881559</v>
+        <f t="shared" ref="AX12" si="60">AW12*1.005</f>
+        <v>19.675058541873941</v>
       </c>
       <c r="AY12" s="6">
-        <f t="shared" ref="AY12" si="56">AX12*1.005</f>
-        <v>15.688658687175964</v>
+        <f t="shared" ref="AY12" si="61">AX12*1.005</f>
+        <v>19.773433834583308</v>
       </c>
       <c r="AZ12" s="6">
-        <f t="shared" ref="AZ12" si="57">AY12*1.005</f>
-        <v>15.767101980611843</v>
+        <f t="shared" ref="AZ12" si="62">AY12*1.005</f>
+        <v>19.872301003756224</v>
       </c>
       <c r="BA12" s="6">
-        <f t="shared" ref="BA12" si="58">AZ12*1.005</f>
-        <v>15.845937490514901</v>
+        <f t="shared" ref="BA12" si="63">AZ12*1.005</f>
+        <v>19.971662508775005</v>
       </c>
     </row>
     <row r="13" spans="2:139" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -2823,121 +2926,133 @@
         <v>31</v>
       </c>
       <c r="C13" s="8">
-        <f t="shared" ref="C13:O13" si="59">C10-C11-C12</f>
+        <f t="shared" ref="C13:O13" si="64">C10-C11-C12</f>
         <v>1736</v>
       </c>
       <c r="D13" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="64"/>
         <v>1066</v>
       </c>
       <c r="E13" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="64"/>
         <v>991</v>
       </c>
       <c r="F13" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="64"/>
         <v>-116</v>
       </c>
       <c r="G13" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="64"/>
         <v>1146</v>
       </c>
       <c r="H13" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="64"/>
         <v>148</v>
       </c>
       <c r="I13" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="64"/>
         <v>425</v>
       </c>
       <c r="J13" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="64"/>
         <v>-1672</v>
       </c>
       <c r="K13" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="64"/>
         <v>-1993</v>
       </c>
       <c r="L13" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="64"/>
         <v>1117</v>
       </c>
       <c r="M13" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="64"/>
         <v>2385</v>
       </c>
       <c r="N13" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="64"/>
         <v>-272.19999999999982</v>
       </c>
       <c r="O13" s="8">
-        <f t="shared" si="59"/>
+        <f t="shared" si="64"/>
         <v>3262</v>
       </c>
       <c r="P13" s="8">
-        <f t="shared" ref="P13" si="60">P10-P11-P12</f>
+        <f t="shared" ref="P13" si="65">P10-P11-P12</f>
         <v>561</v>
       </c>
       <c r="Q13" s="8">
-        <f t="shared" ref="Q13:R13" si="61">Q10-Q11-Q12</f>
+        <f t="shared" ref="Q13:R13" si="66">Q10-Q11-Q12</f>
         <v>1832</v>
       </c>
       <c r="R13" s="8">
-        <f t="shared" si="61"/>
+        <f t="shared" si="66"/>
         <v>12282</v>
       </c>
       <c r="S13" s="8">
-        <f t="shared" ref="S13" si="62">S10-S11-S12</f>
+        <f t="shared" ref="S13" si="67">S10-S11-S12</f>
         <v>-3110</v>
       </c>
       <c r="T13" s="8">
-        <f t="shared" ref="T13" si="63">T10-T11-T12</f>
+        <f t="shared" ref="T13" si="68">T10-T11-T12</f>
         <v>667</v>
       </c>
       <c r="U13" s="8">
-        <f t="shared" ref="U13:W13" si="64">U10-U11-U12</f>
+        <f t="shared" ref="U13:W13" si="69">U10-U11-U12</f>
         <v>-827</v>
       </c>
       <c r="V13" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>1289</v>
       </c>
       <c r="W13" s="8">
-        <f t="shared" si="64"/>
+        <f t="shared" si="69"/>
         <v>1757</v>
       </c>
       <c r="X13" s="8">
-        <f t="shared" ref="X13" si="65">X10-X11-X12</f>
+        <f t="shared" ref="X13" si="70">X10-X11-X12</f>
         <v>1917</v>
       </c>
       <c r="Y13" s="8">
-        <f t="shared" ref="Y13:Z13" si="66">Y10-Y11-Y12</f>
+        <f t="shared" ref="Y13:Z13" si="71">Y10-Y11-Y12</f>
         <v>1199</v>
       </c>
       <c r="Z13" s="8">
-        <f t="shared" si="66"/>
+        <f t="shared" si="71"/>
         <v>-526</v>
       </c>
       <c r="AA13" s="8">
-        <f t="shared" ref="AA13" si="67">AA10-AA11-AA12</f>
+        <f t="shared" ref="AA13" si="72">AA10-AA11-AA12</f>
         <v>1332</v>
       </c>
       <c r="AB13" s="8">
-        <f t="shared" ref="AB13" si="68">AB10-AB11-AB12</f>
+        <f t="shared" ref="AB13" si="73">AB10-AB11-AB12</f>
         <v>1831</v>
       </c>
       <c r="AC13" s="8">
-        <f t="shared" ref="AC13:AD13" si="69">AC10-AC11-AC12</f>
+        <f t="shared" ref="AC13:AD13" si="74">AC10-AC11-AC12</f>
         <v>892</v>
       </c>
       <c r="AD13" s="8">
-        <f t="shared" si="69"/>
-        <v>1181.4300000000003</v>
-      </c>
-      <c r="AE13" s="8"/>
-      <c r="AF13" s="8"/>
-      <c r="AG13" s="8"/>
-      <c r="AH13" s="8"/>
+        <f t="shared" si="74"/>
+        <v>1824</v>
+      </c>
+      <c r="AE13" s="8">
+        <f t="shared" ref="AE13:AH13" si="75">AE10-AE11-AE12</f>
+        <v>471</v>
+      </c>
+      <c r="AF13" s="8">
+        <f t="shared" si="75"/>
+        <v>-36</v>
+      </c>
+      <c r="AG13" s="8">
+        <f t="shared" si="75"/>
+        <v>491.97279999999989</v>
+      </c>
+      <c r="AH13" s="8">
+        <f t="shared" si="75"/>
+        <v>312.46880000000021</v>
+      </c>
       <c r="AJ13" s="8">
         <f>AJ10-AJ11-AJ12</f>
         <v>3677</v>
@@ -2951,408 +3066,408 @@
         <v>-1279</v>
       </c>
       <c r="AM13" s="8">
-        <f t="shared" ref="AM13:AV13" si="70">AM10-AM11-AM12</f>
+        <f t="shared" ref="AM13:AV13" si="76">AM10-AM11-AM12</f>
         <v>17937</v>
       </c>
       <c r="AN13" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="76"/>
         <v>-1981</v>
       </c>
       <c r="AO13" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="76"/>
         <v>4347</v>
       </c>
       <c r="AP13" s="8">
-        <f t="shared" si="70"/>
+        <f t="shared" si="76"/>
         <v>5879</v>
       </c>
       <c r="AQ13" s="8">
-        <f t="shared" si="70"/>
-        <v>6741.3520640000006</v>
+        <f t="shared" si="76"/>
+        <v>1239.4415999999778</v>
       </c>
       <c r="AR13" s="8">
-        <f t="shared" si="70"/>
-        <v>7500.3985802800016</v>
+        <f t="shared" si="76"/>
+        <v>4261.1494255000007</v>
       </c>
       <c r="AS13" s="8">
-        <f t="shared" si="70"/>
-        <v>7575.4783179578044</v>
+        <f t="shared" si="76"/>
+        <v>6642.8283350600059</v>
       </c>
       <c r="AT13" s="8">
-        <f t="shared" si="70"/>
-        <v>7651.3092317717565</v>
+        <f t="shared" si="76"/>
+        <v>7185.6523113568019</v>
       </c>
       <c r="AU13" s="8">
-        <f t="shared" si="70"/>
-        <v>7727.8988353770228</v>
+        <f t="shared" si="76"/>
+        <v>7502.8996330014152</v>
       </c>
       <c r="AV13" s="8">
-        <f t="shared" si="70"/>
-        <v>7805.2547175747741</v>
+        <f t="shared" si="76"/>
+        <v>7578.025543628989</v>
       </c>
       <c r="AW13" s="8">
-        <f t="shared" ref="AW13:BA13" si="71">AW10-AW11-AW12</f>
-        <v>7883.3845430637275</v>
+        <f t="shared" ref="AW13:BA13" si="77">AW10-AW11-AW12</f>
+        <v>7653.9031979343226</v>
       </c>
       <c r="AX13" s="8">
-        <f t="shared" si="71"/>
-        <v>7962.2960531991384</v>
+        <f t="shared" si="77"/>
+        <v>7730.5401157770593</v>
       </c>
       <c r="AY13" s="8">
-        <f t="shared" si="71"/>
-        <v>8041.9970667594253</v>
+        <f t="shared" si="77"/>
+        <v>7807.9438922275367</v>
       </c>
       <c r="AZ13" s="8">
-        <f t="shared" si="71"/>
-        <v>8122.4954807204522</v>
+        <f t="shared" si="77"/>
+        <v>7886.1221983189853</v>
       </c>
       <c r="BA13" s="8">
-        <f t="shared" si="71"/>
-        <v>8203.7992710375638</v>
+        <f t="shared" si="77"/>
+        <v>7965.0827818071921</v>
       </c>
       <c r="BB13" s="3">
         <f>BA13*(1+$BD$19)</f>
-        <v>8121.7612783271879</v>
+        <v>7885.4319539891203</v>
       </c>
       <c r="BC13" s="3">
-        <f t="shared" ref="BC13:DN13" si="72">BB13*(1+$BD$19)</f>
-        <v>8040.5436655439162</v>
+        <f t="shared" ref="BC13:DN13" si="78">BB13*(1+$BD$19)</f>
+        <v>7806.5776344492288</v>
       </c>
       <c r="BD13" s="3">
-        <f t="shared" si="72"/>
-        <v>7960.138228888477</v>
+        <f t="shared" si="78"/>
+        <v>7728.5118581047363</v>
       </c>
       <c r="BE13" s="3">
-        <f t="shared" si="72"/>
-        <v>7880.5368465995925</v>
+        <f t="shared" si="78"/>
+        <v>7651.2267395236886</v>
       </c>
       <c r="BF13" s="3">
-        <f t="shared" si="72"/>
-        <v>7801.7314781335963</v>
+        <f t="shared" si="78"/>
+        <v>7574.7144721284512</v>
       </c>
       <c r="BG13" s="3">
-        <f t="shared" si="72"/>
-        <v>7723.7141633522606</v>
+        <f t="shared" si="78"/>
+        <v>7498.9673274071665</v>
       </c>
       <c r="BH13" s="3">
-        <f t="shared" si="72"/>
-        <v>7646.4770217187379</v>
+        <f t="shared" si="78"/>
+        <v>7423.9776541330948</v>
       </c>
       <c r="BI13" s="3">
-        <f t="shared" si="72"/>
-        <v>7570.0122515015501</v>
+        <f t="shared" si="78"/>
+        <v>7349.7378775917641</v>
       </c>
       <c r="BJ13" s="3">
-        <f t="shared" si="72"/>
-        <v>7494.3121289865348</v>
+        <f t="shared" si="78"/>
+        <v>7276.240498815846</v>
       </c>
       <c r="BK13" s="3">
-        <f t="shared" si="72"/>
-        <v>7419.3690076966695</v>
+        <f t="shared" si="78"/>
+        <v>7203.4780938276872</v>
       </c>
       <c r="BL13" s="3">
-        <f t="shared" si="72"/>
-        <v>7345.1753176197026</v>
+        <f t="shared" si="78"/>
+        <v>7131.4433128894107</v>
       </c>
       <c r="BM13" s="3">
-        <f t="shared" si="72"/>
-        <v>7271.7235644435059</v>
+        <f t="shared" si="78"/>
+        <v>7060.1288797605166</v>
       </c>
       <c r="BN13" s="3">
-        <f t="shared" si="72"/>
-        <v>7199.0063287990706</v>
+        <f t="shared" si="78"/>
+        <v>6989.5275909629117</v>
       </c>
       <c r="BO13" s="3">
-        <f t="shared" si="72"/>
-        <v>7127.0162655110798</v>
+        <f t="shared" si="78"/>
+        <v>6919.6323150532826</v>
       </c>
       <c r="BP13" s="3">
-        <f t="shared" si="72"/>
-        <v>7055.7461028559692</v>
+        <f t="shared" si="78"/>
+        <v>6850.4359919027493</v>
       </c>
       <c r="BQ13" s="3">
-        <f t="shared" si="72"/>
-        <v>6985.1886418274098</v>
+        <f t="shared" si="78"/>
+        <v>6781.9316319837217</v>
       </c>
       <c r="BR13" s="3">
-        <f t="shared" si="72"/>
-        <v>6915.3367554091355</v>
+        <f t="shared" si="78"/>
+        <v>6714.1123156638841</v>
       </c>
       <c r="BS13" s="3">
-        <f t="shared" si="72"/>
-        <v>6846.1833878550442</v>
+        <f t="shared" si="78"/>
+        <v>6646.9711925072452</v>
       </c>
       <c r="BT13" s="3">
-        <f t="shared" si="72"/>
-        <v>6777.7215539764939</v>
+        <f t="shared" si="78"/>
+        <v>6580.5014805821729</v>
       </c>
       <c r="BU13" s="3">
-        <f t="shared" si="72"/>
-        <v>6709.9443384367287</v>
+        <f t="shared" si="78"/>
+        <v>6514.696465776351</v>
       </c>
       <c r="BV13" s="3">
-        <f t="shared" si="72"/>
-        <v>6642.8448950523616</v>
+        <f t="shared" si="78"/>
+        <v>6449.5495011185876</v>
       </c>
       <c r="BW13" s="3">
-        <f t="shared" si="72"/>
-        <v>6576.4164461018381</v>
+        <f t="shared" si="78"/>
+        <v>6385.0540061074016</v>
       </c>
       <c r="BX13" s="3">
-        <f t="shared" si="72"/>
-        <v>6510.6522816408196</v>
+        <f t="shared" si="78"/>
+        <v>6321.2034660463278</v>
       </c>
       <c r="BY13" s="3">
-        <f t="shared" si="72"/>
-        <v>6445.5457588244117</v>
+        <f t="shared" si="78"/>
+        <v>6257.9914313858644</v>
       </c>
       <c r="BZ13" s="3">
-        <f t="shared" si="72"/>
-        <v>6381.0903012361678</v>
+        <f t="shared" si="78"/>
+        <v>6195.4115170720061</v>
       </c>
       <c r="CA13" s="3">
-        <f t="shared" si="72"/>
-        <v>6317.2793982238063</v>
+        <f t="shared" si="78"/>
+        <v>6133.4574019012862</v>
       </c>
       <c r="CB13" s="3">
-        <f t="shared" si="72"/>
-        <v>6254.1066042415678</v>
+        <f t="shared" si="78"/>
+        <v>6072.1228278822737</v>
       </c>
       <c r="CC13" s="3">
-        <f t="shared" si="72"/>
-        <v>6191.5655381991519</v>
+        <f t="shared" si="78"/>
+        <v>6011.4015996034504</v>
       </c>
       <c r="CD13" s="3">
-        <f t="shared" si="72"/>
-        <v>6129.6498828171607</v>
+        <f t="shared" si="78"/>
+        <v>5951.2875836074163</v>
       </c>
       <c r="CE13" s="3">
-        <f t="shared" si="72"/>
-        <v>6068.3533839889888</v>
+        <f t="shared" si="78"/>
+        <v>5891.774707771342</v>
       </c>
       <c r="CF13" s="3">
-        <f t="shared" si="72"/>
-        <v>6007.6698501490991</v>
+        <f t="shared" si="78"/>
+        <v>5832.8569606936289</v>
       </c>
       <c r="CG13" s="3">
-        <f t="shared" si="72"/>
-        <v>5947.5931516476085</v>
+        <f t="shared" si="78"/>
+        <v>5774.5283910866929</v>
       </c>
       <c r="CH13" s="3">
-        <f t="shared" si="72"/>
-        <v>5888.1172201311319</v>
+        <f t="shared" si="78"/>
+        <v>5716.7831071758255</v>
       </c>
       <c r="CI13" s="3">
-        <f t="shared" si="72"/>
-        <v>5829.2360479298204</v>
+        <f t="shared" si="78"/>
+        <v>5659.6152761040676</v>
       </c>
       <c r="CJ13" s="3">
-        <f t="shared" si="72"/>
-        <v>5770.9436874505218</v>
+        <f t="shared" si="78"/>
+        <v>5603.0191233430269</v>
       </c>
       <c r="CK13" s="3">
-        <f t="shared" si="72"/>
-        <v>5713.2342505760162</v>
+        <f t="shared" si="78"/>
+        <v>5546.9889321095961</v>
       </c>
       <c r="CL13" s="3">
-        <f t="shared" si="72"/>
-        <v>5656.1019080702563</v>
+        <f t="shared" si="78"/>
+        <v>5491.5190427885</v>
       </c>
       <c r="CM13" s="3">
-        <f t="shared" si="72"/>
-        <v>5599.5408889895534</v>
+        <f t="shared" si="78"/>
+        <v>5436.6038523606148</v>
       </c>
       <c r="CN13" s="3">
-        <f t="shared" si="72"/>
-        <v>5543.5454800996577</v>
+        <f t="shared" si="78"/>
+        <v>5382.2378138370086</v>
       </c>
       <c r="CO13" s="3">
-        <f t="shared" si="72"/>
-        <v>5488.1100252986607</v>
+        <f t="shared" si="78"/>
+        <v>5328.4154356986382</v>
       </c>
       <c r="CP13" s="3">
-        <f t="shared" si="72"/>
-        <v>5433.2289250456743</v>
+        <f t="shared" si="78"/>
+        <v>5275.1312813416516</v>
       </c>
       <c r="CQ13" s="3">
-        <f t="shared" si="72"/>
-        <v>5378.8966357952177</v>
+        <f t="shared" si="78"/>
+        <v>5222.3799685282347</v>
       </c>
       <c r="CR13" s="3">
-        <f t="shared" si="72"/>
-        <v>5325.107669437265</v>
+        <f t="shared" si="78"/>
+        <v>5170.156168842952</v>
       </c>
       <c r="CS13" s="3">
-        <f t="shared" si="72"/>
-        <v>5271.8565927428926</v>
+        <f t="shared" si="78"/>
+        <v>5118.4546071545228</v>
       </c>
       <c r="CT13" s="3">
-        <f t="shared" si="72"/>
-        <v>5219.1380268154635</v>
+        <f t="shared" si="78"/>
+        <v>5067.2700610829779</v>
       </c>
       <c r="CU13" s="3">
-        <f t="shared" si="72"/>
-        <v>5166.9466465473088</v>
+        <f t="shared" si="78"/>
+        <v>5016.5973604721485</v>
       </c>
       <c r="CV13" s="3">
-        <f t="shared" si="72"/>
-        <v>5115.2771800818355</v>
+        <f t="shared" si="78"/>
+        <v>4966.4313868674271</v>
       </c>
       <c r="CW13" s="3">
-        <f t="shared" si="72"/>
-        <v>5064.1244082810172</v>
+        <f t="shared" si="78"/>
+        <v>4916.7670729987531</v>
       </c>
       <c r="CX13" s="3">
-        <f t="shared" si="72"/>
-        <v>5013.4831641982073</v>
+        <f t="shared" si="78"/>
+        <v>4867.5994022687655</v>
       </c>
       <c r="CY13" s="3">
-        <f t="shared" si="72"/>
-        <v>4963.3483325562256</v>
+        <f t="shared" si="78"/>
+        <v>4818.923408246078</v>
       </c>
       <c r="CZ13" s="3">
-        <f t="shared" si="72"/>
-        <v>4913.7148492306633</v>
+        <f t="shared" si="78"/>
+        <v>4770.7341741636174</v>
       </c>
       <c r="DA13" s="3">
-        <f t="shared" si="72"/>
-        <v>4864.5777007383567</v>
+        <f t="shared" si="78"/>
+        <v>4723.0268324219815</v>
       </c>
       <c r="DB13" s="3">
-        <f t="shared" si="72"/>
-        <v>4815.9319237309728</v>
+        <f t="shared" si="78"/>
+        <v>4675.7965640977618</v>
       </c>
       <c r="DC13" s="3">
-        <f t="shared" si="72"/>
-        <v>4767.7726044936635</v>
+        <f t="shared" si="78"/>
+        <v>4629.0385984567838</v>
       </c>
       <c r="DD13" s="3">
-        <f t="shared" si="72"/>
-        <v>4720.0948784487264</v>
+        <f t="shared" si="78"/>
+        <v>4582.7482124722155</v>
       </c>
       <c r="DE13" s="3">
-        <f t="shared" si="72"/>
-        <v>4672.8939296642393</v>
+        <f t="shared" si="78"/>
+        <v>4536.9207303474932</v>
       </c>
       <c r="DF13" s="3">
-        <f t="shared" si="72"/>
-        <v>4626.1649903675971</v>
+        <f t="shared" si="78"/>
+        <v>4491.5515230440178</v>
       </c>
       <c r="DG13" s="3">
-        <f t="shared" si="72"/>
-        <v>4579.9033404639213</v>
+        <f t="shared" si="78"/>
+        <v>4446.6360078135776</v>
       </c>
       <c r="DH13" s="3">
-        <f t="shared" si="72"/>
-        <v>4534.1043070592823</v>
+        <f t="shared" si="78"/>
+        <v>4402.1696477354417</v>
       </c>
       <c r="DI13" s="3">
-        <f t="shared" si="72"/>
-        <v>4488.7632639886897</v>
+        <f t="shared" si="78"/>
+        <v>4358.1479512580872</v>
       </c>
       <c r="DJ13" s="3">
-        <f t="shared" si="72"/>
-        <v>4443.8756313488029</v>
+        <f t="shared" si="78"/>
+        <v>4314.5664717455065</v>
       </c>
       <c r="DK13" s="3">
-        <f t="shared" si="72"/>
-        <v>4399.4368750353151</v>
+        <f t="shared" si="78"/>
+        <v>4271.4208070280511</v>
       </c>
       <c r="DL13" s="3">
-        <f t="shared" si="72"/>
-        <v>4355.4425062849623</v>
+        <f t="shared" si="78"/>
+        <v>4228.7065989577704</v>
       </c>
       <c r="DM13" s="3">
-        <f t="shared" si="72"/>
-        <v>4311.8880812221123</v>
+        <f t="shared" si="78"/>
+        <v>4186.4195329681925</v>
       </c>
       <c r="DN13" s="3">
-        <f t="shared" si="72"/>
-        <v>4268.7692004098908</v>
+        <f t="shared" si="78"/>
+        <v>4144.5553376385105</v>
       </c>
       <c r="DO13" s="3">
-        <f t="shared" ref="DO13:EI13" si="73">DN13*(1+$BD$19)</f>
-        <v>4226.0815084057922</v>
+        <f t="shared" ref="DO13:EI13" si="79">DN13*(1+$BD$19)</f>
+        <v>4103.1097842621257</v>
       </c>
       <c r="DP13" s="3">
-        <f t="shared" si="73"/>
-        <v>4183.8206933217343</v>
+        <f t="shared" si="79"/>
+        <v>4062.0786864195043</v>
       </c>
       <c r="DQ13" s="3">
-        <f t="shared" si="73"/>
-        <v>4141.9824863885169</v>
+        <f t="shared" si="79"/>
+        <v>4021.4578995553093</v>
       </c>
       <c r="DR13" s="3">
-        <f t="shared" si="73"/>
-        <v>4100.5626615246319</v>
+        <f t="shared" si="79"/>
+        <v>3981.2433205597563</v>
       </c>
       <c r="DS13" s="3">
-        <f t="shared" si="73"/>
-        <v>4059.5570349093855</v>
+        <f t="shared" si="79"/>
+        <v>3941.4308873541586</v>
       </c>
       <c r="DT13" s="3">
-        <f t="shared" si="73"/>
-        <v>4018.9614645602915</v>
+        <f t="shared" si="79"/>
+        <v>3902.0165784806168</v>
       </c>
       <c r="DU13" s="3">
-        <f t="shared" si="73"/>
-        <v>3978.7718499146886</v>
+        <f t="shared" si="79"/>
+        <v>3862.9964126958107</v>
       </c>
       <c r="DV13" s="3">
-        <f t="shared" si="73"/>
-        <v>3938.9841314155415</v>
+        <f t="shared" si="79"/>
+        <v>3824.3664485688528</v>
       </c>
       <c r="DW13" s="3">
-        <f t="shared" si="73"/>
-        <v>3899.5942901013859</v>
+        <f t="shared" si="79"/>
+        <v>3786.1227840831643</v>
       </c>
       <c r="DX13" s="3">
-        <f t="shared" si="73"/>
-        <v>3860.5983472003722</v>
+        <f t="shared" si="79"/>
+        <v>3748.2615562423325</v>
       </c>
       <c r="DY13" s="3">
-        <f t="shared" si="73"/>
-        <v>3821.9923637283687</v>
+        <f t="shared" si="79"/>
+        <v>3710.7789406799093</v>
       </c>
       <c r="DZ13" s="3">
-        <f t="shared" si="73"/>
-        <v>3783.7724400910852</v>
+        <f t="shared" si="79"/>
+        <v>3673.6711512731104</v>
       </c>
       <c r="EA13" s="3">
-        <f t="shared" si="73"/>
-        <v>3745.9347156901745</v>
+        <f t="shared" si="79"/>
+        <v>3636.9344397603791</v>
       </c>
       <c r="EB13" s="3">
-        <f t="shared" si="73"/>
-        <v>3708.4753685332726</v>
+        <f t="shared" si="79"/>
+        <v>3600.5650953627751</v>
       </c>
       <c r="EC13" s="3">
-        <f t="shared" si="73"/>
-        <v>3671.39061484794</v>
+        <f t="shared" si="79"/>
+        <v>3564.5594444091471</v>
       </c>
       <c r="ED13" s="3">
-        <f t="shared" si="73"/>
-        <v>3634.6767086994605</v>
+        <f t="shared" si="79"/>
+        <v>3528.9138499650558</v>
       </c>
       <c r="EE13" s="3">
-        <f t="shared" si="73"/>
-        <v>3598.329941612466</v>
+        <f t="shared" si="79"/>
+        <v>3493.6247114654052</v>
       </c>
       <c r="EF13" s="3">
-        <f t="shared" si="73"/>
-        <v>3562.3466421963412</v>
+        <f t="shared" si="79"/>
+        <v>3458.688464350751</v>
       </c>
       <c r="EG13" s="3">
-        <f t="shared" si="73"/>
-        <v>3526.723175774378</v>
+        <f t="shared" si="79"/>
+        <v>3424.1015797072437</v>
       </c>
       <c r="EH13" s="3">
-        <f t="shared" si="73"/>
-        <v>3491.455944016634</v>
+        <f t="shared" si="79"/>
+        <v>3389.8605639101711</v>
       </c>
       <c r="EI13" s="3">
-        <f t="shared" si="73"/>
-        <v>3456.5413845764679</v>
+        <f t="shared" si="79"/>
+        <v>3355.9619582710693</v>
       </c>
     </row>
     <row r="14" spans="2:139" x14ac:dyDescent="0.3">
@@ -3372,105 +3487,114 @@
         <v>3974</v>
       </c>
       <c r="G14" s="6">
-        <f t="shared" ref="G14:N14" si="74">3907.5+70.85</f>
+        <f t="shared" ref="G14:N14" si="80">3907.5+70.85</f>
         <v>3978.35</v>
       </c>
       <c r="H14" s="6">
-        <f t="shared" si="74"/>
+        <f t="shared" si="80"/>
         <v>3978.35</v>
       </c>
       <c r="I14" s="6">
-        <f t="shared" si="74"/>
+        <f t="shared" si="80"/>
         <v>3978.35</v>
       </c>
       <c r="J14" s="6">
-        <f t="shared" si="74"/>
+        <f t="shared" si="80"/>
         <v>3978.35</v>
       </c>
       <c r="K14" s="6">
-        <f t="shared" si="74"/>
+        <f t="shared" si="80"/>
         <v>3978.35</v>
       </c>
       <c r="L14" s="6">
-        <f t="shared" si="74"/>
+        <f t="shared" si="80"/>
         <v>3978.35</v>
       </c>
       <c r="M14" s="6">
-        <f t="shared" si="74"/>
+        <f t="shared" si="80"/>
         <v>3978.35</v>
       </c>
       <c r="N14" s="6">
-        <f t="shared" si="74"/>
+        <f t="shared" si="80"/>
         <v>3978.35</v>
       </c>
       <c r="O14" s="6">
-        <f t="shared" ref="O14:AD14" si="75">3903.4+70.9</f>
+        <f t="shared" ref="O14:AC14" si="81">3903.4+70.9</f>
         <v>3974.3</v>
       </c>
       <c r="P14" s="6">
-        <f t="shared" si="75"/>
+        <f t="shared" si="81"/>
         <v>3974.3</v>
       </c>
       <c r="Q14" s="6">
-        <f t="shared" si="75"/>
+        <f t="shared" si="81"/>
         <v>3974.3</v>
       </c>
       <c r="R14" s="6">
-        <f t="shared" si="75"/>
+        <f t="shared" si="81"/>
         <v>3974.3</v>
       </c>
       <c r="S14" s="6">
-        <f t="shared" si="75"/>
+        <f t="shared" si="81"/>
         <v>3974.3</v>
       </c>
       <c r="T14" s="6">
-        <f t="shared" si="75"/>
+        <f t="shared" si="81"/>
         <v>3974.3</v>
       </c>
       <c r="U14" s="6">
-        <f t="shared" si="75"/>
+        <f t="shared" si="81"/>
         <v>3974.3</v>
       </c>
       <c r="V14" s="6">
-        <f t="shared" si="75"/>
+        <f t="shared" si="81"/>
         <v>3974.3</v>
       </c>
       <c r="W14" s="6">
-        <f t="shared" si="75"/>
+        <f t="shared" si="81"/>
         <v>3974.3</v>
       </c>
       <c r="X14" s="6">
-        <f t="shared" si="75"/>
+        <f t="shared" si="81"/>
         <v>3974.3</v>
       </c>
       <c r="Y14" s="6">
-        <f t="shared" si="75"/>
+        <f t="shared" si="81"/>
         <v>3974.3</v>
       </c>
       <c r="Z14" s="6">
-        <f t="shared" si="75"/>
+        <f t="shared" si="81"/>
         <v>3974.3</v>
       </c>
       <c r="AA14" s="6">
-        <f t="shared" si="75"/>
+        <f t="shared" si="81"/>
         <v>3974.3</v>
       </c>
       <c r="AB14" s="6">
-        <f t="shared" si="75"/>
+        <f t="shared" si="81"/>
         <v>3974.3</v>
       </c>
       <c r="AC14" s="6">
-        <f t="shared" si="75"/>
+        <f t="shared" si="81"/>
         <v>3974.3</v>
       </c>
       <c r="AD14" s="6">
         <f>3892.6+70.9</f>
         <v>3963.5</v>
       </c>
-      <c r="AE14" s="6"/>
-      <c r="AF14" s="6"/>
-      <c r="AG14" s="6"/>
-      <c r="AH14" s="6"/>
+      <c r="AE14" s="6">
+        <f>3905.7+70.9</f>
+        <v>3976.6</v>
+      </c>
+      <c r="AF14" s="6">
+        <v>3980</v>
+      </c>
+      <c r="AG14" s="6">
+        <v>3980</v>
+      </c>
+      <c r="AH14" s="6">
+        <v>3980</v>
+      </c>
       <c r="AJ14" s="6">
         <v>3974</v>
       </c>
@@ -3483,64 +3607,53 @@
         <v>3978.35</v>
       </c>
       <c r="AM14" s="6">
-        <f t="shared" ref="AM14:AO14" si="76">3907.5+70.85</f>
+        <f t="shared" ref="AM14:AO14" si="82">3907.5+70.85</f>
         <v>3978.35</v>
       </c>
       <c r="AN14" s="6">
-        <f t="shared" si="76"/>
+        <f t="shared" si="82"/>
         <v>3978.35</v>
       </c>
       <c r="AO14" s="6">
-        <f t="shared" si="76"/>
+        <f t="shared" si="82"/>
         <v>3978.35</v>
       </c>
       <c r="AP14" s="6">
-        <f>3892.6+70.9</f>
+        <f t="shared" ref="AP14" si="83">3892.6+70.9</f>
         <v>3963.5</v>
       </c>
       <c r="AQ14" s="6">
-        <f>3892.6+70.9</f>
-        <v>3963.5</v>
+        <v>3980</v>
       </c>
       <c r="AR14" s="6">
-        <f>3892.6+70.9</f>
-        <v>3963.5</v>
+        <v>3980</v>
       </c>
       <c r="AS14" s="6">
-        <f>3892.6+70.9</f>
-        <v>3963.5</v>
+        <v>3980</v>
       </c>
       <c r="AT14" s="6">
-        <f>3892.6+70.9</f>
-        <v>3963.5</v>
+        <v>3980</v>
       </c>
       <c r="AU14" s="6">
-        <f>3892.6+70.9</f>
-        <v>3963.5</v>
+        <v>3980</v>
       </c>
       <c r="AV14" s="6">
-        <f>3892.6+70.9</f>
-        <v>3963.5</v>
+        <v>3980</v>
       </c>
       <c r="AW14" s="6">
-        <f>3892.6+70.9</f>
-        <v>3963.5</v>
+        <v>3980</v>
       </c>
       <c r="AX14" s="6">
-        <f>3892.6+70.9</f>
-        <v>3963.5</v>
+        <v>3980</v>
       </c>
       <c r="AY14" s="6">
-        <f>3892.6+70.9</f>
-        <v>3963.5</v>
+        <v>3980</v>
       </c>
       <c r="AZ14" s="6">
-        <f>3892.6+70.9</f>
-        <v>3963.5</v>
+        <v>3980</v>
       </c>
       <c r="BA14" s="6">
-        <f>3892.6+70.9</f>
-        <v>3963.5</v>
+        <v>3980</v>
       </c>
     </row>
     <row r="15" spans="2:139" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -3548,121 +3661,133 @@
         <v>33</v>
       </c>
       <c r="C15" s="9">
-        <f t="shared" ref="C15:O15" si="77">C13/C14</f>
+        <f t="shared" ref="C15:O15" si="84">C13/C14</f>
         <v>0.43683945646703576</v>
       </c>
       <c r="D15" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0.26824358329139408</v>
       </c>
       <c r="E15" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0.2493709109209864</v>
       </c>
       <c r="F15" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>-2.9189733266230498E-2</v>
       </c>
       <c r="G15" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0.28805911998692924</v>
       </c>
       <c r="H15" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>3.7201352319428907E-2</v>
       </c>
       <c r="I15" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0.10682820767403572</v>
       </c>
       <c r="J15" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>-0.42027473701408874</v>
       </c>
       <c r="K15" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>-0.50096145386906632</v>
       </c>
       <c r="L15" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0.28076966581623036</v>
       </c>
       <c r="M15" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0.59949476541782398</v>
       </c>
       <c r="N15" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>-6.8420325009111771E-2</v>
       </c>
       <c r="O15" s="9">
-        <f t="shared" si="77"/>
+        <f t="shared" si="84"/>
         <v>0.82077346954180608</v>
       </c>
       <c r="P15" s="9">
-        <f t="shared" ref="P15" si="78">P13/P14</f>
+        <f t="shared" ref="P15" si="85">P13/P14</f>
         <v>0.14115693329642956</v>
       </c>
       <c r="Q15" s="9">
-        <f t="shared" ref="Q15:R15" si="79">Q13/Q14</f>
+        <f t="shared" ref="Q15:R15" si="86">Q13/Q14</f>
         <v>0.46096167878620131</v>
       </c>
       <c r="R15" s="9">
-        <f t="shared" si="79"/>
+        <f t="shared" si="86"/>
         <v>3.0903555343079283</v>
       </c>
       <c r="S15" s="9">
-        <f t="shared" ref="S15" si="80">S13/S14</f>
+        <f t="shared" ref="S15" si="87">S13/S14</f>
         <v>-0.78252774073421727</v>
       </c>
       <c r="T15" s="9">
-        <f t="shared" ref="T15" si="81">T13/T14</f>
+        <f t="shared" ref="T15" si="88">T13/T14</f>
         <v>0.16782829680698488</v>
       </c>
       <c r="U15" s="9">
-        <f t="shared" ref="U15:W15" si="82">U13/U14</f>
+        <f t="shared" ref="U15:W15" si="89">U13/U14</f>
         <v>-0.20808695870970986</v>
       </c>
       <c r="V15" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>0.32433384495382833</v>
       </c>
       <c r="W15" s="9">
-        <f t="shared" si="82"/>
+        <f t="shared" si="89"/>
         <v>0.44209043101929896</v>
       </c>
       <c r="X15" s="9">
-        <f t="shared" ref="X15" si="83">X13/X14</f>
+        <f t="shared" ref="X15" si="90">X13/X14</f>
         <v>0.48234909292202399</v>
       </c>
       <c r="Y15" s="9">
-        <f t="shared" ref="Y15:Z15" si="84">Y13/Y14</f>
+        <f t="shared" ref="Y15:Z15" si="91">Y13/Y14</f>
         <v>0.30168834763354552</v>
       </c>
       <c r="Z15" s="9">
-        <f t="shared" si="84"/>
+        <f t="shared" si="91"/>
         <v>-0.13235035100520845</v>
       </c>
       <c r="AA15" s="9">
-        <f t="shared" ref="AA15" si="85">AA13/AA14</f>
+        <f t="shared" ref="AA15" si="92">AA13/AA14</f>
         <v>0.33515336034018567</v>
       </c>
       <c r="AB15" s="9">
-        <f t="shared" ref="AB15" si="86">AB13/AB14</f>
+        <f t="shared" ref="AB15" si="93">AB13/AB14</f>
         <v>0.46071006214930932</v>
       </c>
       <c r="AC15" s="9">
-        <f t="shared" ref="AC15:AD15" si="87">AC13/AC14</f>
+        <f t="shared" ref="AC15:AD15" si="94">AC13/AC14</f>
         <v>0.22444204010769192</v>
       </c>
       <c r="AD15" s="9">
-        <f t="shared" si="87"/>
-        <v>0.29807745679323838</v>
-      </c>
-      <c r="AE15" s="9"/>
-      <c r="AF15" s="9"/>
-      <c r="AG15" s="9"/>
-      <c r="AH15" s="9"/>
+        <f t="shared" si="94"/>
+        <v>0.46019931878390313</v>
+      </c>
+      <c r="AE15" s="9">
+        <f t="shared" ref="AE15:AH15" si="95">AE13/AE14</f>
+        <v>0.11844289091183423</v>
+      </c>
+      <c r="AF15" s="9">
+        <f t="shared" si="95"/>
+        <v>-9.0452261306532659E-3</v>
+      </c>
+      <c r="AG15" s="9">
+        <f t="shared" si="95"/>
+        <v>0.12361125628140701</v>
+      </c>
+      <c r="AH15" s="9">
+        <f t="shared" si="95"/>
+        <v>7.8509748743718646E-2</v>
+      </c>
       <c r="AJ15" s="9">
         <f>AJ13/AJ14</f>
         <v>0.92526421741318565</v>
@@ -3676,64 +3801,64 @@
         <v>-0.32149006497668631</v>
       </c>
       <c r="AM15" s="9">
-        <f t="shared" ref="AM15:AV15" si="88">AM13/AM14</f>
+        <f t="shared" ref="AM15:AV15" si="96">AM13/AM14</f>
         <v>4.5086530848215967</v>
       </c>
       <c r="AN15" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="96"/>
         <v>-0.49794512800532886</v>
       </c>
       <c r="AO15" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="96"/>
         <v>1.0926640441389017</v>
       </c>
       <c r="AP15" s="9">
-        <f t="shared" si="88"/>
+        <f t="shared" si="96"/>
         <v>1.4832849754005297</v>
       </c>
       <c r="AQ15" s="9">
-        <f t="shared" si="88"/>
-        <v>1.7008583484294186</v>
+        <f t="shared" si="96"/>
+        <v>0.31141748743718034</v>
       </c>
       <c r="AR15" s="9">
-        <f t="shared" si="88"/>
-        <v>1.892367498493756</v>
+        <f t="shared" si="96"/>
+        <v>1.0706405591708545</v>
       </c>
       <c r="AS15" s="9">
-        <f t="shared" si="88"/>
-        <v>1.9113102858478124</v>
+        <f t="shared" si="96"/>
+        <v>1.6690523454924637</v>
       </c>
       <c r="AT15" s="9">
-        <f t="shared" si="88"/>
-        <v>1.930442596637254</v>
+        <f t="shared" si="96"/>
+        <v>1.8054402792353774</v>
       </c>
       <c r="AU15" s="9">
-        <f t="shared" si="88"/>
-        <v>1.9497663265742458</v>
+        <f t="shared" si="96"/>
+        <v>1.8851506615581446</v>
       </c>
       <c r="AV15" s="9">
-        <f t="shared" si="88"/>
-        <v>1.969283390330459</v>
+        <f t="shared" si="96"/>
+        <v>1.904026518499746</v>
       </c>
       <c r="AW15" s="9">
-        <f t="shared" ref="AW15:BA15" si="89">AW13/AW14</f>
-        <v>1.9889957217266878</v>
+        <f t="shared" ref="AW15:BA15" si="97">AW13/AW14</f>
+        <v>1.9230912557623927</v>
       </c>
       <c r="AX15" s="9">
-        <f t="shared" si="89"/>
-        <v>2.008905273924344</v>
+        <f t="shared" si="97"/>
+        <v>1.9423467627580551</v>
       </c>
       <c r="AY15" s="9">
-        <f t="shared" si="89"/>
-        <v>2.0290140196188786</v>
+        <f t="shared" si="97"/>
+        <v>1.9617949477958634</v>
       </c>
       <c r="AZ15" s="9">
-        <f t="shared" si="89"/>
-        <v>2.0493239512351336</v>
+        <f t="shared" si="97"/>
+        <v>1.9814377382711019</v>
       </c>
       <c r="BA15" s="9">
-        <f t="shared" si="89"/>
-        <v>2.0698370811246534</v>
+        <f t="shared" si="97"/>
+        <v>2.0012770808560782</v>
       </c>
     </row>
     <row r="17" spans="2:56" x14ac:dyDescent="0.3">
@@ -3745,187 +3870,199 @@
         <v>0.14790628947305703</v>
       </c>
       <c r="D17" s="10">
-        <f t="shared" ref="D17:L17" si="90">D5/D3</f>
+        <f t="shared" ref="D17:L17" si="98">D5/D3</f>
         <v>0.14712230215827338</v>
       </c>
       <c r="E17" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="98"/>
         <v>0.16189667073753516</v>
       </c>
       <c r="F17" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="98"/>
         <v>0.14449788242050104</v>
       </c>
       <c r="G17" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="98"/>
         <v>0.1586435972435675</v>
       </c>
       <c r="H17" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="98"/>
         <v>0.13373484672998223</v>
       </c>
       <c r="I17" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="98"/>
         <v>0.12727764260610977</v>
       </c>
       <c r="J17" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="98"/>
         <v>0.12345461412564522</v>
       </c>
       <c r="K17" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="98"/>
         <v>0.11066433566433566</v>
       </c>
       <c r="L17" s="10">
-        <f t="shared" si="90"/>
+        <f t="shared" si="98"/>
         <v>7.4286304269268494E-2</v>
       </c>
       <c r="M17" s="10">
-        <f t="shared" ref="M17:N17" si="91">M5/M3</f>
+        <f t="shared" ref="M17:N17" si="99">M5/M3</f>
         <v>0.16740886909682409</v>
       </c>
       <c r="N17" s="10">
-        <f t="shared" si="91"/>
+        <f t="shared" si="99"/>
         <v>0.15</v>
       </c>
       <c r="O17" s="10">
-        <f t="shared" ref="O17:AD17" si="92">O5/O3</f>
+        <f t="shared" ref="O17:AD17" si="100">O5/O3</f>
         <v>0.19131610908689411</v>
       </c>
       <c r="P17" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>0.1438397129186603</v>
       </c>
       <c r="Q17" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>0.15766611551719306</v>
       </c>
       <c r="R17" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>0.1402675301236796</v>
       </c>
       <c r="S17" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>0.15779092702169625</v>
       </c>
       <c r="T17" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>0.17414779795969146</v>
       </c>
       <c r="U17" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>0.12789398862713242</v>
       </c>
       <c r="V17" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>0.14052592104366007</v>
       </c>
       <c r="W17" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>0.16407869990837634</v>
       </c>
       <c r="X17" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>0.16645904702584866</v>
       </c>
       <c r="Y17" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>0.14275929773292848</v>
       </c>
       <c r="Z17" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>0.11096122884121666</v>
       </c>
       <c r="AA17" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>0.14729878205577765</v>
       </c>
       <c r="AB17" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>0.15309153279785809</v>
       </c>
       <c r="AC17" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
         <v>0.13048748809420729</v>
       </c>
       <c r="AD17" s="10">
-        <f t="shared" si="92"/>
+        <f t="shared" si="100"/>
+        <v>0.14332828607579184</v>
+      </c>
+      <c r="AE17" s="10">
+        <f t="shared" ref="AE17:AH17" si="101">AE5/AE3</f>
+        <v>0.13455815440615854</v>
+      </c>
+      <c r="AF17" s="10">
+        <f t="shared" si="101"/>
+        <v>0.11834449226845209</v>
+      </c>
+      <c r="AG17" s="10">
+        <f t="shared" si="101"/>
+        <v>0.12</v>
+      </c>
+      <c r="AH17" s="10">
+        <f t="shared" si="101"/>
+        <v>0.12</v>
+      </c>
+      <c r="AJ17" s="10">
+        <f t="shared" ref="AJ17:AV17" si="102">AJ5/AJ3</f>
+        <v>0.15011413389215283</v>
+      </c>
+      <c r="AK17" s="10">
+        <f t="shared" si="102"/>
+        <v>0.13602950609364978</v>
+      </c>
+      <c r="AL17" s="10">
+        <f t="shared" si="102"/>
+        <v>0.11319448813943246</v>
+      </c>
+      <c r="AM17" s="10">
+        <f t="shared" si="102"/>
+        <v>0.15908640834378507</v>
+      </c>
+      <c r="AN17" s="10">
+        <f t="shared" si="102"/>
+        <v>0.1496928323326395</v>
+      </c>
+      <c r="AO17" s="10">
+        <f t="shared" si="102"/>
+        <v>0.14552956734452951</v>
+      </c>
+      <c r="AP17" s="10">
+        <f t="shared" si="102"/>
+        <v>0.143562964884968</v>
+      </c>
+      <c r="AQ17" s="10">
+        <f t="shared" si="102"/>
+        <v>0.12267852325376029</v>
+      </c>
+      <c r="AR17" s="10">
+        <f t="shared" si="102"/>
         <v>0.13</v>
       </c>
-      <c r="AE17" s="10"/>
-      <c r="AF17" s="10"/>
-      <c r="AG17" s="10"/>
-      <c r="AH17" s="10"/>
-      <c r="AJ17" s="10">
-        <f t="shared" ref="AJ17:AV17" si="93">AJ5/AJ3</f>
-        <v>0.15011413389215283</v>
-      </c>
-      <c r="AK17" s="10">
-        <f t="shared" si="93"/>
-        <v>0.13602950609364978</v>
-      </c>
-      <c r="AL17" s="10">
-        <f t="shared" si="93"/>
-        <v>0.11319448813943246</v>
-      </c>
-      <c r="AM17" s="10">
-        <f t="shared" si="93"/>
-        <v>0.15908640834378507</v>
-      </c>
-      <c r="AN17" s="10">
-        <f t="shared" si="93"/>
-        <v>0.1496928323326395</v>
-      </c>
-      <c r="AO17" s="10">
-        <f t="shared" si="93"/>
-        <v>0.14552956734452951</v>
-      </c>
-      <c r="AP17" s="10">
-        <f t="shared" si="93"/>
-        <v>0.143562964884968</v>
-      </c>
-      <c r="AQ17" s="10">
-        <f t="shared" si="93"/>
+      <c r="AS17" s="10">
+        <f t="shared" si="102"/>
         <v>0.14000000000000001</v>
       </c>
-      <c r="AR17" s="10">
-        <f t="shared" si="93"/>
+      <c r="AT17" s="10">
+        <f t="shared" si="102"/>
         <v>0.14000000000000001</v>
       </c>
-      <c r="AS17" s="10">
-        <f t="shared" si="93"/>
+      <c r="AU17" s="10">
+        <f t="shared" si="102"/>
         <v>0.14000000000000001</v>
       </c>
-      <c r="AT17" s="10">
-        <f t="shared" si="93"/>
+      <c r="AV17" s="10">
+        <f t="shared" si="102"/>
         <v>0.14000000000000001</v>
       </c>
-      <c r="AU17" s="10">
-        <f t="shared" si="93"/>
+      <c r="AW17" s="10">
+        <f t="shared" ref="AW17:BA17" si="103">AW5/AW3</f>
         <v>0.14000000000000001</v>
       </c>
-      <c r="AV17" s="10">
-        <f t="shared" si="93"/>
+      <c r="AX17" s="10">
+        <f t="shared" si="103"/>
         <v>0.14000000000000001</v>
       </c>
-      <c r="AW17" s="10">
-        <f t="shared" ref="AW17:BA17" si="94">AW5/AW3</f>
+      <c r="AY17" s="10">
+        <f t="shared" si="103"/>
         <v>0.14000000000000001</v>
       </c>
-      <c r="AX17" s="10">
-        <f t="shared" si="94"/>
+      <c r="AZ17" s="10">
+        <f t="shared" si="103"/>
         <v>0.14000000000000001</v>
       </c>
-      <c r="AY17" s="10">
-        <f t="shared" si="94"/>
-        <v>0.14000000000000001</v>
-      </c>
-      <c r="AZ17" s="10">
-        <f t="shared" si="94"/>
-        <v>0.14000000000000001</v>
-      </c>
       <c r="BA17" s="10">
-        <f t="shared" si="94"/>
+        <f t="shared" si="103"/>
         <v>0.14000000000000001</v>
       </c>
     </row>
@@ -3938,188 +4075,200 @@
         <v>2.6716556638623417E-2</v>
       </c>
       <c r="D18" s="10">
-        <f t="shared" ref="D18:L18" si="95">D8/D3</f>
+        <f t="shared" ref="D18:L18" si="104">D8/D3</f>
         <v>1.5056526207605345E-2</v>
       </c>
       <c r="E18" s="10">
-        <f t="shared" si="95"/>
+        <f t="shared" si="104"/>
         <v>2.2938459087771465E-2</v>
       </c>
       <c r="F18" s="10">
-        <f t="shared" si="95"/>
+        <f t="shared" si="104"/>
         <v>1.5122149642284593E-2</v>
       </c>
       <c r="G18" s="10">
-        <f t="shared" si="95"/>
+        <f t="shared" si="104"/>
         <v>2.9795250607307519E-2</v>
       </c>
       <c r="H18" s="10">
-        <f t="shared" si="95"/>
+        <f t="shared" si="104"/>
         <v>2.3164234422052353E-3</v>
       </c>
       <c r="I18" s="10">
-        <f t="shared" si="95"/>
+        <f t="shared" si="104"/>
         <v>-7.0559610705596106E-3</v>
       </c>
       <c r="J18" s="10">
-        <f t="shared" si="95"/>
+        <f t="shared" si="104"/>
         <v>-1.150698728440136E-2</v>
       </c>
       <c r="K18" s="10">
-        <f t="shared" si="95"/>
+        <f t="shared" si="104"/>
         <v>-4.5396270396270394E-2</v>
       </c>
       <c r="L18" s="10">
-        <f t="shared" si="95"/>
+        <f t="shared" si="104"/>
         <v>-0.14242940478034175</v>
       </c>
       <c r="M18" s="10">
-        <f t="shared" ref="M18:N18" si="96">M8/M3</f>
+        <f t="shared" ref="M18:N18" si="105">M8/M3</f>
         <v>6.2691661555691849E-2</v>
       </c>
       <c r="N18" s="10">
-        <f t="shared" si="96"/>
+        <f t="shared" si="105"/>
         <v>2.0527369826435298E-3</v>
       </c>
       <c r="O18" s="10">
-        <f t="shared" ref="O18:AD18" si="97">O8/O3</f>
+        <f t="shared" ref="O18:AD18" si="106">O8/O3</f>
         <v>6.8013691067682458E-2</v>
       </c>
       <c r="P18" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="106"/>
         <v>-8.2236842105263153E-4</v>
       </c>
       <c r="Q18" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="106"/>
         <v>3.7608945436202114E-2</v>
       </c>
       <c r="R18" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="106"/>
         <v>1.9613567599129467E-2</v>
       </c>
       <c r="S18" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="106"/>
         <v>3.895463510848126E-2</v>
       </c>
       <c r="T18" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="106"/>
         <v>7.1361035083354063E-2</v>
       </c>
       <c r="U18" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="106"/>
         <v>1.2794476035743298E-2</v>
       </c>
       <c r="V18" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="106"/>
         <v>3.5478079047251074E-2</v>
       </c>
       <c r="W18" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="106"/>
         <v>5.0947581617398853E-2</v>
       </c>
       <c r="X18" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="106"/>
         <v>5.4744850291408999E-2</v>
       </c>
       <c r="Y18" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="106"/>
         <v>2.5775667222209538E-2</v>
       </c>
       <c r="Z18" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="106"/>
         <v>-5.3304904051172707E-3</v>
       </c>
       <c r="AA18" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="106"/>
         <v>2.8636884306987399E-2</v>
       </c>
       <c r="AB18" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="106"/>
         <v>3.9386713520749662E-2</v>
       </c>
       <c r="AC18" s="10">
-        <f t="shared" si="97"/>
+        <f t="shared" si="106"/>
         <v>1.9049268334920773E-2</v>
       </c>
       <c r="AD18" s="10">
-        <f t="shared" si="97"/>
-        <v>1.2205305843064868E-2</v>
-      </c>
-      <c r="AE18" s="10"/>
-      <c r="AF18" s="10"/>
-      <c r="AG18" s="10"/>
-      <c r="AH18" s="10"/>
+        <f t="shared" si="106"/>
+        <v>2.5533591918856693E-2</v>
+      </c>
+      <c r="AE18" s="10">
+        <f t="shared" ref="AE18:AH18" si="107">AE8/AE3</f>
+        <v>7.8457414102658697E-3</v>
+      </c>
+      <c r="AF18" s="10">
+        <f t="shared" si="107"/>
+        <v>1.0182528295871194E-2</v>
+      </c>
+      <c r="AG18" s="10">
+        <f t="shared" si="107"/>
+        <v>1.2807045755352965E-2</v>
+      </c>
+      <c r="AH18" s="10">
+        <f t="shared" si="107"/>
+        <v>7.8392700342048045E-3</v>
+      </c>
       <c r="AJ18" s="10">
-        <f t="shared" ref="AJ18:AV18" si="98">AJ8/AJ3</f>
+        <f t="shared" ref="AJ18:AV18" si="108">AJ8/AJ3</f>
         <v>1.9976549539098654E-2</v>
       </c>
       <c r="AK18" s="10">
-        <f t="shared" si="98"/>
+        <f t="shared" si="108"/>
         <v>3.6818473380372035E-3</v>
       </c>
       <c r="AL18" s="10">
-        <f t="shared" si="98"/>
+        <f t="shared" si="108"/>
         <v>-3.4669351286730009E-2</v>
       </c>
       <c r="AM18" s="10">
-        <f t="shared" si="98"/>
+        <f t="shared" si="108"/>
         <v>3.317417357948086E-2</v>
       </c>
       <c r="AN18" s="10">
-        <f t="shared" si="98"/>
+        <f t="shared" si="108"/>
         <v>3.9707194240052639E-2</v>
       </c>
       <c r="AO18" s="10">
-        <f t="shared" si="98"/>
+        <f t="shared" si="108"/>
         <v>3.0977745741836985E-2</v>
       </c>
       <c r="AP18" s="10">
-        <f t="shared" si="98"/>
+        <f t="shared" si="108"/>
         <v>2.8212030790520672E-2</v>
       </c>
       <c r="AQ18" s="10">
-        <f t="shared" si="98"/>
-        <v>3.2254020548081921E-2</v>
+        <f t="shared" si="108"/>
+        <v>9.7281075704707502E-3</v>
       </c>
       <c r="AR18" s="10">
-        <f t="shared" si="98"/>
-        <v>3.6235425137132023E-2</v>
+        <f t="shared" si="108"/>
+        <v>2.4487481862301153E-2</v>
       </c>
       <c r="AS18" s="10">
-        <f t="shared" si="98"/>
-        <v>3.6235425137132043E-2</v>
+        <f t="shared" si="108"/>
+        <v>3.7531112193196332E-2</v>
       </c>
       <c r="AT18" s="10">
-        <f t="shared" si="98"/>
-        <v>3.623542513713203E-2</v>
+        <f t="shared" si="108"/>
+        <v>3.952079933507599E-2</v>
       </c>
       <c r="AU18" s="10">
-        <f t="shared" si="98"/>
-        <v>3.6235425137132043E-2</v>
+        <f t="shared" si="108"/>
+        <v>4.0505889537673305E-2</v>
       </c>
       <c r="AV18" s="10">
-        <f t="shared" si="98"/>
-        <v>3.623542513713203E-2</v>
+        <f t="shared" si="108"/>
+        <v>4.0505889537673298E-2</v>
       </c>
       <c r="AW18" s="10">
-        <f t="shared" ref="AW18:BA18" si="99">AW8/AW3</f>
-        <v>3.623542513713203E-2</v>
+        <f t="shared" ref="AW18:BA18" si="109">AW8/AW3</f>
+        <v>4.0505889537673284E-2</v>
       </c>
       <c r="AX18" s="10">
-        <f t="shared" si="99"/>
-        <v>3.6235425137132043E-2</v>
+        <f t="shared" si="109"/>
+        <v>4.0505889537673291E-2</v>
       </c>
       <c r="AY18" s="10">
-        <f t="shared" si="99"/>
-        <v>3.623542513713205E-2</v>
+        <f t="shared" si="109"/>
+        <v>4.0505889537673277E-2</v>
       </c>
       <c r="AZ18" s="10">
-        <f t="shared" si="99"/>
-        <v>3.623542513713203E-2</v>
+        <f t="shared" si="109"/>
+        <v>4.0505889537673284E-2</v>
       </c>
       <c r="BA18" s="10">
-        <f t="shared" si="99"/>
-        <v>3.6235425137132043E-2</v>
+        <f t="shared" si="109"/>
+        <v>4.050588953767327E-2</v>
       </c>
     </row>
     <row r="19" spans="2:56" x14ac:dyDescent="0.3">
@@ -4131,167 +4280,179 @@
         <v>3.4947215143793287E-2</v>
       </c>
       <c r="H19" s="11">
-        <f t="shared" ref="H19:N19" si="100">H6/D6-1</f>
+        <f t="shared" ref="H19:N19" si="110">H6/D6-1</f>
         <v>-1.9078473722102252E-2</v>
       </c>
       <c r="I19" s="11">
-        <f t="shared" si="100"/>
+        <f t="shared" si="110"/>
         <v>-9.7501734906315085E-2</v>
       </c>
       <c r="J19" s="11">
-        <f t="shared" si="100"/>
+        <f t="shared" si="110"/>
         <v>-1.3351134846462109E-3</v>
       </c>
       <c r="K19" s="11">
-        <f t="shared" si="100"/>
+        <f t="shared" si="110"/>
         <v>-0.14456559971860705</v>
       </c>
       <c r="L19" s="11">
-        <f t="shared" si="100"/>
+        <f t="shared" si="110"/>
         <v>-0.27889908256880735</v>
       </c>
       <c r="M19" s="11">
-        <f t="shared" si="100"/>
+        <f t="shared" si="110"/>
         <v>-0.12879661668589004</v>
       </c>
       <c r="N19" s="11">
-        <f t="shared" si="100"/>
+        <f t="shared" si="110"/>
         <v>0.17981283422459904</v>
       </c>
       <c r="O19" s="11">
-        <f t="shared" ref="O19:O20" si="101">O6/K6-1</f>
+        <f t="shared" ref="O19:O20" si="111">O6/K6-1</f>
         <v>0.16899671052631571</v>
       </c>
       <c r="P19" s="11">
-        <f t="shared" ref="P19:P20" si="102">P6/L6-1</f>
+        <f t="shared" ref="P19:P20" si="112">P6/L6-1</f>
         <v>0.46412213740458008</v>
       </c>
       <c r="Q19" s="11">
-        <f t="shared" ref="Q19:Q20" si="103">Q6/M6-1</f>
+        <f t="shared" ref="Q19:Q20" si="113">Q6/M6-1</f>
         <v>0.30052956751985871</v>
       </c>
       <c r="R19" s="11">
-        <f t="shared" ref="R19:R20" si="104">R6/N6-1</f>
+        <f t="shared" ref="R19:R20" si="114">R6/N6-1</f>
         <v>-7.9886685552407966E-2</v>
       </c>
       <c r="S19" s="11">
-        <f t="shared" ref="S19:S20" si="105">S6/O6-1</f>
+        <f t="shared" ref="S19:S20" si="115">S6/O6-1</f>
         <v>-3.6229335209285951E-2</v>
       </c>
       <c r="T19" s="11">
-        <f t="shared" ref="T19:T20" si="106">T6/P6-1</f>
+        <f t="shared" ref="T19:T20" si="116">T6/P6-1</f>
         <v>-4.1014946124435125E-2</v>
       </c>
       <c r="U19" s="11">
-        <f t="shared" ref="U19:U20" si="107">U6/Q6-1</f>
+        <f t="shared" ref="U19:U20" si="117">U6/Q6-1</f>
         <v>-3.3932813030200237E-2</v>
       </c>
       <c r="V19" s="11">
-        <f t="shared" ref="V19:V20" si="108">V6/R6-1</f>
+        <f t="shared" ref="V19:V20" si="118">V6/R6-1</f>
         <v>-0.2173645320197044</v>
       </c>
       <c r="W19" s="11">
-        <f t="shared" ref="W19:W20" si="109">W6/S6-1</f>
+        <f t="shared" ref="W19:W20" si="119">W6/S6-1</f>
         <v>-8.5401459854014594E-2</v>
       </c>
       <c r="X19" s="11">
-        <f t="shared" ref="X19:X20" si="110">X6/T6-1</f>
+        <f t="shared" ref="X19:X20" si="120">X6/T6-1</f>
         <v>-3.2620514679231327E-3</v>
       </c>
       <c r="Y19" s="11">
-        <f t="shared" ref="Y19:Y20" si="111">Y6/U6-1</f>
+        <f t="shared" ref="Y19:Y20" si="121">Y6/U6-1</f>
         <v>-6.1819459079733075E-2</v>
       </c>
       <c r="Z19" s="11">
-        <f t="shared" ref="Z19:Z20" si="112">Z6/V6-1</f>
+        <f t="shared" ref="Z19:Z20" si="122">Z6/V6-1</f>
         <v>9.1660110149488494E-2</v>
       </c>
       <c r="AA19" s="11">
-        <f t="shared" ref="AA19:AA20" si="113">AA6/W6-1</f>
+        <f t="shared" ref="AA19:AA20" si="123">AA6/W6-1</f>
         <v>-5.1875498802873121E-2</v>
       </c>
       <c r="AB19" s="11">
-        <f t="shared" ref="AB19:AB20" si="114">AB6/X6-1</f>
+        <f t="shared" ref="AB19:AB20" si="124">AB6/X6-1</f>
         <v>-2.6181818181818195E-2</v>
       </c>
       <c r="AC19" s="11">
-        <f t="shared" ref="AC19:AC20" si="115">AC6/Y6-1</f>
+        <f t="shared" ref="AC19:AC20" si="125">AC6/Y6-1</f>
         <v>-8.0494196929988715E-2</v>
       </c>
       <c r="AD19" s="11">
-        <f t="shared" ref="AD19:AD20" si="116">AD6/Z6-1</f>
+        <f t="shared" ref="AD19:AD20" si="126">AD6/Z6-1</f>
         <v>7.2072072072071336E-4</v>
       </c>
-      <c r="AE19" s="11"/>
-      <c r="AF19" s="11"/>
-      <c r="AG19" s="11"/>
-      <c r="AH19" s="11"/>
+      <c r="AE19" s="11">
+        <f t="shared" ref="AE19:AE20" si="127">AE6/AA6-1</f>
+        <v>2.314814814814814E-2</v>
+      </c>
+      <c r="AF19" s="11">
+        <f t="shared" ref="AF19:AF20" si="128">AF6/AB6-1</f>
+        <v>1.0455563853622118E-2</v>
+      </c>
+      <c r="AG19" s="11">
+        <f t="shared" ref="AG19:AG20" si="129">AG6/AC6-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AH19" s="11">
+        <f t="shared" ref="AH19:AH20" si="130">AH6/AD6-1</f>
+        <v>1.0000000000000009E-2</v>
+      </c>
       <c r="AK19" s="11">
         <f>AK6/AJ6-1</f>
         <v>-2.122248531088311E-2</v>
       </c>
       <c r="AL19" s="11">
-        <f t="shared" ref="AL19:AV19" si="117">AL6/AK6-1</f>
+        <f t="shared" ref="AL19:AV19" si="131">AL6/AK6-1</f>
         <v>-8.6730579697159804E-2</v>
       </c>
       <c r="AM19" s="11">
-        <f t="shared" si="117"/>
+        <f t="shared" si="131"/>
         <v>0.16893946826253314</v>
       </c>
       <c r="AN19" s="11">
-        <f t="shared" si="117"/>
+        <f t="shared" si="131"/>
         <v>-8.6193873268988641E-2</v>
       </c>
       <c r="AO19" s="11">
-        <f t="shared" si="117"/>
+        <f t="shared" si="131"/>
         <v>-1.7083027185892719E-2</v>
       </c>
       <c r="AP19" s="11">
-        <f t="shared" si="117"/>
+        <f t="shared" si="131"/>
         <v>-3.8777798542328545E-2</v>
       </c>
       <c r="AQ19" s="11">
-        <f t="shared" si="117"/>
-        <v>-7.0000000000000062E-2</v>
+        <f t="shared" si="131"/>
+        <v>1.3155438903470484E-2</v>
       </c>
       <c r="AR19" s="11">
-        <f t="shared" si="117"/>
-        <v>-5.0000000000000155E-2</v>
+        <f t="shared" si="131"/>
+        <v>-5.0000000000000044E-2</v>
       </c>
       <c r="AS19" s="11">
-        <f t="shared" si="117"/>
+        <f t="shared" si="131"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AT19" s="11">
-        <f t="shared" si="117"/>
+        <f t="shared" si="131"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AU19" s="11">
-        <f t="shared" si="117"/>
+        <f t="shared" si="131"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AV19" s="11">
-        <f t="shared" si="117"/>
+        <f t="shared" si="131"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AW19" s="11">
-        <f t="shared" ref="AW19:AW20" si="118">AW6/AV6-1</f>
+        <f t="shared" ref="AW19:AW20" si="132">AW6/AV6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AX19" s="11">
-        <f t="shared" ref="AX19:AX20" si="119">AX6/AW6-1</f>
+        <f t="shared" ref="AX19:AX20" si="133">AX6/AW6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AY19" s="11">
-        <f t="shared" ref="AY19:AY20" si="120">AY6/AX6-1</f>
+        <f t="shared" ref="AY19:AY20" si="134">AY6/AX6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AZ19" s="11">
-        <f t="shared" ref="AZ19:AZ20" si="121">AZ6/AY6-1</f>
+        <f t="shared" ref="AZ19:AZ20" si="135">AZ6/AY6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BA19" s="11">
-        <f t="shared" ref="BA19:BA20" si="122">BA6/AZ6-1</f>
+        <f t="shared" ref="BA19:BA20" si="136">BA6/AZ6-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BC19" s="1" t="s">
@@ -4306,178 +4467,190 @@
         <v>65</v>
       </c>
       <c r="G20" s="11">
-        <f t="shared" ref="G20:N20" si="123">G7/C7-1</f>
+        <f t="shared" ref="G20:N20" si="137">G7/C7-1</f>
         <v>7.2711719418305787E-3</v>
       </c>
       <c r="H20" s="11">
+        <f t="shared" si="137"/>
+        <v>8.0440304826419062E-3</v>
+      </c>
+      <c r="I20" s="11">
+        <f t="shared" si="137"/>
+        <v>6.8027210884353817E-3</v>
+      </c>
+      <c r="J20" s="11">
+        <f t="shared" si="137"/>
+        <v>-1.7834923268353342E-2</v>
+      </c>
+      <c r="K20" s="11">
+        <f t="shared" si="137"/>
+        <v>0.24161358811040334</v>
+      </c>
+      <c r="L20" s="11">
+        <f t="shared" si="137"/>
+        <v>-6.2158756824863493E-2</v>
+      </c>
+      <c r="M20" s="11">
+        <f t="shared" si="137"/>
+        <v>-0.29856418918918914</v>
+      </c>
+      <c r="N20" s="11">
+        <f t="shared" si="137"/>
+        <v>-0.24451013513513509</v>
+      </c>
+      <c r="O20" s="11">
+        <f t="shared" si="111"/>
+        <v>-0.44459644322845415</v>
+      </c>
+      <c r="P20" s="11">
+        <f t="shared" si="112"/>
+        <v>-0.55530676220331388</v>
+      </c>
+      <c r="Q20" s="11">
+        <f t="shared" si="113"/>
+        <v>-0.19506321493076462</v>
+      </c>
+      <c r="R20" s="11">
+        <f t="shared" si="114"/>
+        <v>-0.27445500279485746</v>
+      </c>
+      <c r="S20" s="11">
+        <f t="shared" si="115"/>
+        <v>-0.16440886699507384</v>
+      </c>
+      <c r="T20" s="11">
+        <f t="shared" si="116"/>
+        <v>0.38167170191339372</v>
+      </c>
+      <c r="U20" s="11">
+        <f t="shared" si="117"/>
+        <v>0.26178010471204183</v>
+      </c>
+      <c r="V20" s="11">
+        <f t="shared" si="118"/>
+        <v>0.60246533127889057</v>
+      </c>
+      <c r="W20" s="11">
+        <f t="shared" si="119"/>
+        <v>0.61090641120117906</v>
+      </c>
+      <c r="X20" s="11">
+        <f t="shared" si="120"/>
+        <v>0.65597667638483959</v>
+      </c>
+      <c r="Y20" s="11">
+        <f t="shared" si="121"/>
+        <v>0.45406046235921749</v>
+      </c>
+      <c r="Z20" s="11">
+        <f t="shared" si="122"/>
+        <v>0.23557692307692313</v>
+      </c>
+      <c r="AA20" s="11">
         <f t="shared" si="123"/>
-        <v>8.0440304826419062E-3</v>
-      </c>
-      <c r="I20" s="11">
-        <f t="shared" si="123"/>
-        <v>6.8027210884353817E-3</v>
-      </c>
-      <c r="J20" s="11">
-        <f t="shared" si="123"/>
-        <v>-1.7834923268353342E-2</v>
-      </c>
-      <c r="K20" s="11">
-        <f t="shared" si="123"/>
-        <v>0.24161358811040334</v>
-      </c>
-      <c r="L20" s="11">
-        <f t="shared" si="123"/>
-        <v>-6.2158756824863493E-2</v>
-      </c>
-      <c r="M20" s="11">
-        <f t="shared" si="123"/>
-        <v>-0.29856418918918914</v>
-      </c>
-      <c r="N20" s="11">
-        <f t="shared" si="123"/>
-        <v>-0.24451013513513509</v>
-      </c>
-      <c r="O20" s="11">
-        <f t="shared" si="101"/>
-        <v>-0.44459644322845415</v>
-      </c>
-      <c r="P20" s="11">
-        <f t="shared" si="102"/>
-        <v>-0.55530676220331388</v>
-      </c>
-      <c r="Q20" s="11">
-        <f t="shared" si="103"/>
-        <v>-0.19506321493076462</v>
-      </c>
-      <c r="R20" s="11">
-        <f t="shared" si="104"/>
-        <v>-0.27445500279485746</v>
-      </c>
-      <c r="S20" s="11">
-        <f t="shared" si="105"/>
-        <v>-0.16440886699507384</v>
-      </c>
-      <c r="T20" s="11">
-        <f t="shared" si="106"/>
-        <v>0.38167170191339372</v>
-      </c>
-      <c r="U20" s="11">
-        <f t="shared" si="107"/>
-        <v>0.26178010471204183</v>
-      </c>
-      <c r="V20" s="11">
-        <f t="shared" si="108"/>
-        <v>0.60246533127889057</v>
-      </c>
-      <c r="W20" s="11">
-        <f t="shared" si="109"/>
-        <v>0.61090641120117906</v>
-      </c>
-      <c r="X20" s="11">
-        <f t="shared" si="110"/>
-        <v>0.65597667638483959</v>
-      </c>
-      <c r="Y20" s="11">
-        <f t="shared" si="111"/>
-        <v>0.45406046235921749</v>
-      </c>
-      <c r="Z20" s="11">
-        <f t="shared" si="112"/>
-        <v>0.23557692307692313</v>
-      </c>
-      <c r="AA20" s="11">
-        <f t="shared" si="113"/>
         <v>0.2351326623970722</v>
       </c>
       <c r="AB20" s="11">
-        <f t="shared" si="114"/>
+        <f t="shared" si="124"/>
         <v>0.21390845070422526</v>
       </c>
       <c r="AC20" s="11">
-        <f t="shared" si="115"/>
+        <f t="shared" si="125"/>
         <v>9.7431716265796942E-2</v>
       </c>
       <c r="AD20" s="11">
-        <f t="shared" si="116"/>
+        <f t="shared" si="126"/>
         <v>0.12918287937743189</v>
       </c>
-      <c r="AE20" s="11"/>
-      <c r="AF20" s="11"/>
-      <c r="AG20" s="11"/>
-      <c r="AH20" s="11"/>
+      <c r="AE20" s="11">
+        <f t="shared" si="127"/>
+        <v>7.7777777777778834E-3</v>
+      </c>
+      <c r="AF20" s="11">
+        <f t="shared" si="128"/>
+        <v>-1.3052936910804891E-2</v>
+      </c>
+      <c r="AG20" s="11">
+        <f t="shared" si="129"/>
+        <v>1.0000000000000009E-2</v>
+      </c>
+      <c r="AH20" s="11">
+        <f t="shared" si="130"/>
+        <v>-1.0000000000000009E-2</v>
+      </c>
       <c r="AK20" s="11">
-        <f t="shared" ref="AK20:AV20" si="124">AK7/AJ7-1</f>
+        <f t="shared" ref="AK20:AV20" si="138">AK7/AJ7-1</f>
         <v>9.5107259854176895E-4</v>
       </c>
       <c r="AL20" s="11">
-        <f t="shared" si="124"/>
+        <f t="shared" si="138"/>
         <v>-9.1321790540540571E-2</v>
       </c>
       <c r="AM20" s="11">
-        <f t="shared" si="124"/>
+        <f t="shared" si="138"/>
         <v>-0.38979900081329155</v>
       </c>
       <c r="AN20" s="11">
-        <f t="shared" si="124"/>
+        <f t="shared" si="138"/>
         <v>0.23686214775323688</v>
       </c>
       <c r="AO20" s="11">
-        <f t="shared" si="124"/>
+        <f t="shared" si="138"/>
         <v>0.45951354679802958</v>
       </c>
       <c r="AP20" s="11">
-        <f t="shared" si="124"/>
+        <f t="shared" si="138"/>
         <v>0.16569982069401967</v>
       </c>
       <c r="AQ20" s="11">
-        <f t="shared" si="124"/>
+        <f t="shared" si="138"/>
+        <v>-1.5472312703583846E-3</v>
+      </c>
+      <c r="AR20" s="11">
+        <f t="shared" si="138"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AR20" s="11">
-        <f t="shared" si="124"/>
+      <c r="AS20" s="11">
+        <f t="shared" si="138"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AS20" s="11">
-        <f t="shared" si="124"/>
+      <c r="AT20" s="11">
+        <f t="shared" si="138"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AT20" s="11">
-        <f t="shared" si="124"/>
+      <c r="AU20" s="11">
+        <f t="shared" si="138"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AU20" s="11">
-        <f t="shared" si="124"/>
+      <c r="AV20" s="11">
+        <f t="shared" si="138"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AV20" s="11">
-        <f t="shared" si="124"/>
+      <c r="AW20" s="11">
+        <f t="shared" si="132"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AW20" s="11">
-        <f t="shared" si="118"/>
+      <c r="AX20" s="11">
+        <f t="shared" si="133"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AX20" s="11">
-        <f t="shared" si="119"/>
+      <c r="AY20" s="11">
+        <f t="shared" si="134"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AY20" s="11">
-        <f t="shared" si="120"/>
+      <c r="AZ20" s="11">
+        <f t="shared" si="135"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AZ20" s="11">
-        <f t="shared" si="121"/>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="BA20" s="11">
-        <f t="shared" si="122"/>
+        <f t="shared" si="136"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BC20" s="1" t="s">
         <v>38</v>
       </c>
       <c r="BD20" s="11">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="21" spans="2:56" x14ac:dyDescent="0.3">
@@ -4489,23 +4662,23 @@
         <v>-3.8537620057675359E-2</v>
       </c>
       <c r="H21" s="10">
-        <f t="shared" ref="H21:L21" si="125">H3/D3-1</f>
+        <f t="shared" ref="H21:L21" si="139">H3/D3-1</f>
         <v>-1.7214799588900487E-3</v>
       </c>
       <c r="I21" s="10">
-        <f t="shared" si="125"/>
+        <f t="shared" si="139"/>
         <v>-1.7947220304784128E-2</v>
       </c>
       <c r="J21" s="10">
-        <f t="shared" si="125"/>
+        <f t="shared" si="139"/>
         <v>-4.9721245184600305E-2</v>
       </c>
       <c r="K21" s="10">
-        <f t="shared" si="125"/>
+        <f t="shared" si="139"/>
         <v>-0.14927370978136933</v>
       </c>
       <c r="L21" s="10">
-        <f t="shared" si="125"/>
+        <f t="shared" si="139"/>
         <v>-0.50142846112269324</v>
       </c>
       <c r="M21" s="10">
@@ -4517,147 +4690,159 @@
         <v>-9.4750094422762166E-2</v>
       </c>
       <c r="O21" s="10">
-        <f t="shared" ref="O21:AD21" si="126">O3/K3-1</f>
+        <f t="shared" ref="O21:AD21" si="140">O3/K3-1</f>
         <v>5.5594405594405538E-2</v>
       </c>
       <c r="P21" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="140"/>
         <v>0.38103350369108457</v>
       </c>
       <c r="Q21" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="140"/>
         <v>-4.8478707234473783E-2</v>
       </c>
       <c r="R21" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="140"/>
         <v>4.8008455718736132E-2</v>
       </c>
       <c r="S21" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="140"/>
         <v>-4.8360384233189779E-2</v>
       </c>
       <c r="T21" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="140"/>
         <v>0.50231758373205748</v>
       </c>
       <c r="U21" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="140"/>
         <v>0.10394305411540516</v>
       </c>
       <c r="V21" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="140"/>
         <v>0.16776368172408307</v>
       </c>
       <c r="W21" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="140"/>
         <v>0.20298178442974812</v>
       </c>
       <c r="X21" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="140"/>
         <v>0.11853694948992288</v>
       </c>
       <c r="Y21" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="140"/>
         <v>0.11192627944760347</v>
       </c>
       <c r="Z21" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="140"/>
         <v>4.461465033296208E-2</v>
       </c>
       <c r="AA21" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="140"/>
         <v>3.1417273472537088E-2</v>
       </c>
       <c r="AB21" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="140"/>
         <v>6.3487120167282196E-2</v>
       </c>
       <c r="AC21" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="140"/>
         <v>5.4679116915138826E-2</v>
       </c>
       <c r="AD21" s="10">
-        <f t="shared" si="126"/>
+        <f t="shared" si="140"/>
         <v>4.8931726208607085E-2</v>
       </c>
-      <c r="AE21" s="10"/>
-      <c r="AF21" s="10"/>
-      <c r="AG21" s="10"/>
-      <c r="AH21" s="10"/>
+      <c r="AE21" s="10">
+        <f t="shared" ref="AE21" si="141">AE3/AA3-1</f>
+        <v>-4.9512588540570834E-2</v>
+      </c>
+      <c r="AF21" s="10">
+        <f t="shared" ref="AF21" si="142">AF3/AB3-1</f>
+        <v>4.9698795180722843E-2</v>
+      </c>
+      <c r="AG21" s="10">
+        <f t="shared" ref="AG21" si="143">AG3/AC3-1</f>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AH21" s="10">
+        <f t="shared" ref="AH21" si="144">AH3/AD3-1</f>
+        <v>5.0000000000000044E-2</v>
+      </c>
       <c r="AK21" s="10">
         <f>AK3/AJ3-1</f>
         <v>-2.767902805323752E-2</v>
       </c>
       <c r="AL21" s="10">
-        <f t="shared" ref="AL21:AV21" si="127">AL3/AK3-1</f>
+        <f t="shared" ref="AL21:AV21" si="145">AL3/AK3-1</f>
         <v>-0.1844515715202053</v>
       </c>
       <c r="AM21" s="10">
-        <f t="shared" si="127"/>
+        <f t="shared" si="145"/>
         <v>7.2335304851192328E-2</v>
       </c>
       <c r="AN21" s="10">
-        <f t="shared" si="127"/>
+        <f t="shared" si="145"/>
         <v>0.15927710666637318</v>
       </c>
       <c r="AO21" s="10">
-        <f t="shared" si="127"/>
+        <f t="shared" si="145"/>
         <v>0.1147307616872395</v>
       </c>
       <c r="AP21" s="10">
-        <f t="shared" si="127"/>
+        <f t="shared" si="145"/>
         <v>4.9951473117242129E-2</v>
       </c>
       <c r="AQ21" s="10">
-        <f t="shared" si="127"/>
+        <f t="shared" si="145"/>
+        <v>2.6911163725998888E-2</v>
+      </c>
+      <c r="AR21" s="10">
+        <f t="shared" si="145"/>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="AS21" s="10">
+        <f t="shared" si="145"/>
         <v>4.0000000000000036E-2</v>
       </c>
-      <c r="AR21" s="10">
-        <f t="shared" si="127"/>
+      <c r="AT21" s="10">
+        <f t="shared" si="145"/>
+        <v>3.0000000000000027E-2</v>
+      </c>
+      <c r="AU21" s="10">
+        <f t="shared" si="145"/>
         <v>2.0000000000000018E-2</v>
       </c>
-      <c r="AS21" s="10">
-        <f t="shared" si="127"/>
+      <c r="AV21" s="10">
+        <f t="shared" si="145"/>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AT21" s="10">
-        <f t="shared" si="127"/>
+      <c r="AW21" s="10">
+        <f t="shared" ref="AW21" si="146">AW3/AV3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AU21" s="10">
-        <f t="shared" si="127"/>
+      <c r="AX21" s="10">
+        <f t="shared" ref="AX21" si="147">AX3/AW3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AV21" s="10">
-        <f t="shared" si="127"/>
+      <c r="AY21" s="10">
+        <f t="shared" ref="AY21" si="148">AY3/AX3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AW21" s="10">
-        <f t="shared" ref="AW21" si="128">AW3/AV3-1</f>
+      <c r="AZ21" s="10">
+        <f t="shared" ref="AZ21" si="149">AZ3/AY3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
-      <c r="AX21" s="10">
-        <f t="shared" ref="AX21" si="129">AX3/AW3-1</f>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AY21" s="10">
-        <f t="shared" ref="AY21" si="130">AY3/AX3-1</f>
-        <v>1.0000000000000009E-2</v>
-      </c>
-      <c r="AZ21" s="10">
-        <f t="shared" ref="AZ21" si="131">AZ3/AY3-1</f>
-        <v>1.0000000000000009E-2</v>
-      </c>
       <c r="BA21" s="10">
-        <f t="shared" ref="BA21" si="132">BA3/AZ3-1</f>
+        <f t="shared" ref="BA21" si="150">BA3/AZ3-1</f>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="BC21" s="1" t="s">
         <v>39</v>
       </c>
       <c r="BD21" s="6">
-        <f>NPV(BD20,AL13:EI13)</f>
-        <v>111750.6888698807</v>
+        <f>NPV(BD20,AQ13:EI13)</f>
+        <v>129785.60162908456</v>
       </c>
     </row>
     <row r="22" spans="2:56" x14ac:dyDescent="0.3">
@@ -4665,191 +4850,203 @@
         <v>30</v>
       </c>
       <c r="C22" s="11">
-        <f t="shared" ref="C22:N22" si="133">C11/C10</f>
+        <f t="shared" ref="C22:N22" si="151">C11/C10</f>
         <v>9.0672225117248567E-2</v>
       </c>
       <c r="D22" s="11">
-        <f t="shared" si="133"/>
+        <f t="shared" si="151"/>
         <v>0.20756115641215717</v>
       </c>
       <c r="E22" s="11">
-        <f t="shared" si="133"/>
+        <f t="shared" si="151"/>
         <v>9.2321755027422306E-2</v>
       </c>
       <c r="F22" s="11">
-        <f t="shared" si="133"/>
+        <f t="shared" si="151"/>
         <v>-5.5882352941176467</v>
       </c>
       <c r="G22" s="11">
-        <f t="shared" si="133"/>
+        <f t="shared" si="151"/>
         <v>0.26521739130434785</v>
       </c>
       <c r="H22" s="11">
-        <f t="shared" si="133"/>
+        <f t="shared" si="151"/>
         <v>0.26829268292682928</v>
       </c>
       <c r="I22" s="11">
-        <f t="shared" si="133"/>
+        <f t="shared" si="151"/>
         <v>23.263157894736842</v>
       </c>
       <c r="J22" s="11">
-        <f t="shared" si="133"/>
+        <f t="shared" si="151"/>
         <v>0.31362889983579639</v>
       </c>
       <c r="K22" s="11">
-        <f t="shared" si="133"/>
+        <f t="shared" si="151"/>
         <v>-0.7390924956369983</v>
       </c>
       <c r="L22" s="11">
-        <f t="shared" si="133"/>
+        <f t="shared" si="151"/>
         <v>-3.136531365313653E-2</v>
       </c>
       <c r="M22" s="11">
-        <f t="shared" si="133"/>
+        <f t="shared" si="151"/>
         <v>0.1328011611030479</v>
       </c>
       <c r="N22" s="11">
-        <f t="shared" si="133"/>
+        <f t="shared" si="151"/>
         <v>0.78735898624632994</v>
       </c>
       <c r="O22" s="11">
-        <f t="shared" ref="O22:AD22" si="134">O11/O10</f>
+        <f t="shared" ref="O22:AD22" si="152">O11/O10</f>
         <v>0.17250126839167934</v>
       </c>
       <c r="P22" s="11">
-        <f t="shared" si="134"/>
+        <f t="shared" si="152"/>
         <v>0.24761904761904763</v>
       </c>
       <c r="Q22" s="11">
-        <f t="shared" si="134"/>
+        <f t="shared" si="152"/>
         <v>3.3421750663129975E-2</v>
       </c>
       <c r="R22" s="11">
-        <f t="shared" si="134"/>
+        <f t="shared" si="152"/>
         <v>-9.4045284364414339E-2</v>
       </c>
       <c r="S22" s="11">
-        <f t="shared" si="134"/>
+        <f t="shared" si="152"/>
         <v>0.18944906444906445</v>
       </c>
       <c r="T22" s="11">
-        <f t="shared" si="134"/>
+        <f t="shared" si="152"/>
         <v>0.19342604298356511</v>
       </c>
       <c r="U22" s="11">
-        <f t="shared" si="134"/>
+        <f t="shared" si="152"/>
         <v>0.17333333333333334</v>
       </c>
       <c r="V22" s="11">
-        <f t="shared" si="134"/>
+        <f t="shared" si="152"/>
         <v>-7.9759862778730706E-2</v>
       </c>
       <c r="W22" s="11">
-        <f t="shared" si="134"/>
+        <f t="shared" si="152"/>
         <v>0.22973598888374247</v>
       </c>
       <c r="X22" s="11">
-        <f t="shared" si="134"/>
+        <f t="shared" si="152"/>
         <v>0.11888111888111888</v>
       </c>
       <c r="Y22" s="11">
-        <f t="shared" si="134"/>
+        <f t="shared" si="152"/>
         <v>0.15428983417447728</v>
       </c>
       <c r="Z22" s="11">
-        <f t="shared" si="134"/>
+        <f t="shared" si="152"/>
         <v>0.71987145152651311</v>
       </c>
       <c r="AA22" s="11">
-        <f t="shared" si="134"/>
+        <f t="shared" si="152"/>
         <v>0.17245657568238212</v>
       </c>
       <c r="AB22" s="11">
-        <f t="shared" si="134"/>
+        <f t="shared" si="152"/>
         <v>0.24815422477440524</v>
       </c>
       <c r="AC22" s="11">
-        <f t="shared" si="134"/>
+        <f t="shared" si="152"/>
         <v>-3.1070195627157654E-2</v>
       </c>
       <c r="AD22" s="11">
-        <f t="shared" si="134"/>
-        <v>0.28897411198793843</v>
-      </c>
-      <c r="AE22" s="11"/>
-      <c r="AF22" s="11"/>
-      <c r="AG22" s="11"/>
-      <c r="AH22" s="11"/>
+        <f t="shared" si="152"/>
+        <v>0.20872947277441659</v>
+      </c>
+      <c r="AE22" s="11">
+        <f t="shared" ref="AE22:AH22" si="153">AE11/AE10</f>
+        <v>0.23832528180354268</v>
+      </c>
+      <c r="AF22" s="11">
+        <f t="shared" si="153"/>
+        <v>1.0536044362292052</v>
+      </c>
+      <c r="AG22" s="11">
+        <f t="shared" si="153"/>
+        <v>0.2</v>
+      </c>
+      <c r="AH22" s="11">
+        <f t="shared" si="153"/>
+        <v>0.2</v>
+      </c>
       <c r="AJ22" s="11">
-        <f t="shared" ref="AJ22:AV22" si="135">AJ11/AJ10</f>
+        <f t="shared" ref="AJ22:AV22" si="154">AJ11/AJ10</f>
         <v>0.14959723820483314</v>
       </c>
       <c r="AK22" s="11">
-        <f t="shared" si="135"/>
+        <f t="shared" si="154"/>
         <v>1.1312500000000001</v>
       </c>
       <c r="AL22" s="11">
-        <f t="shared" si="135"/>
+        <f t="shared" si="154"/>
         <v>-0.14336917562724014</v>
       </c>
       <c r="AM22" s="11">
-        <f t="shared" si="135"/>
+        <f t="shared" si="154"/>
         <v>-7.3115860517435323E-3</v>
       </c>
       <c r="AN22" s="11">
-        <f t="shared" si="135"/>
+        <f t="shared" si="154"/>
         <v>0.28647214854111408</v>
       </c>
       <c r="AO22" s="11">
-        <f t="shared" si="135"/>
+        <f t="shared" si="154"/>
         <v>-9.1252835896143178E-2</v>
       </c>
       <c r="AP22" s="11">
-        <f t="shared" si="135"/>
+        <f t="shared" si="154"/>
         <v>0.18512373842112539</v>
       </c>
       <c r="AQ22" s="11">
-        <f t="shared" si="135"/>
+        <f t="shared" si="154"/>
+        <v>0.4227469803472621</v>
+      </c>
+      <c r="AR22" s="11">
+        <f t="shared" si="154"/>
         <v>0.18</v>
       </c>
-      <c r="AR22" s="11">
-        <f t="shared" si="135"/>
+      <c r="AS22" s="11">
+        <f t="shared" si="154"/>
         <v>0.18</v>
       </c>
-      <c r="AS22" s="11">
-        <f t="shared" si="135"/>
+      <c r="AT22" s="11">
+        <f t="shared" si="154"/>
         <v>0.18</v>
       </c>
-      <c r="AT22" s="11">
-        <f t="shared" si="135"/>
+      <c r="AU22" s="11">
+        <f t="shared" si="154"/>
         <v>0.18</v>
       </c>
-      <c r="AU22" s="11">
-        <f t="shared" si="135"/>
+      <c r="AV22" s="11">
+        <f t="shared" si="154"/>
         <v>0.18</v>
       </c>
-      <c r="AV22" s="11">
-        <f t="shared" si="135"/>
+      <c r="AW22" s="11">
+        <f t="shared" ref="AW22:BA22" si="155">AW11/AW10</f>
         <v>0.18</v>
       </c>
-      <c r="AW22" s="11">
-        <f t="shared" ref="AW22:BA22" si="136">AW11/AW10</f>
+      <c r="AX22" s="11">
+        <f t="shared" si="155"/>
         <v>0.18</v>
       </c>
-      <c r="AX22" s="11">
-        <f t="shared" si="136"/>
+      <c r="AY22" s="11">
+        <f t="shared" si="155"/>
         <v>0.18</v>
       </c>
-      <c r="AY22" s="11">
-        <f t="shared" si="136"/>
+      <c r="AZ22" s="11">
+        <f t="shared" si="155"/>
         <v>0.18</v>
       </c>
-      <c r="AZ22" s="11">
-        <f t="shared" si="136"/>
-        <v>0.18</v>
-      </c>
       <c r="BA22" s="11">
-        <f t="shared" si="136"/>
+        <f t="shared" si="155"/>
         <v>0.18</v>
       </c>
       <c r="BC22" s="1" t="s">
@@ -4857,7 +5054,7 @@
       </c>
       <c r="BD22" s="6">
         <f>Main!D8</f>
-        <v>-109060</v>
+        <v>-113353</v>
       </c>
     </row>
     <row r="23" spans="2:56" x14ac:dyDescent="0.3">
@@ -4869,195 +5066,207 @@
         <v>4.1373721966681758E-2</v>
       </c>
       <c r="D23" s="10">
-        <f t="shared" ref="D23:N23" si="137">D13/D3</f>
+        <f t="shared" ref="D23:N23" si="156">D13/D3</f>
         <v>2.7389516957862282E-2</v>
       </c>
       <c r="E23" s="10">
-        <f t="shared" si="137"/>
+        <f t="shared" si="156"/>
         <v>2.631020018053417E-2</v>
       </c>
       <c r="F23" s="10">
-        <f t="shared" si="137"/>
+        <f t="shared" si="156"/>
         <v>-2.775584428014261E-3</v>
       </c>
       <c r="G23" s="10">
-        <f t="shared" si="137"/>
+        <f t="shared" si="156"/>
         <v>2.8407119131426305E-2</v>
       </c>
       <c r="H23" s="10">
-        <f t="shared" si="137"/>
+        <f t="shared" si="156"/>
         <v>3.8092296605152756E-3</v>
       </c>
       <c r="I23" s="10">
-        <f t="shared" si="137"/>
+        <f t="shared" si="156"/>
         <v>1.1489591781562584E-2</v>
       </c>
       <c r="J23" s="10">
-        <f t="shared" si="137"/>
+        <f t="shared" si="156"/>
         <v>-4.2099962230895127E-2</v>
       </c>
       <c r="K23" s="10">
-        <f t="shared" si="137"/>
+        <f t="shared" si="156"/>
         <v>-5.807109557109557E-2</v>
       </c>
       <c r="L23" s="10">
-        <f t="shared" si="137"/>
+        <f t="shared" si="156"/>
         <v>5.7663517629446076E-2</v>
       </c>
       <c r="M23" s="10">
-        <f t="shared" si="137"/>
+        <f t="shared" si="156"/>
         <v>6.3598304045225457E-2</v>
       </c>
       <c r="N23" s="10">
-        <f t="shared" si="137"/>
+        <f t="shared" si="156"/>
         <v>-7.5712060525144585E-3</v>
       </c>
       <c r="O23" s="10">
-        <f t="shared" ref="O23:AD23" si="138">O13/O3</f>
+        <f t="shared" ref="O23:AD23" si="157">O13/O3</f>
         <v>9.0040852379375064E-2</v>
       </c>
       <c r="P23" s="10">
-        <f t="shared" si="138"/>
+        <f t="shared" si="157"/>
         <v>2.0970394736842105E-2</v>
       </c>
       <c r="Q23" s="10">
-        <f t="shared" si="138"/>
+        <f t="shared" si="157"/>
         <v>5.1340974693831795E-2</v>
       </c>
       <c r="R23" s="10">
-        <f t="shared" si="138"/>
+        <f t="shared" si="157"/>
         <v>0.32597271617389456</v>
       </c>
       <c r="S23" s="10">
-        <f t="shared" si="138"/>
+        <f t="shared" si="157"/>
         <v>-9.0207680705418264E-2</v>
       </c>
       <c r="T23" s="10">
-        <f t="shared" si="138"/>
+        <f t="shared" si="157"/>
         <v>1.6596168201045036E-2</v>
       </c>
       <c r="U23" s="10">
-        <f t="shared" si="138"/>
+        <f t="shared" si="157"/>
         <v>-2.0994110479285136E-2</v>
       </c>
       <c r="V23" s="10">
-        <f t="shared" si="138"/>
+        <f t="shared" si="157"/>
         <v>2.9296120366371962E-2</v>
       </c>
       <c r="W23" s="10">
-        <f t="shared" si="138"/>
+        <f t="shared" si="157"/>
         <v>4.236389063027439E-2</v>
       </c>
       <c r="X23" s="10">
-        <f t="shared" si="138"/>
+        <f t="shared" si="157"/>
         <v>4.2643591226587181E-2</v>
       </c>
       <c r="Y23" s="10">
-        <f t="shared" si="138"/>
+        <f t="shared" si="157"/>
         <v>2.7373804251044496E-2</v>
       </c>
       <c r="Z23" s="10">
-        <f t="shared" si="138"/>
+        <f t="shared" si="157"/>
         <v>-1.1444236543231364E-2</v>
       </c>
       <c r="AA23" s="10">
-        <f t="shared" si="138"/>
+        <f t="shared" si="157"/>
         <v>3.1138228487271196E-2</v>
       </c>
       <c r="AB23" s="10">
-        <f t="shared" si="138"/>
+        <f t="shared" si="157"/>
         <v>3.8299029451137882E-2</v>
       </c>
       <c r="AC23" s="10">
-        <f t="shared" si="138"/>
+        <f t="shared" si="157"/>
         <v>1.9309031084942418E-2</v>
       </c>
       <c r="AD23" s="10">
-        <f t="shared" si="138"/>
-        <v>2.4505403331189984E-2</v>
-      </c>
-      <c r="AE23" s="10"/>
-      <c r="AF23" s="10"/>
-      <c r="AG23" s="10"/>
-      <c r="AH23" s="10"/>
+        <f t="shared" si="157"/>
+        <v>3.7833689406981806E-2</v>
+      </c>
+      <c r="AE23" s="10">
+        <f t="shared" ref="AE23:AH23" si="158">AE13/AE3</f>
+        <v>1.158415111045525E-2</v>
+      </c>
+      <c r="AF23" s="10">
+        <f t="shared" si="158"/>
+        <v>-7.173601147776184E-4</v>
+      </c>
+      <c r="AG23" s="10">
+        <f t="shared" si="158"/>
+        <v>1.0142556147924576E-2</v>
+      </c>
+      <c r="AH23" s="10">
+        <f t="shared" si="158"/>
+        <v>6.1726438641250651E-3</v>
+      </c>
       <c r="AJ23" s="10">
-        <f t="shared" ref="AJ23:AV23" si="139">AJ13/AJ3</f>
+        <f t="shared" ref="AJ23:AV23" si="159">AJ13/AJ3</f>
         <v>2.2932804450598112E-2</v>
       </c>
       <c r="AK23" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="159"/>
         <v>3.0147530468248876E-4</v>
       </c>
       <c r="AL23" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="159"/>
         <v>-1.0059460139684138E-2</v>
       </c>
       <c r="AM23" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="159"/>
         <v>0.13155983893326292</v>
       </c>
       <c r="AN23" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="159"/>
         <v>-1.2533453121342301E-2</v>
       </c>
       <c r="AO23" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="159"/>
         <v>2.4672088812708937E-2</v>
       </c>
       <c r="AP23" s="10">
-        <f t="shared" si="139"/>
+        <f t="shared" si="159"/>
         <v>3.1779752637951908E-2</v>
       </c>
       <c r="AQ23" s="10">
-        <f t="shared" si="139"/>
-        <v>3.5039727622317142E-2</v>
+        <f t="shared" si="159"/>
+        <v>6.5243949911129705E-3</v>
       </c>
       <c r="AR23" s="10">
-        <f t="shared" si="139"/>
-        <v>3.8220633768835437E-2</v>
+        <f t="shared" si="159"/>
+        <v>2.1362478660987037E-2</v>
       </c>
       <c r="AS23" s="10">
-        <f t="shared" si="139"/>
-        <v>3.8221015964322279E-2</v>
+        <f t="shared" si="159"/>
+        <v>3.2021713551653355E-2</v>
       </c>
       <c r="AT23" s="10">
-        <f t="shared" si="139"/>
-        <v>3.8221396267752242E-2</v>
+        <f t="shared" si="159"/>
+        <v>3.3629507985446075E-2</v>
       </c>
       <c r="AU23" s="10">
-        <f t="shared" si="139"/>
-        <v>3.8221774688491965E-2</v>
+        <f t="shared" si="159"/>
+        <v>3.4425739584797589E-2</v>
       </c>
       <c r="AV23" s="10">
-        <f t="shared" si="139"/>
-        <v>3.8222151235861666E-2</v>
+        <f t="shared" si="159"/>
+        <v>3.4426179856345794E-2</v>
       </c>
       <c r="AW23" s="10">
-        <f t="shared" ref="AW23:BA23" si="140">AW13/AW3</f>
-        <v>3.8222525919135497E-2</v>
+        <f t="shared" ref="AW23:BA23" si="160">AW13/AW3</f>
+        <v>3.4426617948331871E-2</v>
       </c>
       <c r="AX23" s="10">
-        <f t="shared" si="140"/>
-        <v>3.8222898747541652E-2</v>
+        <f t="shared" si="160"/>
+        <v>3.4427053871545751E-2</v>
       </c>
       <c r="AY23" s="10">
-        <f t="shared" si="140"/>
-        <v>3.8223269730262611E-2</v>
+        <f t="shared" si="160"/>
+        <v>3.4427487636723902E-2</v>
       </c>
       <c r="AZ23" s="10">
-        <f t="shared" si="140"/>
-        <v>3.8223638876435428E-2</v>
+        <f t="shared" si="160"/>
+        <v>3.4427919254549702E-2</v>
       </c>
       <c r="BA23" s="10">
-        <f t="shared" si="140"/>
-        <v>3.8224006195151983E-2</v>
+        <f t="shared" si="160"/>
+        <v>3.4428348735653584E-2</v>
       </c>
       <c r="BC23" s="1" t="s">
         <v>41</v>
       </c>
       <c r="BD23" s="6">
         <f>BD21+BD22</f>
-        <v>2690.6888698807015</v>
+        <v>16432.601629084558</v>
       </c>
     </row>
     <row r="24" spans="2:56" x14ac:dyDescent="0.3">
@@ -5066,7 +5275,7 @@
       </c>
       <c r="BD24" s="4">
         <f>BD23/AV14</f>
-        <v>0.67886687772945664</v>
+        <v>4.1287943791669743</v>
       </c>
     </row>
     <row r="25" spans="2:56" x14ac:dyDescent="0.3">
@@ -5075,7 +5284,7 @@
       </c>
       <c r="BD25" s="4">
         <f>Main!D3</f>
-        <v>9.77</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="26" spans="2:56" x14ac:dyDescent="0.3">
@@ -5084,7 +5293,7 @@
       </c>
       <c r="BD26" s="10">
         <f>BD24/BD25-1</f>
-        <v>-0.93051516092840769</v>
+        <v>-0.61304644993749069</v>
       </c>
     </row>
     <row r="27" spans="2:56" x14ac:dyDescent="0.3">

--- a/Financial Analysis/F.xlsx
+++ b/Financial Analysis/F.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C8FB418-6509-4919-A85D-362D94A701C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57775898-4195-43C4-8809-E33EDA86E2F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{DBEEBD90-F12B-4C1A-B913-1AA5EC76930C}"/>
   </bookViews>
@@ -367,14 +367,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>7620</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>83820</xdr:rowOff>
     </xdr:to>
@@ -391,7 +391,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="19629120" y="0"/>
+          <a:off x="21473160" y="0"/>
           <a:ext cx="0" cy="6301740"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -793,17 +793,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="4">
-        <v>10.67</v>
+        <v>13.76</v>
       </c>
       <c r="E3" s="5">
-        <v>45869</v>
+        <v>45957</v>
       </c>
       <c r="F3" s="5">
         <f ca="1">TODAY()</f>
-        <v>45869</v>
+        <v>45957</v>
       </c>
       <c r="G3" s="5">
-        <v>45952</v>
+        <v>46063</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -811,10 +811,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="6">
-        <v>3980</v>
+        <f>3976</f>
+        <v>3976</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -823,7 +824,7 @@
       </c>
       <c r="D5" s="6">
         <f>D3*D4</f>
-        <v>42466.6</v>
+        <v>54709.760000000002</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -835,7 +836,7 @@
         <v>45169</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -847,7 +848,7 @@
         <v>158522</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -865,7 +866,7 @@
       </c>
       <c r="D9" s="6">
         <f>D5-D8</f>
-        <v>155819.6</v>
+        <v>168062.76</v>
       </c>
     </row>
   </sheetData>
@@ -1145,12 +1146,11 @@
         <v>50184</v>
       </c>
       <c r="AG3" s="8">
-        <f>AC3*1.05</f>
-        <v>48505.8</v>
+        <v>50534</v>
       </c>
       <c r="AH3" s="8">
-        <f>AD3*1.05</f>
-        <v>50621.55</v>
+        <f>AD3*1.06</f>
+        <v>51103.66</v>
       </c>
       <c r="AJ3" s="8">
         <f>SUM(C3:F3)</f>
@@ -1177,47 +1177,47 @@
       </c>
       <c r="AQ3" s="8">
         <f>SUM(AE3:AH3)</f>
-        <v>189970.34999999998</v>
+        <v>192480.66</v>
       </c>
       <c r="AR3" s="8">
-        <f>AQ3*1.05</f>
-        <v>199468.86749999999</v>
+        <f>AQ3*1.06</f>
+        <v>204029.49960000001</v>
       </c>
       <c r="AS3" s="8">
-        <f>AR3*1.04</f>
-        <v>207447.62220000001</v>
+        <f>AR3*1.05</f>
+        <v>214230.97458000001</v>
       </c>
       <c r="AT3" s="8">
         <f>AS3*1.03</f>
-        <v>213671.05086600001</v>
+        <v>220657.90381740002</v>
       </c>
       <c r="AU3" s="8">
         <f>AT3*1.02</f>
-        <v>217944.47188332002</v>
+        <v>225071.06189374803</v>
       </c>
       <c r="AV3" s="8">
-        <f t="shared" ref="AS3:BA3" si="0">AU3*1.01</f>
-        <v>220123.91660215321</v>
+        <f t="shared" ref="AV3:BA3" si="0">AU3*1.01</f>
+        <v>227321.77251268551</v>
       </c>
       <c r="AW3" s="8">
         <f t="shared" si="0"/>
-        <v>222325.15576817474</v>
+        <v>229594.99023781237</v>
       </c>
       <c r="AX3" s="8">
         <f t="shared" si="0"/>
-        <v>224548.40732585647</v>
+        <v>231890.94014019051</v>
       </c>
       <c r="AY3" s="8">
         <f t="shared" si="0"/>
-        <v>226793.89139911503</v>
+        <v>234209.84954159241</v>
       </c>
       <c r="AZ3" s="8">
         <f t="shared" si="0"/>
-        <v>229061.83031310618</v>
+        <v>236551.94803700835</v>
       </c>
       <c r="BA3" s="8">
         <f t="shared" si="0"/>
-        <v>231352.44861623723</v>
+        <v>238917.46751737842</v>
       </c>
     </row>
     <row r="4" spans="2:139" x14ac:dyDescent="0.3">
@@ -1322,12 +1322,11 @@
         <v>44245</v>
       </c>
       <c r="AG4" s="6">
-        <f>AG3-AG5</f>
-        <v>42685.104000000007</v>
+        <v>43411</v>
       </c>
       <c r="AH4" s="6">
         <f>AH3-AH5</f>
-        <v>44546.964</v>
+        <v>44460.184200000003</v>
       </c>
       <c r="AJ4" s="6">
         <f>SUM(C4:F4)</f>
@@ -1354,47 +1353,47 @@
       </c>
       <c r="AQ4" s="6">
         <f>SUM(AE4:AH4)</f>
-        <v>166665.068</v>
+        <v>167304.18420000002</v>
       </c>
       <c r="AR4" s="6">
-        <f t="shared" ref="AQ4:AV4" si="1">AR3-AR5</f>
-        <v>173537.91472499998</v>
+        <f t="shared" ref="AR4:AV4" si="1">AR3-AR5</f>
+        <v>177505.66465200001</v>
       </c>
       <c r="AS4" s="6">
         <f t="shared" si="1"/>
-        <v>178404.95509200002</v>
+        <v>184238.63813880002</v>
       </c>
       <c r="AT4" s="6">
         <f t="shared" si="1"/>
-        <v>183757.10374476001</v>
+        <v>189765.79728296402</v>
       </c>
       <c r="AU4" s="6">
         <f t="shared" si="1"/>
-        <v>187432.24581965522</v>
+        <v>193561.11322862329</v>
       </c>
       <c r="AV4" s="6">
         <f t="shared" si="1"/>
-        <v>189306.56827785177</v>
+        <v>195496.72436090955</v>
       </c>
       <c r="AW4" s="6">
         <f t="shared" ref="AW4:BA4" si="2">AW3-AW5</f>
-        <v>191199.63396063028</v>
+        <v>197451.69160451862</v>
       </c>
       <c r="AX4" s="6">
         <f t="shared" si="2"/>
-        <v>193111.63030023657</v>
+        <v>199426.20852056384</v>
       </c>
       <c r="AY4" s="6">
         <f t="shared" si="2"/>
-        <v>195042.74660323892</v>
+        <v>201420.47060576949</v>
       </c>
       <c r="AZ4" s="6">
         <f t="shared" si="2"/>
-        <v>196993.17406927131</v>
+        <v>203434.67531182716</v>
       </c>
       <c r="BA4" s="6">
         <f t="shared" si="2"/>
-        <v>198963.10580996401</v>
+        <v>205469.02206494543</v>
       </c>
     </row>
     <row r="5" spans="2:139" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -1514,7 +1513,7 @@
         <v>6910</v>
       </c>
       <c r="AE5" s="8">
-        <f t="shared" ref="AE5:AF5" si="15">AE3-AE4</f>
+        <f t="shared" ref="AE5:AG5" si="15">AE3-AE4</f>
         <v>5471</v>
       </c>
       <c r="AF5" s="8">
@@ -1522,12 +1521,12 @@
         <v>5939</v>
       </c>
       <c r="AG5" s="8">
-        <f>AG3*0.12</f>
-        <v>5820.6959999999999</v>
+        <f t="shared" si="15"/>
+        <v>7123</v>
       </c>
       <c r="AH5" s="8">
-        <f>AH3*0.12</f>
-        <v>6074.5860000000002</v>
+        <f>AH3*0.13</f>
+        <v>6643.4758000000011</v>
       </c>
       <c r="AJ5" s="8">
         <f>AJ3-AJ4</f>
@@ -1559,47 +1558,47 @@
       </c>
       <c r="AQ5" s="8">
         <f t="shared" si="16"/>
-        <v>23305.281999999977</v>
+        <v>25176.475799999986</v>
       </c>
       <c r="AR5" s="8">
         <f>AR3*0.13</f>
-        <v>25930.952775000002</v>
+        <v>26523.834948000003</v>
       </c>
       <c r="AS5" s="8">
-        <f t="shared" ref="AR5:BA5" si="17">AS3*0.14</f>
-        <v>29042.667108000005</v>
+        <f t="shared" ref="AS5:BA5" si="17">AS3*0.14</f>
+        <v>29992.336441200005</v>
       </c>
       <c r="AT5" s="8">
         <f t="shared" si="17"/>
-        <v>29913.947121240002</v>
+        <v>30892.106534436007</v>
       </c>
       <c r="AU5" s="8">
         <f t="shared" si="17"/>
-        <v>30512.226063664806</v>
+        <v>31509.948665124728</v>
       </c>
       <c r="AV5" s="8">
         <f t="shared" si="17"/>
-        <v>30817.348324301453</v>
+        <v>31825.048151775973</v>
       </c>
       <c r="AW5" s="8">
         <f t="shared" si="17"/>
-        <v>31125.521807544465</v>
+        <v>32143.298633293733</v>
       </c>
       <c r="AX5" s="8">
         <f t="shared" si="17"/>
-        <v>31436.777025619911</v>
+        <v>32464.731619626673</v>
       </c>
       <c r="AY5" s="8">
         <f t="shared" si="17"/>
-        <v>31751.144795876109</v>
+        <v>32789.378935822941</v>
       </c>
       <c r="AZ5" s="8">
         <f t="shared" si="17"/>
-        <v>32068.65624383487</v>
+        <v>33117.272725181174</v>
       </c>
       <c r="BA5" s="8">
         <f t="shared" si="17"/>
-        <v>32389.342806273216</v>
+        <v>33448.445452432985</v>
       </c>
     </row>
     <row r="6" spans="2:139" x14ac:dyDescent="0.3">
@@ -1704,12 +1703,11 @@
         <v>2706</v>
       </c>
       <c r="AG6" s="6">
-        <f>AC6*1.01</f>
-        <v>2480.56</v>
+        <v>2740</v>
       </c>
       <c r="AH6" s="6">
-        <f>AD6*1.01</f>
-        <v>2804.77</v>
+        <f>AD6*1.02</f>
+        <v>2832.54</v>
       </c>
       <c r="AJ6" s="6">
         <f>SUM(C6:F6)</f>
@@ -1736,47 +1734,47 @@
       </c>
       <c r="AQ6" s="6">
         <f t="shared" ref="AQ6:AQ7" si="19">SUM(AE6:AH6)</f>
-        <v>10422.33</v>
+        <v>10709.54</v>
       </c>
       <c r="AR6" s="6">
-        <f>AQ6*0.95</f>
-        <v>9901.2134999999998</v>
+        <f>AQ6*0.98</f>
+        <v>10495.349200000001</v>
       </c>
       <c r="AS6" s="6">
         <f t="shared" ref="AS6:BA7" si="20">AR6*1.01</f>
-        <v>10000.225635000001</v>
+        <v>10600.302692000001</v>
       </c>
       <c r="AT6" s="6">
         <f t="shared" si="20"/>
-        <v>10100.227891350001</v>
+        <v>10706.305718920001</v>
       </c>
       <c r="AU6" s="6">
         <f t="shared" si="20"/>
-        <v>10201.230170263501</v>
+        <v>10813.368776109201</v>
       </c>
       <c r="AV6" s="6">
         <f t="shared" si="20"/>
-        <v>10303.242471966136</v>
+        <v>10921.502463870293</v>
       </c>
       <c r="AW6" s="6">
         <f t="shared" si="20"/>
-        <v>10406.274896685798</v>
+        <v>11030.717488508995</v>
       </c>
       <c r="AX6" s="6">
         <f t="shared" si="20"/>
-        <v>10510.337645652657</v>
+        <v>11141.024663394086</v>
       </c>
       <c r="AY6" s="6">
         <f t="shared" si="20"/>
-        <v>10615.441022109184</v>
+        <v>11252.434910028027</v>
       </c>
       <c r="AZ6" s="6">
         <f t="shared" si="20"/>
-        <v>10721.595432330276</v>
+        <v>11364.959259128307</v>
       </c>
       <c r="BA6" s="6">
         <f t="shared" si="20"/>
-        <v>10828.811386653579</v>
+        <v>11478.608851719589</v>
       </c>
     </row>
     <row r="7" spans="2:139" x14ac:dyDescent="0.3">
@@ -1881,8 +1879,7 @@
         <v>2722</v>
       </c>
       <c r="AG7" s="6">
-        <f>AC7*1.01</f>
-        <v>2718.92</v>
+        <v>2825</v>
       </c>
       <c r="AH7" s="6">
         <f>AD7*0.99</f>
@@ -1913,47 +1910,47 @@
       </c>
       <c r="AQ7" s="6">
         <f t="shared" si="19"/>
-        <v>11034.9</v>
+        <v>11140.98</v>
       </c>
       <c r="AR7" s="6">
         <f t="shared" ref="AR7" si="21">AQ7*1.01</f>
-        <v>11145.249</v>
+        <v>11252.389799999999</v>
       </c>
       <c r="AS7" s="6">
         <f t="shared" si="20"/>
-        <v>11256.701489999999</v>
+        <v>11364.913697999998</v>
       </c>
       <c r="AT7" s="6">
         <f t="shared" si="20"/>
-        <v>11369.268504899999</v>
+        <v>11478.562834979999</v>
       </c>
       <c r="AU7" s="6">
         <f t="shared" si="20"/>
-        <v>11482.961189948999</v>
+        <v>11593.348463329799</v>
       </c>
       <c r="AV7" s="6">
         <f t="shared" si="20"/>
-        <v>11597.790801848489</v>
+        <v>11709.281947963098</v>
       </c>
       <c r="AW7" s="6">
         <f t="shared" si="20"/>
-        <v>11713.768709866974</v>
+        <v>11826.374767442729</v>
       </c>
       <c r="AX7" s="6">
         <f t="shared" si="20"/>
-        <v>11830.906396965644</v>
+        <v>11944.638515117156</v>
       </c>
       <c r="AY7" s="6">
         <f t="shared" si="20"/>
-        <v>11949.2154609353</v>
+        <v>12064.084900268328</v>
       </c>
       <c r="AZ7" s="6">
         <f t="shared" si="20"/>
-        <v>12068.707615544654</v>
+        <v>12184.725749271012</v>
       </c>
       <c r="BA7" s="6">
         <f t="shared" si="20"/>
-        <v>12189.394691700101</v>
+        <v>12306.573006763723</v>
       </c>
     </row>
     <row r="8" spans="2:139" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -2082,11 +2079,11 @@
       </c>
       <c r="AG8" s="8">
         <f t="shared" si="33"/>
-        <v>621.21599999999989</v>
+        <v>1558</v>
       </c>
       <c r="AH8" s="8">
         <f t="shared" si="33"/>
-        <v>396.83600000000024</v>
+        <v>937.95580000000109</v>
       </c>
       <c r="AJ8" s="8">
         <f>AJ5-AJ6-AJ7</f>
@@ -2118,47 +2115,47 @@
       </c>
       <c r="AQ8" s="8">
         <f t="shared" si="34"/>
-        <v>1848.0519999999779</v>
+        <v>3325.9557999999852</v>
       </c>
       <c r="AR8" s="8">
         <f t="shared" si="34"/>
-        <v>4884.4902750000019</v>
+        <v>4776.0959480000038</v>
       </c>
       <c r="AS8" s="8">
         <f t="shared" si="34"/>
-        <v>7785.7399830000068</v>
+        <v>8027.120051200005</v>
       </c>
       <c r="AT8" s="8">
         <f t="shared" si="34"/>
-        <v>8444.4507249900016</v>
+        <v>8707.2379805360069</v>
       </c>
       <c r="AU8" s="8">
         <f t="shared" si="34"/>
-        <v>8828.0347034523056</v>
+        <v>9103.231425685728</v>
       </c>
       <c r="AV8" s="8">
         <f t="shared" si="34"/>
-        <v>8916.3150504868281</v>
+        <v>9194.2637399425821</v>
       </c>
       <c r="AW8" s="8">
         <f t="shared" ref="AW8:BA8" si="35">AW5-AW6-AW7</f>
-        <v>9005.4782009916926</v>
+        <v>9286.2063773420086</v>
       </c>
       <c r="AX8" s="8">
         <f t="shared" si="35"/>
-        <v>9095.5329830016108</v>
+        <v>9379.0684411154289</v>
       </c>
       <c r="AY8" s="8">
         <f t="shared" si="35"/>
-        <v>9186.4883128316233</v>
+        <v>9472.8591255265856</v>
       </c>
       <c r="AZ8" s="8">
         <f t="shared" si="35"/>
-        <v>9278.3531959599404</v>
+        <v>9567.5877167818544</v>
       </c>
       <c r="BA8" s="8">
         <f t="shared" si="35"/>
-        <v>9371.1367279195365</v>
+        <v>9663.2635939496722</v>
       </c>
     </row>
     <row r="9" spans="2:139" x14ac:dyDescent="0.3">
@@ -2286,7 +2283,8 @@
         <v>-30</v>
       </c>
       <c r="AG9" s="6">
-        <v>0</v>
+        <f>321-560-21</f>
+        <v>-260</v>
       </c>
       <c r="AH9" s="6">
         <v>0</v>
@@ -2321,47 +2319,47 @@
       </c>
       <c r="AQ9" s="6">
         <f>SUM(AE9:AH9)</f>
-        <v>-332</v>
+        <v>-592</v>
       </c>
       <c r="AR9" s="6">
-        <f t="shared" ref="AQ9:AV9" si="36">AQ9*1.01</f>
-        <v>-335.32</v>
+        <f t="shared" ref="AR9:AV9" si="36">AQ9*1.01</f>
+        <v>-597.91999999999996</v>
       </c>
       <c r="AS9" s="6">
         <f t="shared" si="36"/>
-        <v>-338.67320000000001</v>
+        <v>-603.89919999999995</v>
       </c>
       <c r="AT9" s="6">
         <f t="shared" si="36"/>
-        <v>-342.059932</v>
+        <v>-609.93819199999996</v>
       </c>
       <c r="AU9" s="6">
         <f t="shared" si="36"/>
-        <v>-345.48053132000001</v>
+        <v>-616.03757392</v>
       </c>
       <c r="AV9" s="6">
         <f t="shared" si="36"/>
-        <v>-348.9353366332</v>
+        <v>-622.19794965920005</v>
       </c>
       <c r="AW9" s="6">
         <f t="shared" ref="AW9" si="37">AV9*1.01</f>
-        <v>-352.42468999953201</v>
+        <v>-628.41992915579203</v>
       </c>
       <c r="AX9" s="6">
         <f t="shared" ref="AX9" si="38">AW9*1.01</f>
-        <v>-355.94893689952733</v>
+        <v>-634.70412844734994</v>
       </c>
       <c r="AY9" s="6">
         <f t="shared" ref="AY9" si="39">AX9*1.01</f>
-        <v>-359.50842626852261</v>
+        <v>-641.05116973182339</v>
       </c>
       <c r="AZ9" s="6">
         <f t="shared" ref="AZ9" si="40">AY9*1.01</f>
-        <v>-363.10351053120786</v>
+        <v>-647.46168142914166</v>
       </c>
       <c r="BA9" s="6">
         <f t="shared" ref="BA9" si="41">AZ9*1.01</f>
-        <v>-366.73454563651995</v>
+        <v>-653.93629824343304</v>
       </c>
     </row>
     <row r="10" spans="2:139" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -2490,11 +2488,11 @@
       </c>
       <c r="AG10" s="8">
         <f t="shared" si="53"/>
-        <v>621.21599999999989</v>
+        <v>1818</v>
       </c>
       <c r="AH10" s="8">
         <f t="shared" si="53"/>
-        <v>396.83600000000024</v>
+        <v>937.95580000000109</v>
       </c>
       <c r="AJ10" s="8">
         <f>AJ8-AJ9</f>
@@ -2526,47 +2524,47 @@
       </c>
       <c r="AQ10" s="8">
         <f t="shared" si="54"/>
-        <v>2180.0519999999779</v>
+        <v>3917.9557999999852</v>
       </c>
       <c r="AR10" s="8">
         <f t="shared" si="54"/>
-        <v>5219.8102750000016</v>
+        <v>5374.0159480000038</v>
       </c>
       <c r="AS10" s="8">
         <f t="shared" si="54"/>
-        <v>8124.4131830000069</v>
+        <v>8631.0192512000049</v>
       </c>
       <c r="AT10" s="8">
         <f t="shared" si="54"/>
-        <v>8786.5106569900017</v>
+        <v>9317.1761725360066</v>
       </c>
       <c r="AU10" s="8">
         <f t="shared" si="54"/>
-        <v>9173.5152347723051</v>
+        <v>9719.2689996057288</v>
       </c>
       <c r="AV10" s="8">
         <f t="shared" si="54"/>
-        <v>9265.2503871200279</v>
+        <v>9816.4616896017815</v>
       </c>
       <c r="AW10" s="8">
         <f t="shared" ref="AW10:BA10" si="55">AW8-AW9</f>
-        <v>9357.9028909912249</v>
+        <v>9914.6263064978011</v>
       </c>
       <c r="AX10" s="8">
         <f t="shared" si="55"/>
-        <v>9451.4819199011381</v>
+        <v>10013.77256956278</v>
       </c>
       <c r="AY10" s="8">
         <f t="shared" si="55"/>
-        <v>9545.9967391001464</v>
+        <v>10113.910295258409</v>
       </c>
       <c r="AZ10" s="8">
         <f t="shared" si="55"/>
-        <v>9641.456706491148</v>
+        <v>10215.049398210997</v>
       </c>
       <c r="BA10" s="8">
         <f t="shared" si="55"/>
-        <v>9737.8712735560566</v>
+        <v>10317.199892193104</v>
       </c>
     </row>
     <row r="11" spans="2:139" x14ac:dyDescent="0.3">
@@ -2671,12 +2669,11 @@
         <v>570</v>
       </c>
       <c r="AG11" s="6">
-        <f>AG10*0.2</f>
-        <v>124.24319999999999</v>
+        <v>-630</v>
       </c>
       <c r="AH11" s="6">
         <f>AH10*0.2</f>
-        <v>79.367200000000054</v>
+        <v>187.59116000000023</v>
       </c>
       <c r="AJ11" s="6">
         <f>SUM(C11:F11)</f>
@@ -2703,47 +2700,47 @@
       </c>
       <c r="AQ11" s="6">
         <f t="shared" ref="AQ11:AQ12" si="56">SUM(AE11:AH11)</f>
-        <v>921.61040000000003</v>
+        <v>275.59116000000023</v>
       </c>
       <c r="AR11" s="6">
         <f t="shared" ref="AR11:BA11" si="57">AR10*0.18</f>
-        <v>939.56584950000024</v>
+        <v>967.3228706400007</v>
       </c>
       <c r="AS11" s="6">
         <f t="shared" si="57"/>
-        <v>1462.3943729400012</v>
+        <v>1553.5834652160008</v>
       </c>
       <c r="AT11" s="6">
         <f t="shared" si="57"/>
-        <v>1581.5719182582002</v>
+        <v>1677.091711056481</v>
       </c>
       <c r="AU11" s="6">
         <f t="shared" si="57"/>
-        <v>1651.2327422590149</v>
+        <v>1749.4684199290311</v>
       </c>
       <c r="AV11" s="6">
         <f t="shared" si="57"/>
-        <v>1667.7450696816049</v>
+        <v>1766.9631041283205</v>
       </c>
       <c r="AW11" s="6">
         <f t="shared" si="57"/>
-        <v>1684.4225203784204</v>
+        <v>1784.6327351696041</v>
       </c>
       <c r="AX11" s="6">
         <f t="shared" si="57"/>
-        <v>1701.2667455822047</v>
+        <v>1802.4790625213002</v>
       </c>
       <c r="AY11" s="6">
         <f t="shared" si="57"/>
-        <v>1718.2794130380264</v>
+        <v>1820.5038531465136</v>
       </c>
       <c r="AZ11" s="6">
         <f t="shared" si="57"/>
-        <v>1735.4622071684066</v>
+        <v>1838.7088916779794</v>
       </c>
       <c r="BA11" s="6">
         <f t="shared" si="57"/>
-        <v>1752.8168292400901</v>
+        <v>1857.0959805947587</v>
       </c>
     </row>
     <row r="12" spans="2:139" x14ac:dyDescent="0.3">
@@ -2848,7 +2845,7 @@
         <v>7</v>
       </c>
       <c r="AG12" s="6">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AH12" s="6">
         <v>5</v>
@@ -2878,47 +2875,47 @@
       </c>
       <c r="AQ12" s="6">
         <f t="shared" si="56"/>
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AR12" s="6">
-        <f t="shared" ref="AQ12:AV12" si="58">AQ12*1.005</f>
-        <v>19.094999999999999</v>
+        <f t="shared" ref="AR12:AV12" si="58">AQ12*1.005</f>
+        <v>15.074999999999999</v>
       </c>
       <c r="AS12" s="6">
         <f t="shared" si="58"/>
-        <v>19.190474999999996</v>
+        <v>15.150374999999997</v>
       </c>
       <c r="AT12" s="6">
         <f t="shared" si="58"/>
-        <v>19.286427374999995</v>
+        <v>15.226126874999995</v>
       </c>
       <c r="AU12" s="6">
         <f t="shared" si="58"/>
-        <v>19.382859511874994</v>
+        <v>15.302257509374993</v>
       </c>
       <c r="AV12" s="6">
         <f t="shared" si="58"/>
-        <v>19.479773809434366</v>
+        <v>15.378768796921866</v>
       </c>
       <c r="AW12" s="6">
         <f t="shared" ref="AW12" si="59">AV12*1.005</f>
-        <v>19.577172678481535</v>
+        <v>15.455662640906475</v>
       </c>
       <c r="AX12" s="6">
         <f t="shared" ref="AX12" si="60">AW12*1.005</f>
-        <v>19.675058541873941</v>
+        <v>15.532940954111005</v>
       </c>
       <c r="AY12" s="6">
         <f t="shared" ref="AY12" si="61">AX12*1.005</f>
-        <v>19.773433834583308</v>
+        <v>15.610605658881559</v>
       </c>
       <c r="AZ12" s="6">
         <f t="shared" ref="AZ12" si="62">AY12*1.005</f>
-        <v>19.872301003756224</v>
+        <v>15.688658687175964</v>
       </c>
       <c r="BA12" s="6">
         <f t="shared" ref="BA12" si="63">AZ12*1.005</f>
-        <v>19.971662508775005</v>
+        <v>15.767101980611843</v>
       </c>
     </row>
     <row r="13" spans="2:139" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -3047,11 +3044,11 @@
       </c>
       <c r="AG13" s="8">
         <f t="shared" si="75"/>
-        <v>491.97279999999989</v>
+        <v>2447</v>
       </c>
       <c r="AH13" s="8">
         <f t="shared" si="75"/>
-        <v>312.46880000000021</v>
+        <v>745.36464000000092</v>
       </c>
       <c r="AJ13" s="8">
         <f>AJ10-AJ11-AJ12</f>
@@ -3083,391 +3080,391 @@
       </c>
       <c r="AQ13" s="8">
         <f t="shared" si="76"/>
-        <v>1239.4415999999778</v>
+        <v>3627.3646399999848</v>
       </c>
       <c r="AR13" s="8">
         <f t="shared" si="76"/>
-        <v>4261.1494255000007</v>
+        <v>4391.6180773600036</v>
       </c>
       <c r="AS13" s="8">
         <f t="shared" si="76"/>
-        <v>6642.8283350600059</v>
+        <v>7062.2854109840036</v>
       </c>
       <c r="AT13" s="8">
         <f t="shared" si="76"/>
-        <v>7185.6523113568019</v>
+        <v>7624.8583346045261</v>
       </c>
       <c r="AU13" s="8">
         <f t="shared" si="76"/>
-        <v>7502.8996330014152</v>
+        <v>7954.4983221673228</v>
       </c>
       <c r="AV13" s="8">
         <f t="shared" si="76"/>
-        <v>7578.025543628989</v>
+        <v>8034.1198166765389</v>
       </c>
       <c r="AW13" s="8">
         <f t="shared" ref="AW13:BA13" si="77">AW10-AW11-AW12</f>
-        <v>7653.9031979343226</v>
+        <v>8114.5379086872908</v>
       </c>
       <c r="AX13" s="8">
         <f t="shared" si="77"/>
-        <v>7730.5401157770593</v>
+        <v>8195.7605660873669</v>
       </c>
       <c r="AY13" s="8">
         <f t="shared" si="77"/>
-        <v>7807.9438922275367</v>
+        <v>8277.7958364530132</v>
       </c>
       <c r="AZ13" s="8">
         <f t="shared" si="77"/>
-        <v>7886.1221983189853</v>
+        <v>8360.651847845842</v>
       </c>
       <c r="BA13" s="8">
         <f t="shared" si="77"/>
-        <v>7965.0827818071921</v>
+        <v>8444.3368096177346</v>
       </c>
       <c r="BB13" s="3">
         <f>BA13*(1+$BD$19)</f>
-        <v>7885.4319539891203</v>
+        <v>8359.8934415215572</v>
       </c>
       <c r="BC13" s="3">
         <f t="shared" ref="BC13:DN13" si="78">BB13*(1+$BD$19)</f>
-        <v>7806.5776344492288</v>
+        <v>8276.2945071063423</v>
       </c>
       <c r="BD13" s="3">
         <f t="shared" si="78"/>
-        <v>7728.5118581047363</v>
+        <v>8193.5315620352794</v>
       </c>
       <c r="BE13" s="3">
         <f t="shared" si="78"/>
-        <v>7651.2267395236886</v>
+        <v>8111.596246414927</v>
       </c>
       <c r="BF13" s="3">
         <f t="shared" si="78"/>
-        <v>7574.7144721284512</v>
+        <v>8030.4802839507774</v>
       </c>
       <c r="BG13" s="3">
         <f t="shared" si="78"/>
-        <v>7498.9673274071665</v>
+        <v>7950.1754811112696</v>
       </c>
       <c r="BH13" s="3">
         <f t="shared" si="78"/>
-        <v>7423.9776541330948</v>
+        <v>7870.6737263001569</v>
       </c>
       <c r="BI13" s="3">
         <f t="shared" si="78"/>
-        <v>7349.7378775917641</v>
+        <v>7791.9669890371551</v>
       </c>
       <c r="BJ13" s="3">
         <f t="shared" si="78"/>
-        <v>7276.240498815846</v>
+        <v>7714.0473191467836</v>
       </c>
       <c r="BK13" s="3">
         <f t="shared" si="78"/>
-        <v>7203.4780938276872</v>
+        <v>7636.9068459553155</v>
       </c>
       <c r="BL13" s="3">
         <f t="shared" si="78"/>
-        <v>7131.4433128894107</v>
+        <v>7560.5377774957624</v>
       </c>
       <c r="BM13" s="3">
         <f t="shared" si="78"/>
-        <v>7060.1288797605166</v>
+        <v>7484.9323997208048</v>
       </c>
       <c r="BN13" s="3">
         <f t="shared" si="78"/>
-        <v>6989.5275909629117</v>
+        <v>7410.0830757235963</v>
       </c>
       <c r="BO13" s="3">
         <f t="shared" si="78"/>
-        <v>6919.6323150532826</v>
+        <v>7335.9822449663607</v>
       </c>
       <c r="BP13" s="3">
         <f t="shared" si="78"/>
-        <v>6850.4359919027493</v>
+        <v>7262.622422516697</v>
       </c>
       <c r="BQ13" s="3">
         <f t="shared" si="78"/>
-        <v>6781.9316319837217</v>
+        <v>7189.9961982915302</v>
       </c>
       <c r="BR13" s="3">
         <f t="shared" si="78"/>
-        <v>6714.1123156638841</v>
+        <v>7118.0962363086146</v>
       </c>
       <c r="BS13" s="3">
         <f t="shared" si="78"/>
-        <v>6646.9711925072452</v>
+        <v>7046.9152739455285</v>
       </c>
       <c r="BT13" s="3">
         <f t="shared" si="78"/>
-        <v>6580.5014805821729</v>
+        <v>6976.4461212060733</v>
       </c>
       <c r="BU13" s="3">
         <f t="shared" si="78"/>
-        <v>6514.696465776351</v>
+        <v>6906.6816599940121</v>
       </c>
       <c r="BV13" s="3">
         <f t="shared" si="78"/>
-        <v>6449.5495011185876</v>
+        <v>6837.6148433940716</v>
       </c>
       <c r="BW13" s="3">
         <f t="shared" si="78"/>
-        <v>6385.0540061074016</v>
+        <v>6769.2386949601305</v>
       </c>
       <c r="BX13" s="3">
         <f t="shared" si="78"/>
-        <v>6321.2034660463278</v>
+        <v>6701.5463080105292</v>
       </c>
       <c r="BY13" s="3">
         <f t="shared" si="78"/>
-        <v>6257.9914313858644</v>
+        <v>6634.5308449304239</v>
       </c>
       <c r="BZ13" s="3">
         <f t="shared" si="78"/>
-        <v>6195.4115170720061</v>
+        <v>6568.1855364811199</v>
       </c>
       <c r="CA13" s="3">
         <f t="shared" si="78"/>
-        <v>6133.4574019012862</v>
+        <v>6502.5036811163091</v>
       </c>
       <c r="CB13" s="3">
         <f t="shared" si="78"/>
-        <v>6072.1228278822737</v>
+        <v>6437.4786443051462</v>
       </c>
       <c r="CC13" s="3">
         <f t="shared" si="78"/>
-        <v>6011.4015996034504</v>
+        <v>6373.1038578620946</v>
       </c>
       <c r="CD13" s="3">
         <f t="shared" si="78"/>
-        <v>5951.2875836074163</v>
+        <v>6309.3728192834733</v>
       </c>
       <c r="CE13" s="3">
         <f t="shared" si="78"/>
-        <v>5891.774707771342</v>
+        <v>6246.2790910906388</v>
       </c>
       <c r="CF13" s="3">
         <f t="shared" si="78"/>
-        <v>5832.8569606936289</v>
+        <v>6183.816300179732</v>
       </c>
       <c r="CG13" s="3">
         <f t="shared" si="78"/>
-        <v>5774.5283910866929</v>
+        <v>6121.9781371779345</v>
       </c>
       <c r="CH13" s="3">
         <f t="shared" si="78"/>
-        <v>5716.7831071758255</v>
+        <v>6060.7583558061551</v>
       </c>
       <c r="CI13" s="3">
         <f t="shared" si="78"/>
-        <v>5659.6152761040676</v>
+        <v>6000.1507722480937</v>
       </c>
       <c r="CJ13" s="3">
         <f t="shared" si="78"/>
-        <v>5603.0191233430269</v>
+        <v>5940.149264525613</v>
       </c>
       <c r="CK13" s="3">
         <f t="shared" si="78"/>
-        <v>5546.9889321095961</v>
+        <v>5880.7477718803566</v>
       </c>
       <c r="CL13" s="3">
         <f t="shared" si="78"/>
-        <v>5491.5190427885</v>
+        <v>5821.9402941615526</v>
       </c>
       <c r="CM13" s="3">
         <f t="shared" si="78"/>
-        <v>5436.6038523606148</v>
+        <v>5763.7208912199367</v>
       </c>
       <c r="CN13" s="3">
         <f t="shared" si="78"/>
-        <v>5382.2378138370086</v>
+        <v>5706.083682307737</v>
       </c>
       <c r="CO13" s="3">
         <f t="shared" si="78"/>
-        <v>5328.4154356986382</v>
+        <v>5649.0228454846592</v>
       </c>
       <c r="CP13" s="3">
         <f t="shared" si="78"/>
-        <v>5275.1312813416516</v>
+        <v>5592.5326170298122</v>
       </c>
       <c r="CQ13" s="3">
         <f t="shared" si="78"/>
-        <v>5222.3799685282347</v>
+        <v>5536.6072908595143</v>
       </c>
       <c r="CR13" s="3">
         <f t="shared" si="78"/>
-        <v>5170.156168842952</v>
+        <v>5481.2412179509192</v>
       </c>
       <c r="CS13" s="3">
         <f t="shared" si="78"/>
-        <v>5118.4546071545228</v>
+        <v>5426.4288057714102</v>
       </c>
       <c r="CT13" s="3">
         <f t="shared" si="78"/>
-        <v>5067.2700610829779</v>
+        <v>5372.1645177136961</v>
       </c>
       <c r="CU13" s="3">
         <f t="shared" si="78"/>
-        <v>5016.5973604721485</v>
+        <v>5318.4428725365588</v>
       </c>
       <c r="CV13" s="3">
         <f t="shared" si="78"/>
-        <v>4966.4313868674271</v>
+        <v>5265.2584438111935</v>
       </c>
       <c r="CW13" s="3">
         <f t="shared" si="78"/>
-        <v>4916.7670729987531</v>
+        <v>5212.6058593730813</v>
       </c>
       <c r="CX13" s="3">
         <f t="shared" si="78"/>
-        <v>4867.5994022687655</v>
+        <v>5160.4798007793506</v>
       </c>
       <c r="CY13" s="3">
         <f t="shared" si="78"/>
-        <v>4818.923408246078</v>
+        <v>5108.8750027715569</v>
       </c>
       <c r="CZ13" s="3">
         <f t="shared" si="78"/>
-        <v>4770.7341741636174</v>
+        <v>5057.786252743841</v>
       </c>
       <c r="DA13" s="3">
         <f t="shared" si="78"/>
-        <v>4723.0268324219815</v>
+        <v>5007.2083902164022</v>
       </c>
       <c r="DB13" s="3">
         <f t="shared" si="78"/>
-        <v>4675.7965640977618</v>
+        <v>4957.136306314238</v>
       </c>
       <c r="DC13" s="3">
         <f t="shared" si="78"/>
-        <v>4629.0385984567838</v>
+        <v>4907.5649432510954</v>
       </c>
       <c r="DD13" s="3">
         <f t="shared" si="78"/>
-        <v>4582.7482124722155</v>
+        <v>4858.4892938185849</v>
       </c>
       <c r="DE13" s="3">
         <f t="shared" si="78"/>
-        <v>4536.9207303474932</v>
+        <v>4809.9044008803994</v>
       </c>
       <c r="DF13" s="3">
         <f t="shared" si="78"/>
-        <v>4491.5515230440178</v>
+        <v>4761.805356871595</v>
       </c>
       <c r="DG13" s="3">
         <f t="shared" si="78"/>
-        <v>4446.6360078135776</v>
+        <v>4714.1873033028787</v>
       </c>
       <c r="DH13" s="3">
         <f t="shared" si="78"/>
-        <v>4402.1696477354417</v>
+        <v>4667.0454302698499</v>
       </c>
       <c r="DI13" s="3">
         <f t="shared" si="78"/>
-        <v>4358.1479512580872</v>
+        <v>4620.3749759671518</v>
       </c>
       <c r="DJ13" s="3">
         <f t="shared" si="78"/>
-        <v>4314.5664717455065</v>
+        <v>4574.1712262074807</v>
       </c>
       <c r="DK13" s="3">
         <f t="shared" si="78"/>
-        <v>4271.4208070280511</v>
+        <v>4528.4295139454061</v>
       </c>
       <c r="DL13" s="3">
         <f t="shared" si="78"/>
-        <v>4228.7065989577704</v>
+        <v>4483.145218805952</v>
       </c>
       <c r="DM13" s="3">
         <f t="shared" si="78"/>
-        <v>4186.4195329681925</v>
+        <v>4438.3137666178927</v>
       </c>
       <c r="DN13" s="3">
         <f t="shared" si="78"/>
-        <v>4144.5553376385105</v>
+        <v>4393.9306289517135</v>
       </c>
       <c r="DO13" s="3">
         <f t="shared" ref="DO13:EI13" si="79">DN13*(1+$BD$19)</f>
-        <v>4103.1097842621257</v>
+        <v>4349.9913226621966</v>
       </c>
       <c r="DP13" s="3">
         <f t="shared" si="79"/>
-        <v>4062.0786864195043</v>
+        <v>4306.4914094355745</v>
       </c>
       <c r="DQ13" s="3">
         <f t="shared" si="79"/>
-        <v>4021.4578995553093</v>
+        <v>4263.4264953412185</v>
       </c>
       <c r="DR13" s="3">
         <f t="shared" si="79"/>
-        <v>3981.2433205597563</v>
+        <v>4220.7922303878058</v>
       </c>
       <c r="DS13" s="3">
         <f t="shared" si="79"/>
-        <v>3941.4308873541586</v>
+        <v>4178.5843080839277</v>
       </c>
       <c r="DT13" s="3">
         <f t="shared" si="79"/>
-        <v>3902.0165784806168</v>
+        <v>4136.7984650030885</v>
       </c>
       <c r="DU13" s="3">
         <f t="shared" si="79"/>
-        <v>3862.9964126958107</v>
+        <v>4095.4304803530576</v>
       </c>
       <c r="DV13" s="3">
         <f t="shared" si="79"/>
-        <v>3824.3664485688528</v>
+        <v>4054.4761755495269</v>
       </c>
       <c r="DW13" s="3">
         <f t="shared" si="79"/>
-        <v>3786.1227840831643</v>
+        <v>4013.9314137940314</v>
       </c>
       <c r="DX13" s="3">
         <f t="shared" si="79"/>
-        <v>3748.2615562423325</v>
+        <v>3973.7920996560911</v>
       </c>
       <c r="DY13" s="3">
         <f t="shared" si="79"/>
-        <v>3710.7789406799093</v>
+        <v>3934.05417865953</v>
       </c>
       <c r="DZ13" s="3">
         <f t="shared" si="79"/>
-        <v>3673.6711512731104</v>
+        <v>3894.7136368729348</v>
       </c>
       <c r="EA13" s="3">
         <f t="shared" si="79"/>
-        <v>3636.9344397603791</v>
+        <v>3855.7665005042054</v>
       </c>
       <c r="EB13" s="3">
         <f t="shared" si="79"/>
-        <v>3600.5650953627751</v>
+        <v>3817.2088354991633</v>
       </c>
       <c r="EC13" s="3">
         <f t="shared" si="79"/>
-        <v>3564.5594444091471</v>
+        <v>3779.0367471441718</v>
       </c>
       <c r="ED13" s="3">
         <f t="shared" si="79"/>
-        <v>3528.9138499650558</v>
+        <v>3741.2463796727302</v>
       </c>
       <c r="EE13" s="3">
         <f t="shared" si="79"/>
-        <v>3493.6247114654052</v>
+        <v>3703.8339158760027</v>
       </c>
       <c r="EF13" s="3">
         <f t="shared" si="79"/>
-        <v>3458.688464350751</v>
+        <v>3666.7955767172425</v>
       </c>
       <c r="EG13" s="3">
         <f t="shared" si="79"/>
-        <v>3424.1015797072437</v>
+        <v>3630.1276209500702</v>
       </c>
       <c r="EH13" s="3">
         <f t="shared" si="79"/>
-        <v>3389.8605639101711</v>
+        <v>3593.8263447405693</v>
       </c>
       <c r="EI13" s="3">
         <f t="shared" si="79"/>
-        <v>3355.9619582710693</v>
+        <v>3557.8880812931634</v>
       </c>
     </row>
     <row r="14" spans="2:139" x14ac:dyDescent="0.3">
@@ -3590,10 +3587,12 @@
         <v>3980</v>
       </c>
       <c r="AG14" s="6">
-        <v>3980</v>
+        <f>3976</f>
+        <v>3976</v>
       </c>
       <c r="AH14" s="6">
-        <v>3980</v>
+        <f>3976</f>
+        <v>3976</v>
       </c>
       <c r="AJ14" s="6">
         <v>3974</v>
@@ -3623,37 +3622,48 @@
         <v>3963.5</v>
       </c>
       <c r="AQ14" s="6">
-        <v>3980</v>
+        <f>3976</f>
+        <v>3976</v>
       </c>
       <c r="AR14" s="6">
-        <v>3980</v>
+        <f>3976</f>
+        <v>3976</v>
       </c>
       <c r="AS14" s="6">
-        <v>3980</v>
+        <f>3976</f>
+        <v>3976</v>
       </c>
       <c r="AT14" s="6">
-        <v>3980</v>
+        <f>3976</f>
+        <v>3976</v>
       </c>
       <c r="AU14" s="6">
-        <v>3980</v>
+        <f>3976</f>
+        <v>3976</v>
       </c>
       <c r="AV14" s="6">
-        <v>3980</v>
+        <f>3976</f>
+        <v>3976</v>
       </c>
       <c r="AW14" s="6">
-        <v>3980</v>
+        <f>3976</f>
+        <v>3976</v>
       </c>
       <c r="AX14" s="6">
-        <v>3980</v>
+        <f>3976</f>
+        <v>3976</v>
       </c>
       <c r="AY14" s="6">
-        <v>3980</v>
+        <f>3976</f>
+        <v>3976</v>
       </c>
       <c r="AZ14" s="6">
-        <v>3980</v>
+        <f>3976</f>
+        <v>3976</v>
       </c>
       <c r="BA14" s="6">
-        <v>3980</v>
+        <f>3976</f>
+        <v>3976</v>
       </c>
     </row>
     <row r="15" spans="2:139" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -3782,11 +3792,11 @@
       </c>
       <c r="AG15" s="9">
         <f t="shared" si="95"/>
-        <v>0.12361125628140701</v>
+        <v>0.61544265593561365</v>
       </c>
       <c r="AH15" s="9">
         <f t="shared" si="95"/>
-        <v>7.8509748743718646E-2</v>
+        <v>0.18746595573440666</v>
       </c>
       <c r="AJ15" s="9">
         <f>AJ13/AJ14</f>
@@ -3818,47 +3828,47 @@
       </c>
       <c r="AQ15" s="9">
         <f t="shared" si="96"/>
-        <v>0.31141748743718034</v>
+        <v>0.91231505030180704</v>
       </c>
       <c r="AR15" s="9">
         <f t="shared" si="96"/>
-        <v>1.0706405591708545</v>
+        <v>1.1045317095975864</v>
       </c>
       <c r="AS15" s="9">
         <f t="shared" si="96"/>
-        <v>1.6690523454924637</v>
+        <v>1.7762287250965805</v>
       </c>
       <c r="AT15" s="9">
         <f t="shared" si="96"/>
-        <v>1.8054402792353774</v>
+        <v>1.9177209091057661</v>
       </c>
       <c r="AU15" s="9">
         <f t="shared" si="96"/>
-        <v>1.8851506615581446</v>
+        <v>2.0006283506457048</v>
       </c>
       <c r="AV15" s="9">
         <f t="shared" si="96"/>
-        <v>1.904026518499746</v>
+        <v>2.020653877433737</v>
       </c>
       <c r="AW15" s="9">
         <f t="shared" ref="AW15:BA15" si="97">AW13/AW14</f>
-        <v>1.9230912557623927</v>
+        <v>2.040879755706059</v>
       </c>
       <c r="AX15" s="9">
         <f t="shared" si="97"/>
-        <v>1.9423467627580551</v>
+        <v>2.0613079894585935</v>
       </c>
       <c r="AY15" s="9">
         <f t="shared" si="97"/>
-        <v>1.9617949477958634</v>
+        <v>2.081940602729631</v>
       </c>
       <c r="AZ15" s="9">
         <f t="shared" si="97"/>
-        <v>1.9814377382711019</v>
+        <v>2.1027796398002621</v>
       </c>
       <c r="BA15" s="9">
         <f t="shared" si="97"/>
-        <v>2.0012770808560782</v>
+        <v>2.1238271653968144</v>
       </c>
     </row>
     <row r="17" spans="2:56" x14ac:dyDescent="0.3">
@@ -3987,11 +3997,11 @@
       </c>
       <c r="AG17" s="10">
         <f t="shared" si="101"/>
-        <v>0.12</v>
+        <v>0.14095460482051689</v>
       </c>
       <c r="AH17" s="10">
         <f t="shared" si="101"/>
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="AJ17" s="10">
         <f t="shared" ref="AJ17:AV17" si="102">AJ5/AJ3</f>
@@ -4023,7 +4033,7 @@
       </c>
       <c r="AQ17" s="10">
         <f t="shared" si="102"/>
-        <v>0.12267852325376029</v>
+        <v>0.13080002842883012</v>
       </c>
       <c r="AR17" s="10">
         <f t="shared" si="102"/>
@@ -4192,11 +4202,11 @@
       </c>
       <c r="AG18" s="10">
         <f t="shared" si="107"/>
-        <v>1.2807045755352965E-2</v>
+        <v>3.0830727826809672E-2</v>
       </c>
       <c r="AH18" s="10">
         <f t="shared" si="107"/>
-        <v>7.8392700342048045E-3</v>
+        <v>1.8353984822222148E-2</v>
       </c>
       <c r="AJ18" s="10">
         <f t="shared" ref="AJ18:AV18" si="108">AJ8/AJ3</f>
@@ -4228,47 +4238,47 @@
       </c>
       <c r="AQ18" s="10">
         <f t="shared" si="108"/>
-        <v>9.7281075704707502E-3</v>
+        <v>1.7279428489075137E-2</v>
       </c>
       <c r="AR18" s="10">
         <f t="shared" si="108"/>
-        <v>2.4487481862301153E-2</v>
+        <v>2.3408849981809216E-2</v>
       </c>
       <c r="AS18" s="10">
         <f t="shared" si="108"/>
-        <v>3.7531112193196332E-2</v>
+        <v>3.7469465220597443E-2</v>
       </c>
       <c r="AT18" s="10">
         <f t="shared" si="108"/>
-        <v>3.952079933507599E-2</v>
+        <v>3.9460349391071285E-2</v>
       </c>
       <c r="AU18" s="10">
         <f t="shared" si="108"/>
-        <v>4.0505889537673305E-2</v>
+        <v>4.0446032240178433E-2</v>
       </c>
       <c r="AV18" s="10">
         <f t="shared" si="108"/>
-        <v>4.0505889537673298E-2</v>
+        <v>4.0446032240178419E-2</v>
       </c>
       <c r="AW18" s="10">
         <f t="shared" ref="AW18:BA18" si="109">AW8/AW3</f>
-        <v>4.0505889537673284E-2</v>
+        <v>4.0446032240178419E-2</v>
       </c>
       <c r="AX18" s="10">
         <f t="shared" si="109"/>
-        <v>4.0505889537673291E-2</v>
+        <v>4.0446032240178419E-2</v>
       </c>
       <c r="AY18" s="10">
         <f t="shared" si="109"/>
-        <v>4.0505889537673277E-2</v>
+        <v>4.0446032240178426E-2</v>
       </c>
       <c r="AZ18" s="10">
         <f t="shared" si="109"/>
-        <v>4.0505889537673284E-2</v>
+        <v>4.0446032240178439E-2</v>
       </c>
       <c r="BA18" s="10">
         <f t="shared" si="109"/>
-        <v>4.050588953767327E-2</v>
+        <v>4.0446032240178439E-2</v>
       </c>
     </row>
     <row r="19" spans="2:56" x14ac:dyDescent="0.3">
@@ -4381,11 +4391,11 @@
       </c>
       <c r="AG19" s="11">
         <f t="shared" ref="AG19:AG20" si="129">AG6/AC6-1</f>
-        <v>1.0000000000000009E-2</v>
+        <v>0.11563517915309451</v>
       </c>
       <c r="AH19" s="11">
         <f t="shared" ref="AH19:AH20" si="130">AH6/AD6-1</f>
-        <v>1.0000000000000009E-2</v>
+        <v>2.0000000000000018E-2</v>
       </c>
       <c r="AK19" s="11">
         <f>AK6/AJ6-1</f>
@@ -4413,11 +4423,11 @@
       </c>
       <c r="AQ19" s="11">
         <f t="shared" si="131"/>
-        <v>1.3155438903470484E-2</v>
+        <v>4.1075143384854851E-2</v>
       </c>
       <c r="AR19" s="11">
         <f t="shared" si="131"/>
-        <v>-5.0000000000000044E-2</v>
+        <v>-2.0000000000000018E-2</v>
       </c>
       <c r="AS19" s="11">
         <f t="shared" si="131"/>
@@ -4572,7 +4582,7 @@
       </c>
       <c r="AG20" s="11">
         <f t="shared" si="129"/>
-        <v>1.0000000000000009E-2</v>
+        <v>4.9405646359583999E-2</v>
       </c>
       <c r="AH20" s="11">
         <f t="shared" si="130"/>
@@ -4604,7 +4614,7 @@
       </c>
       <c r="AQ20" s="11">
         <f t="shared" si="138"/>
-        <v>-1.5472312703583846E-3</v>
+        <v>8.0510314875135158E-3</v>
       </c>
       <c r="AR20" s="11">
         <f t="shared" si="138"/>
@@ -4763,11 +4773,11 @@
       </c>
       <c r="AG21" s="10">
         <f t="shared" ref="AG21" si="143">AG3/AC3-1</f>
-        <v>5.0000000000000044E-2</v>
+        <v>9.3904234132825337E-2</v>
       </c>
       <c r="AH21" s="10">
         <f t="shared" ref="AH21" si="144">AH3/AD3-1</f>
-        <v>5.0000000000000044E-2</v>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="AK21" s="10">
         <f>AK3/AJ3-1</f>
@@ -4795,15 +4805,15 @@
       </c>
       <c r="AQ21" s="10">
         <f t="shared" si="145"/>
-        <v>2.6911163725998888E-2</v>
+        <v>4.0480993772703755E-2</v>
       </c>
       <c r="AR21" s="10">
         <f t="shared" si="145"/>
-        <v>5.0000000000000044E-2</v>
+        <v>6.0000000000000053E-2</v>
       </c>
       <c r="AS21" s="10">
         <f t="shared" si="145"/>
-        <v>4.0000000000000036E-2</v>
+        <v>5.0000000000000044E-2</v>
       </c>
       <c r="AT21" s="10">
         <f t="shared" si="145"/>
@@ -4842,7 +4852,7 @@
       </c>
       <c r="BD21" s="6">
         <f>NPV(BD20,AQ13:EI13)</f>
-        <v>129785.60162908456</v>
+        <v>139706.79355484099</v>
       </c>
     </row>
     <row r="22" spans="2:56" x14ac:dyDescent="0.3">
@@ -4971,7 +4981,7 @@
       </c>
       <c r="AG22" s="11">
         <f t="shared" si="153"/>
-        <v>0.2</v>
+        <v>-0.34653465346534651</v>
       </c>
       <c r="AH22" s="11">
         <f t="shared" si="153"/>
@@ -5007,7 +5017,7 @@
       </c>
       <c r="AQ22" s="11">
         <f t="shared" si="154"/>
-        <v>0.4227469803472621</v>
+        <v>7.0340548507464351E-2</v>
       </c>
       <c r="AR22" s="11">
         <f t="shared" si="154"/>
@@ -5183,11 +5193,11 @@
       </c>
       <c r="AG23" s="10">
         <f t="shared" si="158"/>
-        <v>1.0142556147924576E-2</v>
+        <v>4.8422844025804407E-2</v>
       </c>
       <c r="AH23" s="10">
         <f t="shared" si="158"/>
-        <v>6.1726438641250651E-3</v>
+        <v>1.4585347507399683E-2</v>
       </c>
       <c r="AJ23" s="10">
         <f t="shared" ref="AJ23:AV23" si="159">AJ13/AJ3</f>
@@ -5219,54 +5229,54 @@
       </c>
       <c r="AQ23" s="10">
         <f t="shared" si="159"/>
-        <v>6.5243949911129705E-3</v>
+        <v>1.8845346020737796E-2</v>
       </c>
       <c r="AR23" s="10">
         <f t="shared" si="159"/>
-        <v>2.1362478660987037E-2</v>
+        <v>2.1524427036138275E-2</v>
       </c>
       <c r="AS23" s="10">
         <f t="shared" si="159"/>
-        <v>3.2021713551653355E-2</v>
+        <v>3.2965753084163572E-2</v>
       </c>
       <c r="AT23" s="10">
         <f t="shared" si="159"/>
-        <v>3.3629507985446075E-2</v>
+        <v>3.455511088745903E-2</v>
       </c>
       <c r="AU23" s="10">
         <f t="shared" si="159"/>
-        <v>3.4425739584797589E-2</v>
+        <v>3.5342163738146387E-2</v>
       </c>
       <c r="AV23" s="10">
         <f t="shared" si="159"/>
-        <v>3.4426179856345794E-2</v>
+        <v>3.534250031517857E-2</v>
       </c>
       <c r="AW23" s="10">
         <f t="shared" ref="AW23:BA23" si="160">AW13/AW3</f>
-        <v>3.4426617948331871E-2</v>
+        <v>3.5342835225987849E-2</v>
       </c>
       <c r="AX23" s="10">
         <f t="shared" si="160"/>
-        <v>3.4427053871545751E-2</v>
+        <v>3.5343168478822802E-2</v>
       </c>
       <c r="AY23" s="10">
         <f t="shared" si="160"/>
-        <v>3.4427487636723902E-2</v>
+        <v>3.5343500081891271E-2</v>
       </c>
       <c r="AZ23" s="10">
         <f t="shared" si="160"/>
-        <v>3.4427919254549702E-2</v>
+        <v>3.5343830043360391E-2</v>
       </c>
       <c r="BA23" s="10">
         <f t="shared" si="160"/>
-        <v>3.4428348735653584E-2</v>
+        <v>3.5344158371356876E-2</v>
       </c>
       <c r="BC23" s="1" t="s">
         <v>41</v>
       </c>
       <c r="BD23" s="6">
         <f>BD21+BD22</f>
-        <v>16432.601629084558</v>
+        <v>26353.793554840988</v>
       </c>
     </row>
     <row r="24" spans="2:56" x14ac:dyDescent="0.3">
@@ -5275,7 +5285,7 @@
       </c>
       <c r="BD24" s="4">
         <f>BD23/AV14</f>
-        <v>4.1287943791669743</v>
+        <v>6.6282176948795239</v>
       </c>
     </row>
     <row r="25" spans="2:56" x14ac:dyDescent="0.3">
@@ -5284,7 +5294,7 @@
       </c>
       <c r="BD25" s="4">
         <f>Main!D3</f>
-        <v>10.67</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="26" spans="2:56" x14ac:dyDescent="0.3">
@@ -5293,7 +5303,7 @@
       </c>
       <c r="BD26" s="10">
         <f>BD24/BD25-1</f>
-        <v>-0.61304644993749069</v>
+        <v>-0.51829813263956948</v>
       </c>
     </row>
     <row r="27" spans="2:56" x14ac:dyDescent="0.3">
